--- a/dist/Kursanwahl_Vorlage.xlsx
+++ b/dist/Kursanwahl_Vorlage.xlsx
@@ -2,10 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anleitung" sheetId="1" r:id="R79ed1bcc86b54ac2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workshops" sheetId="2" r:id="R4da7409a2dfb4ee9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kursanwahl" sheetId="3" r:id="R748ed728fe854e94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sperrungen" sheetId="4" r:id="R9c899b254b574e0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anleitung" sheetId="1" r:id="R3021059d2c6d46bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workshops" sheetId="2" r:id="R857f45bdfb4c431d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jahrgangsbelegung" sheetId="3" r:id="R0363f534afc04533"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teamregeln" sheetId="4" r:id="R533c7c3298de49dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kursanwahl" sheetId="5" r:id="R5bbd9d90aee6436f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sperrungen" sheetId="6" r:id="Rf98abd005d6743da"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -67,25 +69,19 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -94,7 +90,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -320,99 +316,99 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="85" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="95" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="12" t="str">
-        <x:v>Workshop-Zuteilung – vollständige Importvorlage</x:v>
+      <x:c r="A1" s="10" t="str">
+        <x:v>Workshop-Zuteilung – vollständige Importvorlage V9.3</x:v>
       </x:c>
-      <x:c r="B1" s="12"/>
-      <x:c r="C1" s="12"/>
-      <x:c r="D1" s="12"/>
+      <x:c r="B1" s="10"/>
+      <x:c r="C1" s="10"/>
+      <x:c r="D1" s="10"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="13"/>
-      <x:c r="B2" s="13"/>
-      <x:c r="C2" s="13"/>
-      <x:c r="D2" s="13"/>
+      <x:c r="A2" s="11"/>
+      <x:c r="B2" s="11"/>
+      <x:c r="C2" s="11"/>
+      <x:c r="D2" s="11"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="14" t="str">
+      <x:c r="A3" s="12" t="str">
         <x:v>Blatt</x:v>
       </x:c>
-      <x:c r="B3" s="14" t="str">
+      <x:c r="B3" s="12" t="str">
         <x:v>Verwendung</x:v>
       </x:c>
-      <x:c r="C3" s="13"/>
-      <x:c r="D3" s="13"/>
+      <x:c r="C3" s="11"/>
+      <x:c r="D3" s="11"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="13" t="str">
+      <x:c r="A4" s="11" t="str">
         <x:v>Workshops</x:v>
       </x:c>
-      <x:c r="B4" s="13" t="str">
-        <x:v>Kurse/Durchführungen einschließlich Mindest- und Maximalbelegung pflegen.</x:v>
+      <x:c r="B4" s="11" t="str">
+        <x:v>Kursarten und Durchführungen einschließlich Min./Max., Klassenbereich und Bildungsgang.</x:v>
       </x:c>
-      <x:c r="C4" s="13"/>
-      <x:c r="D4" s="13"/>
+      <x:c r="C4" s="11"/>
+      <x:c r="D4" s="11"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="13" t="str">
+      <x:c r="A5" s="11" t="str">
+        <x:v>Jahrgangsbelegung</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>Optionale harte Mindest- und Höchstzahlen je Jahrgang. Leer = keine Vorgabe.</x:v>
+      </x:c>
+      <x:c r="C5" s="11"/>
+      <x:c r="D5" s="11"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="11" t="str">
+        <x:v>Teamregeln</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>Optionale harte Teamgrößen für Jahrgangsgruppen. Beispiel: 8,9 / 4 bedeutet zusammen 0, 4, 8, 12 … Schüler.</x:v>
+      </x:c>
+      <x:c r="C6" s="11"/>
+      <x:c r="D6" s="11"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="11" t="str">
         <x:v>Kursanwahl</x:v>
       </x:c>
-      <x:c r="B5" s="13" t="str">
-        <x:v>Teilnehmerdaten und vier Wünsche erfassen.</x:v>
+      <x:c r="B7" s="11" t="str">
+        <x:v>Teilnehmer und vier Wünsche.</x:v>
       </x:c>
-      <x:c r="C5" s="13"/>
-      <x:c r="D5" s="13"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="13" t="str">
+      <x:c r="C7" s="11"/>
+      <x:c r="D7" s="11"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="11" t="str">
         <x:v>Sperrungen</x:v>
       </x:c>
-      <x:c r="B6" s="13" t="str">
-        <x:v>Unerlaubte Kombinationen Person ↔ konkrete Durchführung eintragen.</x:v>
+      <x:c r="B8" s="11" t="str">
+        <x:v>Unerlaubte Person-/Durchführungs-Kombinationen.</x:v>
       </x:c>
-      <x:c r="C6" s="13"/>
-      <x:c r="D6" s="13"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="13" t="str"/>
-      <x:c r="B7" s="13" t="str"/>
-      <x:c r="C7" s="13"/>
-      <x:c r="D7" s="13"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="13" t="str">
-        <x:v>Wünsche</x:v>
+      <x:c r="C8" s="11"/>
+      <x:c r="D8" s="11"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="11" t="str"/>
+      <x:c r="B9" s="11" t="str"/>
+      <x:c r="C9" s="11"/>
+      <x:c r="D9" s="11"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="11" t="str">
+        <x:v>Wichtig</x:v>
       </x:c>
-      <x:c r="B8" s="13" t="str">
-        <x:v>Erst- bis Viertwunsch verwenden die Kursart-ID aus Workshops.</x:v>
+      <x:c r="B10" s="11" t="str">
+        <x:v>Kursart-ID ist der gemeinsame Wunsch; Durchführungs-ID bezeichnet die konkrete Gruppe.</x:v>
       </x:c>
-      <x:c r="C8" s="13"/>
-      <x:c r="D8" s="13"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="13" t="str">
-        <x:v>Feste Setzung</x:v>
-      </x:c>
-      <x:c r="B9" s="13" t="str">
-        <x:v>Verwendet die konkrete Durchführungs-ID aus Workshops.</x:v>
-      </x:c>
-      <x:c r="C9" s="13"/>
-      <x:c r="D9" s="13"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="13" t="str">
-        <x:v>Kohortenminimum</x:v>
-      </x:c>
-      <x:c r="B10" s="13" t="str">
-        <x:v>Leer = globaler Wert der Anwendung, 0 = aus, ab 2 = eigener harter Wert für diese Durchführung.</x:v>
-      </x:c>
-      <x:c r="C10" s="13"/>
-      <x:c r="D10" s="13"/>
+      <x:c r="C10" s="11"/>
+      <x:c r="D10" s="11"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -428,7 +424,7 @@
   <x:cols>
     <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
@@ -440,37 +436,37 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="20" t="str">
+      <x:c r="A1" s="18" t="str">
         <x:v>Durchführungs-ID</x:v>
       </x:c>
-      <x:c r="B1" s="20" t="str">
+      <x:c r="B1" s="18" t="str">
         <x:v>Kursart-ID</x:v>
       </x:c>
-      <x:c r="C1" s="20" t="str">
+      <x:c r="C1" s="18" t="str">
         <x:v>Kursart</x:v>
       </x:c>
-      <x:c r="D1" s="20" t="str">
+      <x:c r="D1" s="18" t="str">
         <x:v>Gruppe</x:v>
       </x:c>
-      <x:c r="E1" s="20" t="str">
+      <x:c r="E1" s="18" t="str">
         <x:v>Klasse von</x:v>
       </x:c>
-      <x:c r="F1" s="20" t="str">
+      <x:c r="F1" s="18" t="str">
         <x:v>Klasse bis</x:v>
       </x:c>
-      <x:c r="G1" s="20" t="str">
+      <x:c r="G1" s="18" t="str">
         <x:v>Bildungsgang</x:v>
       </x:c>
-      <x:c r="H1" s="20" t="str">
+      <x:c r="H1" s="18" t="str">
         <x:v>Kohortenminimum</x:v>
       </x:c>
-      <x:c r="I1" s="20" t="str">
+      <x:c r="I1" s="18" t="str">
         <x:v>Mindestbelegung</x:v>
       </x:c>
-      <x:c r="J1" s="20" t="str">
+      <x:c r="J1" s="18" t="str">
         <x:v>Maximalbelegung</x:v>
       </x:c>
-      <x:c r="K1" s="20" t="str">
+      <x:c r="K1" s="18" t="str">
         <x:v>Pflicht/Optional</x:v>
       </x:c>
     </x:row>
@@ -881,9 +877,1643 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="18" t="str">
+        <x:v>Durchführungs-ID</x:v>
+      </x:c>
+      <x:c r="B1" s="18" t="str">
+        <x:v>Jahrgang</x:v>
+      </x:c>
+      <x:c r="C1" s="18" t="str">
+        <x:v>Minimum</x:v>
+      </x:c>
+      <x:c r="D1" s="18" t="str">
+        <x:v>Maximum</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str"/>
+      <x:c r="B2" t="str"/>
+      <x:c r="C2" t="str"/>
+      <x:c r="D2" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str"/>
+      <x:c r="B3" t="str"/>
+      <x:c r="C3" t="str"/>
+      <x:c r="D3" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str"/>
+      <x:c r="B4" t="str"/>
+      <x:c r="C4" t="str"/>
+      <x:c r="D4" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str"/>
+      <x:c r="B5" t="str"/>
+      <x:c r="C5" t="str"/>
+      <x:c r="D5" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str"/>
+      <x:c r="B6" t="str"/>
+      <x:c r="C6" t="str"/>
+      <x:c r="D6" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str"/>
+      <x:c r="B7" t="str"/>
+      <x:c r="C7" t="str"/>
+      <x:c r="D7" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str"/>
+      <x:c r="B8" t="str"/>
+      <x:c r="C8" t="str"/>
+      <x:c r="D8" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str"/>
+      <x:c r="B9" t="str"/>
+      <x:c r="C9" t="str"/>
+      <x:c r="D9" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str"/>
+      <x:c r="B10" t="str"/>
+      <x:c r="C10" t="str"/>
+      <x:c r="D10" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str"/>
+      <x:c r="B11" t="str"/>
+      <x:c r="C11" t="str"/>
+      <x:c r="D11" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str"/>
+      <x:c r="B12" t="str"/>
+      <x:c r="C12" t="str"/>
+      <x:c r="D12" t="str"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str"/>
+      <x:c r="B13" t="str"/>
+      <x:c r="C13" t="str"/>
+      <x:c r="D13" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str"/>
+      <x:c r="B14" t="str"/>
+      <x:c r="C14" t="str"/>
+      <x:c r="D14" t="str"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str"/>
+      <x:c r="B15" t="str"/>
+      <x:c r="C15" t="str"/>
+      <x:c r="D15" t="str"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str"/>
+      <x:c r="B16" t="str"/>
+      <x:c r="C16" t="str"/>
+      <x:c r="D16" t="str"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str"/>
+      <x:c r="B17" t="str"/>
+      <x:c r="C17" t="str"/>
+      <x:c r="D17" t="str"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str"/>
+      <x:c r="B18" t="str"/>
+      <x:c r="C18" t="str"/>
+      <x:c r="D18" t="str"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str"/>
+      <x:c r="B19" t="str"/>
+      <x:c r="C19" t="str"/>
+      <x:c r="D19" t="str"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str"/>
+      <x:c r="B20" t="str"/>
+      <x:c r="C20" t="str"/>
+      <x:c r="D20" t="str"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str"/>
+      <x:c r="B21" t="str"/>
+      <x:c r="C21" t="str"/>
+      <x:c r="D21" t="str"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str"/>
+      <x:c r="B22" t="str"/>
+      <x:c r="C22" t="str"/>
+      <x:c r="D22" t="str"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str"/>
+      <x:c r="B23" t="str"/>
+      <x:c r="C23" t="str"/>
+      <x:c r="D23" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str"/>
+      <x:c r="B24" t="str"/>
+      <x:c r="C24" t="str"/>
+      <x:c r="D24" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str"/>
+      <x:c r="B25" t="str"/>
+      <x:c r="C25" t="str"/>
+      <x:c r="D25" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str"/>
+      <x:c r="B26" t="str"/>
+      <x:c r="C26" t="str"/>
+      <x:c r="D26" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str"/>
+      <x:c r="B27" t="str"/>
+      <x:c r="C27" t="str"/>
+      <x:c r="D27" t="str"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str"/>
+      <x:c r="B28" t="str"/>
+      <x:c r="C28" t="str"/>
+      <x:c r="D28" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str"/>
+      <x:c r="B29" t="str"/>
+      <x:c r="C29" t="str"/>
+      <x:c r="D29" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str"/>
+      <x:c r="B30" t="str"/>
+      <x:c r="C30" t="str"/>
+      <x:c r="D30" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str"/>
+      <x:c r="B31" t="str"/>
+      <x:c r="C31" t="str"/>
+      <x:c r="D31" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str"/>
+      <x:c r="B32" t="str"/>
+      <x:c r="C32" t="str"/>
+      <x:c r="D32" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str"/>
+      <x:c r="B33" t="str"/>
+      <x:c r="C33" t="str"/>
+      <x:c r="D33" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str"/>
+      <x:c r="B34" t="str"/>
+      <x:c r="C34" t="str"/>
+      <x:c r="D34" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str"/>
+      <x:c r="B35" t="str"/>
+      <x:c r="C35" t="str"/>
+      <x:c r="D35" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str"/>
+      <x:c r="B36" t="str"/>
+      <x:c r="C36" t="str"/>
+      <x:c r="D36" t="str"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str"/>
+      <x:c r="B37" t="str"/>
+      <x:c r="C37" t="str"/>
+      <x:c r="D37" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str"/>
+      <x:c r="B38" t="str"/>
+      <x:c r="C38" t="str"/>
+      <x:c r="D38" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str"/>
+      <x:c r="B39" t="str"/>
+      <x:c r="C39" t="str"/>
+      <x:c r="D39" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str"/>
+      <x:c r="B40" t="str"/>
+      <x:c r="C40" t="str"/>
+      <x:c r="D40" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str"/>
+      <x:c r="B41" t="str"/>
+      <x:c r="C41" t="str"/>
+      <x:c r="D41" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str"/>
+      <x:c r="B42" t="str"/>
+      <x:c r="C42" t="str"/>
+      <x:c r="D42" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str"/>
+      <x:c r="B43" t="str"/>
+      <x:c r="C43" t="str"/>
+      <x:c r="D43" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str"/>
+      <x:c r="B44" t="str"/>
+      <x:c r="C44" t="str"/>
+      <x:c r="D44" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str"/>
+      <x:c r="B45" t="str"/>
+      <x:c r="C45" t="str"/>
+      <x:c r="D45" t="str"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str"/>
+      <x:c r="B46" t="str"/>
+      <x:c r="C46" t="str"/>
+      <x:c r="D46" t="str"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str"/>
+      <x:c r="B47" t="str"/>
+      <x:c r="C47" t="str"/>
+      <x:c r="D47" t="str"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str"/>
+      <x:c r="B48" t="str"/>
+      <x:c r="C48" t="str"/>
+      <x:c r="D48" t="str"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str"/>
+      <x:c r="B49" t="str"/>
+      <x:c r="C49" t="str"/>
+      <x:c r="D49" t="str"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str"/>
+      <x:c r="B50" t="str"/>
+      <x:c r="C50" t="str"/>
+      <x:c r="D50" t="str"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str"/>
+      <x:c r="B51" t="str"/>
+      <x:c r="C51" t="str"/>
+      <x:c r="D51" t="str"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str"/>
+      <x:c r="B52" t="str"/>
+      <x:c r="C52" t="str"/>
+      <x:c r="D52" t="str"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="str"/>
+      <x:c r="B53" t="str"/>
+      <x:c r="C53" t="str"/>
+      <x:c r="D53" t="str"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="str"/>
+      <x:c r="B54" t="str"/>
+      <x:c r="C54" t="str"/>
+      <x:c r="D54" t="str"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str"/>
+      <x:c r="B55" t="str"/>
+      <x:c r="C55" t="str"/>
+      <x:c r="D55" t="str"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str"/>
+      <x:c r="B56" t="str"/>
+      <x:c r="C56" t="str"/>
+      <x:c r="D56" t="str"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="str"/>
+      <x:c r="B57" t="str"/>
+      <x:c r="C57" t="str"/>
+      <x:c r="D57" t="str"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str"/>
+      <x:c r="B58" t="str"/>
+      <x:c r="C58" t="str"/>
+      <x:c r="D58" t="str"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="str"/>
+      <x:c r="B59" t="str"/>
+      <x:c r="C59" t="str"/>
+      <x:c r="D59" t="str"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" t="str"/>
+      <x:c r="B60" t="str"/>
+      <x:c r="C60" t="str"/>
+      <x:c r="D60" t="str"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="str"/>
+      <x:c r="B61" t="str"/>
+      <x:c r="C61" t="str"/>
+      <x:c r="D61" t="str"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="str"/>
+      <x:c r="B62" t="str"/>
+      <x:c r="C62" t="str"/>
+      <x:c r="D62" t="str"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="str"/>
+      <x:c r="B63" t="str"/>
+      <x:c r="C63" t="str"/>
+      <x:c r="D63" t="str"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="str"/>
+      <x:c r="B64" t="str"/>
+      <x:c r="C64" t="str"/>
+      <x:c r="D64" t="str"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="str"/>
+      <x:c r="B65" t="str"/>
+      <x:c r="C65" t="str"/>
+      <x:c r="D65" t="str"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str"/>
+      <x:c r="B66" t="str"/>
+      <x:c r="C66" t="str"/>
+      <x:c r="D66" t="str"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str"/>
+      <x:c r="B67" t="str"/>
+      <x:c r="C67" t="str"/>
+      <x:c r="D67" t="str"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str"/>
+      <x:c r="B68" t="str"/>
+      <x:c r="C68" t="str"/>
+      <x:c r="D68" t="str"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="str"/>
+      <x:c r="B69" t="str"/>
+      <x:c r="C69" t="str"/>
+      <x:c r="D69" t="str"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str"/>
+      <x:c r="B70" t="str"/>
+      <x:c r="C70" t="str"/>
+      <x:c r="D70" t="str"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str"/>
+      <x:c r="B71" t="str"/>
+      <x:c r="C71" t="str"/>
+      <x:c r="D71" t="str"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="str"/>
+      <x:c r="B72" t="str"/>
+      <x:c r="C72" t="str"/>
+      <x:c r="D72" t="str"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="str"/>
+      <x:c r="B73" t="str"/>
+      <x:c r="C73" t="str"/>
+      <x:c r="D73" t="str"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="str"/>
+      <x:c r="B74" t="str"/>
+      <x:c r="C74" t="str"/>
+      <x:c r="D74" t="str"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="str"/>
+      <x:c r="B75" t="str"/>
+      <x:c r="C75" t="str"/>
+      <x:c r="D75" t="str"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="str"/>
+      <x:c r="B76" t="str"/>
+      <x:c r="C76" t="str"/>
+      <x:c r="D76" t="str"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="str"/>
+      <x:c r="B77" t="str"/>
+      <x:c r="C77" t="str"/>
+      <x:c r="D77" t="str"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="str"/>
+      <x:c r="B78" t="str"/>
+      <x:c r="C78" t="str"/>
+      <x:c r="D78" t="str"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="str"/>
+      <x:c r="B79" t="str"/>
+      <x:c r="C79" t="str"/>
+      <x:c r="D79" t="str"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="str"/>
+      <x:c r="B80" t="str"/>
+      <x:c r="C80" t="str"/>
+      <x:c r="D80" t="str"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="str"/>
+      <x:c r="B81" t="str"/>
+      <x:c r="C81" t="str"/>
+      <x:c r="D81" t="str"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="str"/>
+      <x:c r="B82" t="str"/>
+      <x:c r="C82" t="str"/>
+      <x:c r="D82" t="str"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" t="str"/>
+      <x:c r="B83" t="str"/>
+      <x:c r="C83" t="str"/>
+      <x:c r="D83" t="str"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="str"/>
+      <x:c r="B84" t="str"/>
+      <x:c r="C84" t="str"/>
+      <x:c r="D84" t="str"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="str"/>
+      <x:c r="B85" t="str"/>
+      <x:c r="C85" t="str"/>
+      <x:c r="D85" t="str"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="str"/>
+      <x:c r="B86" t="str"/>
+      <x:c r="C86" t="str"/>
+      <x:c r="D86" t="str"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="str"/>
+      <x:c r="B87" t="str"/>
+      <x:c r="C87" t="str"/>
+      <x:c r="D87" t="str"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str"/>
+      <x:c r="B88" t="str"/>
+      <x:c r="C88" t="str"/>
+      <x:c r="D88" t="str"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str"/>
+      <x:c r="B89" t="str"/>
+      <x:c r="C89" t="str"/>
+      <x:c r="D89" t="str"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="str"/>
+      <x:c r="B90" t="str"/>
+      <x:c r="C90" t="str"/>
+      <x:c r="D90" t="str"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str"/>
+      <x:c r="B91" t="str"/>
+      <x:c r="C91" t="str"/>
+      <x:c r="D91" t="str"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str"/>
+      <x:c r="B92" t="str"/>
+      <x:c r="C92" t="str"/>
+      <x:c r="D92" t="str"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str"/>
+      <x:c r="B93" t="str"/>
+      <x:c r="C93" t="str"/>
+      <x:c r="D93" t="str"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str"/>
+      <x:c r="B94" t="str"/>
+      <x:c r="C94" t="str"/>
+      <x:c r="D94" t="str"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str"/>
+      <x:c r="B95" t="str"/>
+      <x:c r="C95" t="str"/>
+      <x:c r="D95" t="str"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str"/>
+      <x:c r="B96" t="str"/>
+      <x:c r="C96" t="str"/>
+      <x:c r="D96" t="str"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str"/>
+      <x:c r="B97" t="str"/>
+      <x:c r="C97" t="str"/>
+      <x:c r="D97" t="str"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str"/>
+      <x:c r="B98" t="str"/>
+      <x:c r="C98" t="str"/>
+      <x:c r="D98" t="str"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str"/>
+      <x:c r="B99" t="str"/>
+      <x:c r="C99" t="str"/>
+      <x:c r="D99" t="str"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str"/>
+      <x:c r="B100" t="str"/>
+      <x:c r="C100" t="str"/>
+      <x:c r="D100" t="str"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str"/>
+      <x:c r="B101" t="str"/>
+      <x:c r="C101" t="str"/>
+      <x:c r="D101" t="str"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="str"/>
+      <x:c r="B102" t="str"/>
+      <x:c r="C102" t="str"/>
+      <x:c r="D102" t="str"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str"/>
+      <x:c r="B103" t="str"/>
+      <x:c r="C103" t="str"/>
+      <x:c r="D103" t="str"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str"/>
+      <x:c r="B104" t="str"/>
+      <x:c r="C104" t="str"/>
+      <x:c r="D104" t="str"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str"/>
+      <x:c r="B105" t="str"/>
+      <x:c r="C105" t="str"/>
+      <x:c r="D105" t="str"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str"/>
+      <x:c r="B106" t="str"/>
+      <x:c r="C106" t="str"/>
+      <x:c r="D106" t="str"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="str"/>
+      <x:c r="B107" t="str"/>
+      <x:c r="C107" t="str"/>
+      <x:c r="D107" t="str"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="str"/>
+      <x:c r="B108" t="str"/>
+      <x:c r="C108" t="str"/>
+      <x:c r="D108" t="str"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" t="str"/>
+      <x:c r="B109" t="str"/>
+      <x:c r="C109" t="str"/>
+      <x:c r="D109" t="str"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" t="str"/>
+      <x:c r="B110" t="str"/>
+      <x:c r="C110" t="str"/>
+      <x:c r="D110" t="str"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" t="str"/>
+      <x:c r="B111" t="str"/>
+      <x:c r="C111" t="str"/>
+      <x:c r="D111" t="str"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" t="str"/>
+      <x:c r="B112" t="str"/>
+      <x:c r="C112" t="str"/>
+      <x:c r="D112" t="str"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="str"/>
+      <x:c r="B113" t="str"/>
+      <x:c r="C113" t="str"/>
+      <x:c r="D113" t="str"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="str"/>
+      <x:c r="B114" t="str"/>
+      <x:c r="C114" t="str"/>
+      <x:c r="D114" t="str"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="str"/>
+      <x:c r="B115" t="str"/>
+      <x:c r="C115" t="str"/>
+      <x:c r="D115" t="str"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="str"/>
+      <x:c r="B116" t="str"/>
+      <x:c r="C116" t="str"/>
+      <x:c r="D116" t="str"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="str"/>
+      <x:c r="B117" t="str"/>
+      <x:c r="C117" t="str"/>
+      <x:c r="D117" t="str"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="str"/>
+      <x:c r="B118" t="str"/>
+      <x:c r="C118" t="str"/>
+      <x:c r="D118" t="str"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="str"/>
+      <x:c r="B119" t="str"/>
+      <x:c r="C119" t="str"/>
+      <x:c r="D119" t="str"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str"/>
+      <x:c r="B120" t="str"/>
+      <x:c r="C120" t="str"/>
+      <x:c r="D120" t="str"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str"/>
+      <x:c r="B121" t="str"/>
+      <x:c r="C121" t="str"/>
+      <x:c r="D121" t="str"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="str"/>
+      <x:c r="B122" t="str"/>
+      <x:c r="C122" t="str"/>
+      <x:c r="D122" t="str"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="str"/>
+      <x:c r="B123" t="str"/>
+      <x:c r="C123" t="str"/>
+      <x:c r="D123" t="str"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="str"/>
+      <x:c r="B124" t="str"/>
+      <x:c r="C124" t="str"/>
+      <x:c r="D124" t="str"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="str"/>
+      <x:c r="B125" t="str"/>
+      <x:c r="C125" t="str"/>
+      <x:c r="D125" t="str"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="str"/>
+      <x:c r="B126" t="str"/>
+      <x:c r="C126" t="str"/>
+      <x:c r="D126" t="str"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="str"/>
+      <x:c r="B127" t="str"/>
+      <x:c r="C127" t="str"/>
+      <x:c r="D127" t="str"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="str"/>
+      <x:c r="B128" t="str"/>
+      <x:c r="C128" t="str"/>
+      <x:c r="D128" t="str"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="str"/>
+      <x:c r="B129" t="str"/>
+      <x:c r="C129" t="str"/>
+      <x:c r="D129" t="str"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="str"/>
+      <x:c r="B130" t="str"/>
+      <x:c r="C130" t="str"/>
+      <x:c r="D130" t="str"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="str"/>
+      <x:c r="B131" t="str"/>
+      <x:c r="C131" t="str"/>
+      <x:c r="D131" t="str"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="str"/>
+      <x:c r="B132" t="str"/>
+      <x:c r="C132" t="str"/>
+      <x:c r="D132" t="str"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="str"/>
+      <x:c r="B133" t="str"/>
+      <x:c r="C133" t="str"/>
+      <x:c r="D133" t="str"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="str"/>
+      <x:c r="B134" t="str"/>
+      <x:c r="C134" t="str"/>
+      <x:c r="D134" t="str"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="str"/>
+      <x:c r="B135" t="str"/>
+      <x:c r="C135" t="str"/>
+      <x:c r="D135" t="str"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="str"/>
+      <x:c r="B136" t="str"/>
+      <x:c r="C136" t="str"/>
+      <x:c r="D136" t="str"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="str"/>
+      <x:c r="B137" t="str"/>
+      <x:c r="C137" t="str"/>
+      <x:c r="D137" t="str"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="str"/>
+      <x:c r="B138" t="str"/>
+      <x:c r="C138" t="str"/>
+      <x:c r="D138" t="str"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="str"/>
+      <x:c r="B139" t="str"/>
+      <x:c r="C139" t="str"/>
+      <x:c r="D139" t="str"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str"/>
+      <x:c r="B140" t="str"/>
+      <x:c r="C140" t="str"/>
+      <x:c r="D140" t="str"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str"/>
+      <x:c r="B141" t="str"/>
+      <x:c r="C141" t="str"/>
+      <x:c r="D141" t="str"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str"/>
+      <x:c r="B142" t="str"/>
+      <x:c r="C142" t="str"/>
+      <x:c r="D142" t="str"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str"/>
+      <x:c r="B143" t="str"/>
+      <x:c r="C143" t="str"/>
+      <x:c r="D143" t="str"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str"/>
+      <x:c r="B144" t="str"/>
+      <x:c r="C144" t="str"/>
+      <x:c r="D144" t="str"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str"/>
+      <x:c r="B145" t="str"/>
+      <x:c r="C145" t="str"/>
+      <x:c r="D145" t="str"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="str"/>
+      <x:c r="B146" t="str"/>
+      <x:c r="C146" t="str"/>
+      <x:c r="D146" t="str"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="str"/>
+      <x:c r="B147" t="str"/>
+      <x:c r="C147" t="str"/>
+      <x:c r="D147" t="str"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="str"/>
+      <x:c r="B148" t="str"/>
+      <x:c r="C148" t="str"/>
+      <x:c r="D148" t="str"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="str"/>
+      <x:c r="B149" t="str"/>
+      <x:c r="C149" t="str"/>
+      <x:c r="D149" t="str"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="str"/>
+      <x:c r="B150" t="str"/>
+      <x:c r="C150" t="str"/>
+      <x:c r="D150" t="str"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" t="str"/>
+      <x:c r="B151" t="str"/>
+      <x:c r="C151" t="str"/>
+      <x:c r="D151" t="str"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" t="str"/>
+      <x:c r="B152" t="str"/>
+      <x:c r="C152" t="str"/>
+      <x:c r="D152" t="str"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="str"/>
+      <x:c r="B153" t="str"/>
+      <x:c r="C153" t="str"/>
+      <x:c r="D153" t="str"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="str"/>
+      <x:c r="B154" t="str"/>
+      <x:c r="C154" t="str"/>
+      <x:c r="D154" t="str"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="str"/>
+      <x:c r="B155" t="str"/>
+      <x:c r="C155" t="str"/>
+      <x:c r="D155" t="str"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="str"/>
+      <x:c r="B156" t="str"/>
+      <x:c r="C156" t="str"/>
+      <x:c r="D156" t="str"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" t="str"/>
+      <x:c r="B157" t="str"/>
+      <x:c r="C157" t="str"/>
+      <x:c r="D157" t="str"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" t="str"/>
+      <x:c r="B158" t="str"/>
+      <x:c r="C158" t="str"/>
+      <x:c r="D158" t="str"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" t="str"/>
+      <x:c r="B159" t="str"/>
+      <x:c r="C159" t="str"/>
+      <x:c r="D159" t="str"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" t="str"/>
+      <x:c r="B160" t="str"/>
+      <x:c r="C160" t="str"/>
+      <x:c r="D160" t="str"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" t="str"/>
+      <x:c r="B161" t="str"/>
+      <x:c r="C161" t="str"/>
+      <x:c r="D161" t="str"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" t="str"/>
+      <x:c r="B162" t="str"/>
+      <x:c r="C162" t="str"/>
+      <x:c r="D162" t="str"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" t="str"/>
+      <x:c r="B163" t="str"/>
+      <x:c r="C163" t="str"/>
+      <x:c r="D163" t="str"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" t="str"/>
+      <x:c r="B164" t="str"/>
+      <x:c r="C164" t="str"/>
+      <x:c r="D164" t="str"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" t="str"/>
+      <x:c r="B165" t="str"/>
+      <x:c r="C165" t="str"/>
+      <x:c r="D165" t="str"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" t="str"/>
+      <x:c r="B166" t="str"/>
+      <x:c r="C166" t="str"/>
+      <x:c r="D166" t="str"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" t="str"/>
+      <x:c r="B167" t="str"/>
+      <x:c r="C167" t="str"/>
+      <x:c r="D167" t="str"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" t="str"/>
+      <x:c r="B168" t="str"/>
+      <x:c r="C168" t="str"/>
+      <x:c r="D168" t="str"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" t="str"/>
+      <x:c r="B169" t="str"/>
+      <x:c r="C169" t="str"/>
+      <x:c r="D169" t="str"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" t="str"/>
+      <x:c r="B170" t="str"/>
+      <x:c r="C170" t="str"/>
+      <x:c r="D170" t="str"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" t="str"/>
+      <x:c r="B171" t="str"/>
+      <x:c r="C171" t="str"/>
+      <x:c r="D171" t="str"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" t="str"/>
+      <x:c r="B172" t="str"/>
+      <x:c r="C172" t="str"/>
+      <x:c r="D172" t="str"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" t="str"/>
+      <x:c r="B173" t="str"/>
+      <x:c r="C173" t="str"/>
+      <x:c r="D173" t="str"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" t="str"/>
+      <x:c r="B174" t="str"/>
+      <x:c r="C174" t="str"/>
+      <x:c r="D174" t="str"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" t="str"/>
+      <x:c r="B175" t="str"/>
+      <x:c r="C175" t="str"/>
+      <x:c r="D175" t="str"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" t="str"/>
+      <x:c r="B176" t="str"/>
+      <x:c r="C176" t="str"/>
+      <x:c r="D176" t="str"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" t="str"/>
+      <x:c r="B177" t="str"/>
+      <x:c r="C177" t="str"/>
+      <x:c r="D177" t="str"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" t="str"/>
+      <x:c r="B178" t="str"/>
+      <x:c r="C178" t="str"/>
+      <x:c r="D178" t="str"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" t="str"/>
+      <x:c r="B179" t="str"/>
+      <x:c r="C179" t="str"/>
+      <x:c r="D179" t="str"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" t="str"/>
+      <x:c r="B180" t="str"/>
+      <x:c r="C180" t="str"/>
+      <x:c r="D180" t="str"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" t="str"/>
+      <x:c r="B181" t="str"/>
+      <x:c r="C181" t="str"/>
+      <x:c r="D181" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="18" t="str">
+        <x:v>Durchführungs-ID</x:v>
+      </x:c>
+      <x:c r="B1" s="18" t="str">
+        <x:v>Jahrgänge</x:v>
+      </x:c>
+      <x:c r="C1" s="18" t="str">
+        <x:v>Teamgröße</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str"/>
+      <x:c r="B2" t="str"/>
+      <x:c r="C2" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str"/>
+      <x:c r="B3" t="str"/>
+      <x:c r="C3" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str"/>
+      <x:c r="B4" t="str"/>
+      <x:c r="C4" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str"/>
+      <x:c r="B5" t="str"/>
+      <x:c r="C5" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str"/>
+      <x:c r="B6" t="str"/>
+      <x:c r="C6" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str"/>
+      <x:c r="B7" t="str"/>
+      <x:c r="C7" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str"/>
+      <x:c r="B8" t="str"/>
+      <x:c r="C8" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str"/>
+      <x:c r="B9" t="str"/>
+      <x:c r="C9" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str"/>
+      <x:c r="B10" t="str"/>
+      <x:c r="C10" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str"/>
+      <x:c r="B11" t="str"/>
+      <x:c r="C11" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str"/>
+      <x:c r="B12" t="str"/>
+      <x:c r="C12" t="str"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str"/>
+      <x:c r="B13" t="str"/>
+      <x:c r="C13" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str"/>
+      <x:c r="B14" t="str"/>
+      <x:c r="C14" t="str"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str"/>
+      <x:c r="B15" t="str"/>
+      <x:c r="C15" t="str"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str"/>
+      <x:c r="B16" t="str"/>
+      <x:c r="C16" t="str"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str"/>
+      <x:c r="B17" t="str"/>
+      <x:c r="C17" t="str"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str"/>
+      <x:c r="B18" t="str"/>
+      <x:c r="C18" t="str"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str"/>
+      <x:c r="B19" t="str"/>
+      <x:c r="C19" t="str"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str"/>
+      <x:c r="B20" t="str"/>
+      <x:c r="C20" t="str"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str"/>
+      <x:c r="B21" t="str"/>
+      <x:c r="C21" t="str"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str"/>
+      <x:c r="B22" t="str"/>
+      <x:c r="C22" t="str"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str"/>
+      <x:c r="B23" t="str"/>
+      <x:c r="C23" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str"/>
+      <x:c r="B24" t="str"/>
+      <x:c r="C24" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str"/>
+      <x:c r="B25" t="str"/>
+      <x:c r="C25" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str"/>
+      <x:c r="B26" t="str"/>
+      <x:c r="C26" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str"/>
+      <x:c r="B27" t="str"/>
+      <x:c r="C27" t="str"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str"/>
+      <x:c r="B28" t="str"/>
+      <x:c r="C28" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str"/>
+      <x:c r="B29" t="str"/>
+      <x:c r="C29" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str"/>
+      <x:c r="B30" t="str"/>
+      <x:c r="C30" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str"/>
+      <x:c r="B31" t="str"/>
+      <x:c r="C31" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str"/>
+      <x:c r="B32" t="str"/>
+      <x:c r="C32" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str"/>
+      <x:c r="B33" t="str"/>
+      <x:c r="C33" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str"/>
+      <x:c r="B34" t="str"/>
+      <x:c r="C34" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str"/>
+      <x:c r="B35" t="str"/>
+      <x:c r="C35" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str"/>
+      <x:c r="B36" t="str"/>
+      <x:c r="C36" t="str"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str"/>
+      <x:c r="B37" t="str"/>
+      <x:c r="C37" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str"/>
+      <x:c r="B38" t="str"/>
+      <x:c r="C38" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str"/>
+      <x:c r="B39" t="str"/>
+      <x:c r="C39" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str"/>
+      <x:c r="B40" t="str"/>
+      <x:c r="C40" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str"/>
+      <x:c r="B41" t="str"/>
+      <x:c r="C41" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str"/>
+      <x:c r="B42" t="str"/>
+      <x:c r="C42" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str"/>
+      <x:c r="B43" t="str"/>
+      <x:c r="C43" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str"/>
+      <x:c r="B44" t="str"/>
+      <x:c r="C44" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str"/>
+      <x:c r="B45" t="str"/>
+      <x:c r="C45" t="str"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str"/>
+      <x:c r="B46" t="str"/>
+      <x:c r="C46" t="str"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str"/>
+      <x:c r="B47" t="str"/>
+      <x:c r="C47" t="str"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str"/>
+      <x:c r="B48" t="str"/>
+      <x:c r="C48" t="str"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str"/>
+      <x:c r="B49" t="str"/>
+      <x:c r="C49" t="str"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str"/>
+      <x:c r="B50" t="str"/>
+      <x:c r="C50" t="str"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str"/>
+      <x:c r="B51" t="str"/>
+      <x:c r="C51" t="str"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str"/>
+      <x:c r="B52" t="str"/>
+      <x:c r="C52" t="str"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="str"/>
+      <x:c r="B53" t="str"/>
+      <x:c r="C53" t="str"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="str"/>
+      <x:c r="B54" t="str"/>
+      <x:c r="C54" t="str"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str"/>
+      <x:c r="B55" t="str"/>
+      <x:c r="C55" t="str"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str"/>
+      <x:c r="B56" t="str"/>
+      <x:c r="C56" t="str"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="str"/>
+      <x:c r="B57" t="str"/>
+      <x:c r="C57" t="str"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str"/>
+      <x:c r="B58" t="str"/>
+      <x:c r="C58" t="str"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="str"/>
+      <x:c r="B59" t="str"/>
+      <x:c r="C59" t="str"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" t="str"/>
+      <x:c r="B60" t="str"/>
+      <x:c r="C60" t="str"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="str"/>
+      <x:c r="B61" t="str"/>
+      <x:c r="C61" t="str"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="str"/>
+      <x:c r="B62" t="str"/>
+      <x:c r="C62" t="str"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="str"/>
+      <x:c r="B63" t="str"/>
+      <x:c r="C63" t="str"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="str"/>
+      <x:c r="B64" t="str"/>
+      <x:c r="C64" t="str"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="str"/>
+      <x:c r="B65" t="str"/>
+      <x:c r="C65" t="str"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str"/>
+      <x:c r="B66" t="str"/>
+      <x:c r="C66" t="str"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str"/>
+      <x:c r="B67" t="str"/>
+      <x:c r="C67" t="str"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str"/>
+      <x:c r="B68" t="str"/>
+      <x:c r="C68" t="str"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="str"/>
+      <x:c r="B69" t="str"/>
+      <x:c r="C69" t="str"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str"/>
+      <x:c r="B70" t="str"/>
+      <x:c r="C70" t="str"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str"/>
+      <x:c r="B71" t="str"/>
+      <x:c r="C71" t="str"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="str"/>
+      <x:c r="B72" t="str"/>
+      <x:c r="C72" t="str"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="str"/>
+      <x:c r="B73" t="str"/>
+      <x:c r="C73" t="str"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="str"/>
+      <x:c r="B74" t="str"/>
+      <x:c r="C74" t="str"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="str"/>
+      <x:c r="B75" t="str"/>
+      <x:c r="C75" t="str"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="str"/>
+      <x:c r="B76" t="str"/>
+      <x:c r="C76" t="str"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="str"/>
+      <x:c r="B77" t="str"/>
+      <x:c r="C77" t="str"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="str"/>
+      <x:c r="B78" t="str"/>
+      <x:c r="C78" t="str"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="str"/>
+      <x:c r="B79" t="str"/>
+      <x:c r="C79" t="str"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="str"/>
+      <x:c r="B80" t="str"/>
+      <x:c r="C80" t="str"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="str"/>
+      <x:c r="B81" t="str"/>
+      <x:c r="C81" t="str"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="str"/>
+      <x:c r="B82" t="str"/>
+      <x:c r="C82" t="str"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" t="str"/>
+      <x:c r="B83" t="str"/>
+      <x:c r="C83" t="str"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="str"/>
+      <x:c r="B84" t="str"/>
+      <x:c r="C84" t="str"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="str"/>
+      <x:c r="B85" t="str"/>
+      <x:c r="C85" t="str"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="str"/>
+      <x:c r="B86" t="str"/>
+      <x:c r="C86" t="str"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="str"/>
+      <x:c r="B87" t="str"/>
+      <x:c r="C87" t="str"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str"/>
+      <x:c r="B88" t="str"/>
+      <x:c r="C88" t="str"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str"/>
+      <x:c r="B89" t="str"/>
+      <x:c r="C89" t="str"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="str"/>
+      <x:c r="B90" t="str"/>
+      <x:c r="C90" t="str"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str"/>
+      <x:c r="B91" t="str"/>
+      <x:c r="C91" t="str"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str"/>
+      <x:c r="B92" t="str"/>
+      <x:c r="C92" t="str"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str"/>
+      <x:c r="B93" t="str"/>
+      <x:c r="C93" t="str"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str"/>
+      <x:c r="B94" t="str"/>
+      <x:c r="C94" t="str"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str"/>
+      <x:c r="B95" t="str"/>
+      <x:c r="C95" t="str"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str"/>
+      <x:c r="B96" t="str"/>
+      <x:c r="C96" t="str"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str"/>
+      <x:c r="B97" t="str"/>
+      <x:c r="C97" t="str"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str"/>
+      <x:c r="B98" t="str"/>
+      <x:c r="C98" t="str"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str"/>
+      <x:c r="B99" t="str"/>
+      <x:c r="C99" t="str"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str"/>
+      <x:c r="B100" t="str"/>
+      <x:c r="C100" t="str"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str"/>
+      <x:c r="B101" t="str"/>
+      <x:c r="C101" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
@@ -894,42 +2524,42 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="20" t="str">
+      <x:c r="A1" s="18" t="str">
         <x:v>Person-ID</x:v>
       </x:c>
-      <x:c r="B1" s="20" t="str">
+      <x:c r="B1" s="18" t="str">
         <x:v>Vorname</x:v>
       </x:c>
-      <x:c r="C1" s="20" t="str">
+      <x:c r="C1" s="18" t="str">
         <x:v>Nachname</x:v>
       </x:c>
-      <x:c r="D1" s="20" t="str">
+      <x:c r="D1" s="18" t="str">
         <x:v>Klasse</x:v>
       </x:c>
-      <x:c r="E1" s="20" t="str">
+      <x:c r="E1" s="18" t="str">
         <x:v>Bildungsgang</x:v>
       </x:c>
-      <x:c r="F1" s="20" t="str">
+      <x:c r="F1" s="18" t="str">
         <x:v>Erstwunsch</x:v>
       </x:c>
-      <x:c r="G1" s="20" t="str">
+      <x:c r="G1" s="18" t="str">
         <x:v>Zweitwunsch</x:v>
       </x:c>
-      <x:c r="H1" s="20" t="str">
+      <x:c r="H1" s="18" t="str">
         <x:v>Drittwunsch</x:v>
       </x:c>
-      <x:c r="I1" s="20" t="str">
+      <x:c r="I1" s="18" t="str">
         <x:v>Viertwunsch</x:v>
       </x:c>
-      <x:c r="J1" s="20" t="str">
+      <x:c r="J1" s="18" t="str">
         <x:v>Feste Setzung</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="24" t="str"/>
+      <x:c r="A2" s="22" t="str"/>
       <x:c r="B2" t="str"/>
       <x:c r="C2" t="str"/>
-      <x:c r="D2" s="24" t="str"/>
+      <x:c r="D2" s="22" t="str"/>
       <x:c r="E2" t="str"/>
       <x:c r="F2" t="str"/>
       <x:c r="G2" t="str"/>
@@ -938,10 +2568,10 @@
       <x:c r="J2" t="str"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="24" t="str"/>
+      <x:c r="A3" s="22" t="str"/>
       <x:c r="B3" t="str"/>
       <x:c r="C3" t="str"/>
-      <x:c r="D3" s="24" t="str"/>
+      <x:c r="D3" s="22" t="str"/>
       <x:c r="E3" t="str"/>
       <x:c r="F3" t="str"/>
       <x:c r="G3" t="str"/>
@@ -950,10 +2580,10 @@
       <x:c r="J3" t="str"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="24" t="str"/>
+      <x:c r="A4" s="22" t="str"/>
       <x:c r="B4" t="str"/>
       <x:c r="C4" t="str"/>
-      <x:c r="D4" s="24" t="str"/>
+      <x:c r="D4" s="22" t="str"/>
       <x:c r="E4" t="str"/>
       <x:c r="F4" t="str"/>
       <x:c r="G4" t="str"/>
@@ -962,10 +2592,10 @@
       <x:c r="J4" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="24" t="str"/>
+      <x:c r="A5" s="22" t="str"/>
       <x:c r="B5" t="str"/>
       <x:c r="C5" t="str"/>
-      <x:c r="D5" s="24" t="str"/>
+      <x:c r="D5" s="22" t="str"/>
       <x:c r="E5" t="str"/>
       <x:c r="F5" t="str"/>
       <x:c r="G5" t="str"/>
@@ -974,10 +2604,10 @@
       <x:c r="J5" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="24" t="str"/>
+      <x:c r="A6" s="22" t="str"/>
       <x:c r="B6" t="str"/>
       <x:c r="C6" t="str"/>
-      <x:c r="D6" s="24" t="str"/>
+      <x:c r="D6" s="22" t="str"/>
       <x:c r="E6" t="str"/>
       <x:c r="F6" t="str"/>
       <x:c r="G6" t="str"/>
@@ -986,10 +2616,10 @@
       <x:c r="J6" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="24" t="str"/>
+      <x:c r="A7" s="22" t="str"/>
       <x:c r="B7" t="str"/>
       <x:c r="C7" t="str"/>
-      <x:c r="D7" s="24" t="str"/>
+      <x:c r="D7" s="22" t="str"/>
       <x:c r="E7" t="str"/>
       <x:c r="F7" t="str"/>
       <x:c r="G7" t="str"/>
@@ -998,10 +2628,10 @@
       <x:c r="J7" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="24" t="str"/>
+      <x:c r="A8" s="22" t="str"/>
       <x:c r="B8" t="str"/>
       <x:c r="C8" t="str"/>
-      <x:c r="D8" s="24" t="str"/>
+      <x:c r="D8" s="22" t="str"/>
       <x:c r="E8" t="str"/>
       <x:c r="F8" t="str"/>
       <x:c r="G8" t="str"/>
@@ -1010,10 +2640,10 @@
       <x:c r="J8" t="str"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="24" t="str"/>
+      <x:c r="A9" s="22" t="str"/>
       <x:c r="B9" t="str"/>
       <x:c r="C9" t="str"/>
-      <x:c r="D9" s="24" t="str"/>
+      <x:c r="D9" s="22" t="str"/>
       <x:c r="E9" t="str"/>
       <x:c r="F9" t="str"/>
       <x:c r="G9" t="str"/>
@@ -1022,10 +2652,10 @@
       <x:c r="J9" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="24" t="str"/>
+      <x:c r="A10" s="22" t="str"/>
       <x:c r="B10" t="str"/>
       <x:c r="C10" t="str"/>
-      <x:c r="D10" s="24" t="str"/>
+      <x:c r="D10" s="22" t="str"/>
       <x:c r="E10" t="str"/>
       <x:c r="F10" t="str"/>
       <x:c r="G10" t="str"/>
@@ -1034,10 +2664,10 @@
       <x:c r="J10" t="str"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="24" t="str"/>
+      <x:c r="A11" s="22" t="str"/>
       <x:c r="B11" t="str"/>
       <x:c r="C11" t="str"/>
-      <x:c r="D11" s="24" t="str"/>
+      <x:c r="D11" s="22" t="str"/>
       <x:c r="E11" t="str"/>
       <x:c r="F11" t="str"/>
       <x:c r="G11" t="str"/>
@@ -1046,10 +2676,10 @@
       <x:c r="J11" t="str"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="24" t="str"/>
+      <x:c r="A12" s="22" t="str"/>
       <x:c r="B12" t="str"/>
       <x:c r="C12" t="str"/>
-      <x:c r="D12" s="24" t="str"/>
+      <x:c r="D12" s="22" t="str"/>
       <x:c r="E12" t="str"/>
       <x:c r="F12" t="str"/>
       <x:c r="G12" t="str"/>
@@ -1058,10 +2688,10 @@
       <x:c r="J12" t="str"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="24" t="str"/>
+      <x:c r="A13" s="22" t="str"/>
       <x:c r="B13" t="str"/>
       <x:c r="C13" t="str"/>
-      <x:c r="D13" s="24" t="str"/>
+      <x:c r="D13" s="22" t="str"/>
       <x:c r="E13" t="str"/>
       <x:c r="F13" t="str"/>
       <x:c r="G13" t="str"/>
@@ -1070,10 +2700,10 @@
       <x:c r="J13" t="str"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="24" t="str"/>
+      <x:c r="A14" s="22" t="str"/>
       <x:c r="B14" t="str"/>
       <x:c r="C14" t="str"/>
-      <x:c r="D14" s="24" t="str"/>
+      <x:c r="D14" s="22" t="str"/>
       <x:c r="E14" t="str"/>
       <x:c r="F14" t="str"/>
       <x:c r="G14" t="str"/>
@@ -1082,10 +2712,10 @@
       <x:c r="J14" t="str"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="24" t="str"/>
+      <x:c r="A15" s="22" t="str"/>
       <x:c r="B15" t="str"/>
       <x:c r="C15" t="str"/>
-      <x:c r="D15" s="24" t="str"/>
+      <x:c r="D15" s="22" t="str"/>
       <x:c r="E15" t="str"/>
       <x:c r="F15" t="str"/>
       <x:c r="G15" t="str"/>
@@ -1094,10 +2724,10 @@
       <x:c r="J15" t="str"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="24" t="str"/>
+      <x:c r="A16" s="22" t="str"/>
       <x:c r="B16" t="str"/>
       <x:c r="C16" t="str"/>
-      <x:c r="D16" s="24" t="str"/>
+      <x:c r="D16" s="22" t="str"/>
       <x:c r="E16" t="str"/>
       <x:c r="F16" t="str"/>
       <x:c r="G16" t="str"/>
@@ -1106,10 +2736,10 @@
       <x:c r="J16" t="str"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="24" t="str"/>
+      <x:c r="A17" s="22" t="str"/>
       <x:c r="B17" t="str"/>
       <x:c r="C17" t="str"/>
-      <x:c r="D17" s="24" t="str"/>
+      <x:c r="D17" s="22" t="str"/>
       <x:c r="E17" t="str"/>
       <x:c r="F17" t="str"/>
       <x:c r="G17" t="str"/>
@@ -1118,10 +2748,10 @@
       <x:c r="J17" t="str"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="24" t="str"/>
+      <x:c r="A18" s="22" t="str"/>
       <x:c r="B18" t="str"/>
       <x:c r="C18" t="str"/>
-      <x:c r="D18" s="24" t="str"/>
+      <x:c r="D18" s="22" t="str"/>
       <x:c r="E18" t="str"/>
       <x:c r="F18" t="str"/>
       <x:c r="G18" t="str"/>
@@ -1130,10 +2760,10 @@
       <x:c r="J18" t="str"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="24" t="str"/>
+      <x:c r="A19" s="22" t="str"/>
       <x:c r="B19" t="str"/>
       <x:c r="C19" t="str"/>
-      <x:c r="D19" s="24" t="str"/>
+      <x:c r="D19" s="22" t="str"/>
       <x:c r="E19" t="str"/>
       <x:c r="F19" t="str"/>
       <x:c r="G19" t="str"/>
@@ -1142,10 +2772,10 @@
       <x:c r="J19" t="str"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="24" t="str"/>
+      <x:c r="A20" s="22" t="str"/>
       <x:c r="B20" t="str"/>
       <x:c r="C20" t="str"/>
-      <x:c r="D20" s="24" t="str"/>
+      <x:c r="D20" s="22" t="str"/>
       <x:c r="E20" t="str"/>
       <x:c r="F20" t="str"/>
       <x:c r="G20" t="str"/>
@@ -1154,10 +2784,10 @@
       <x:c r="J20" t="str"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="24" t="str"/>
+      <x:c r="A21" s="22" t="str"/>
       <x:c r="B21" t="str"/>
       <x:c r="C21" t="str"/>
-      <x:c r="D21" s="24" t="str"/>
+      <x:c r="D21" s="22" t="str"/>
       <x:c r="E21" t="str"/>
       <x:c r="F21" t="str"/>
       <x:c r="G21" t="str"/>
@@ -1166,10 +2796,10 @@
       <x:c r="J21" t="str"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="24" t="str"/>
+      <x:c r="A22" s="22" t="str"/>
       <x:c r="B22" t="str"/>
       <x:c r="C22" t="str"/>
-      <x:c r="D22" s="24" t="str"/>
+      <x:c r="D22" s="22" t="str"/>
       <x:c r="E22" t="str"/>
       <x:c r="F22" t="str"/>
       <x:c r="G22" t="str"/>
@@ -1178,10 +2808,10 @@
       <x:c r="J22" t="str"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="24" t="str"/>
+      <x:c r="A23" s="22" t="str"/>
       <x:c r="B23" t="str"/>
       <x:c r="C23" t="str"/>
-      <x:c r="D23" s="24" t="str"/>
+      <x:c r="D23" s="22" t="str"/>
       <x:c r="E23" t="str"/>
       <x:c r="F23" t="str"/>
       <x:c r="G23" t="str"/>
@@ -1190,10 +2820,10 @@
       <x:c r="J23" t="str"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="24" t="str"/>
+      <x:c r="A24" s="22" t="str"/>
       <x:c r="B24" t="str"/>
       <x:c r="C24" t="str"/>
-      <x:c r="D24" s="24" t="str"/>
+      <x:c r="D24" s="22" t="str"/>
       <x:c r="E24" t="str"/>
       <x:c r="F24" t="str"/>
       <x:c r="G24" t="str"/>
@@ -1202,10 +2832,10 @@
       <x:c r="J24" t="str"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="24" t="str"/>
+      <x:c r="A25" s="22" t="str"/>
       <x:c r="B25" t="str"/>
       <x:c r="C25" t="str"/>
-      <x:c r="D25" s="24" t="str"/>
+      <x:c r="D25" s="22" t="str"/>
       <x:c r="E25" t="str"/>
       <x:c r="F25" t="str"/>
       <x:c r="G25" t="str"/>
@@ -1214,10 +2844,10 @@
       <x:c r="J25" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="24" t="str"/>
+      <x:c r="A26" s="22" t="str"/>
       <x:c r="B26" t="str"/>
       <x:c r="C26" t="str"/>
-      <x:c r="D26" s="24" t="str"/>
+      <x:c r="D26" s="22" t="str"/>
       <x:c r="E26" t="str"/>
       <x:c r="F26" t="str"/>
       <x:c r="G26" t="str"/>
@@ -1226,10 +2856,10 @@
       <x:c r="J26" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="24" t="str"/>
+      <x:c r="A27" s="22" t="str"/>
       <x:c r="B27" t="str"/>
       <x:c r="C27" t="str"/>
-      <x:c r="D27" s="24" t="str"/>
+      <x:c r="D27" s="22" t="str"/>
       <x:c r="E27" t="str"/>
       <x:c r="F27" t="str"/>
       <x:c r="G27" t="str"/>
@@ -1238,10 +2868,10 @@
       <x:c r="J27" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="24" t="str"/>
+      <x:c r="A28" s="22" t="str"/>
       <x:c r="B28" t="str"/>
       <x:c r="C28" t="str"/>
-      <x:c r="D28" s="24" t="str"/>
+      <x:c r="D28" s="22" t="str"/>
       <x:c r="E28" t="str"/>
       <x:c r="F28" t="str"/>
       <x:c r="G28" t="str"/>
@@ -1250,10 +2880,10 @@
       <x:c r="J28" t="str"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="24" t="str"/>
+      <x:c r="A29" s="22" t="str"/>
       <x:c r="B29" t="str"/>
       <x:c r="C29" t="str"/>
-      <x:c r="D29" s="24" t="str"/>
+      <x:c r="D29" s="22" t="str"/>
       <x:c r="E29" t="str"/>
       <x:c r="F29" t="str"/>
       <x:c r="G29" t="str"/>
@@ -1262,10 +2892,10 @@
       <x:c r="J29" t="str"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="24" t="str"/>
+      <x:c r="A30" s="22" t="str"/>
       <x:c r="B30" t="str"/>
       <x:c r="C30" t="str"/>
-      <x:c r="D30" s="24" t="str"/>
+      <x:c r="D30" s="22" t="str"/>
       <x:c r="E30" t="str"/>
       <x:c r="F30" t="str"/>
       <x:c r="G30" t="str"/>
@@ -1274,10 +2904,10 @@
       <x:c r="J30" t="str"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="24" t="str"/>
+      <x:c r="A31" s="22" t="str"/>
       <x:c r="B31" t="str"/>
       <x:c r="C31" t="str"/>
-      <x:c r="D31" s="24" t="str"/>
+      <x:c r="D31" s="22" t="str"/>
       <x:c r="E31" t="str"/>
       <x:c r="F31" t="str"/>
       <x:c r="G31" t="str"/>
@@ -1286,10 +2916,10 @@
       <x:c r="J31" t="str"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="24" t="str"/>
+      <x:c r="A32" s="22" t="str"/>
       <x:c r="B32" t="str"/>
       <x:c r="C32" t="str"/>
-      <x:c r="D32" s="24" t="str"/>
+      <x:c r="D32" s="22" t="str"/>
       <x:c r="E32" t="str"/>
       <x:c r="F32" t="str"/>
       <x:c r="G32" t="str"/>
@@ -1298,10 +2928,10 @@
       <x:c r="J32" t="str"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="24" t="str"/>
+      <x:c r="A33" s="22" t="str"/>
       <x:c r="B33" t="str"/>
       <x:c r="C33" t="str"/>
-      <x:c r="D33" s="24" t="str"/>
+      <x:c r="D33" s="22" t="str"/>
       <x:c r="E33" t="str"/>
       <x:c r="F33" t="str"/>
       <x:c r="G33" t="str"/>
@@ -1310,10 +2940,10 @@
       <x:c r="J33" t="str"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="24" t="str"/>
+      <x:c r="A34" s="22" t="str"/>
       <x:c r="B34" t="str"/>
       <x:c r="C34" t="str"/>
-      <x:c r="D34" s="24" t="str"/>
+      <x:c r="D34" s="22" t="str"/>
       <x:c r="E34" t="str"/>
       <x:c r="F34" t="str"/>
       <x:c r="G34" t="str"/>
@@ -1322,10 +2952,10 @@
       <x:c r="J34" t="str"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="24" t="str"/>
+      <x:c r="A35" s="22" t="str"/>
       <x:c r="B35" t="str"/>
       <x:c r="C35" t="str"/>
-      <x:c r="D35" s="24" t="str"/>
+      <x:c r="D35" s="22" t="str"/>
       <x:c r="E35" t="str"/>
       <x:c r="F35" t="str"/>
       <x:c r="G35" t="str"/>
@@ -1334,10 +2964,10 @@
       <x:c r="J35" t="str"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="24" t="str"/>
+      <x:c r="A36" s="22" t="str"/>
       <x:c r="B36" t="str"/>
       <x:c r="C36" t="str"/>
-      <x:c r="D36" s="24" t="str"/>
+      <x:c r="D36" s="22" t="str"/>
       <x:c r="E36" t="str"/>
       <x:c r="F36" t="str"/>
       <x:c r="G36" t="str"/>
@@ -1346,10 +2976,10 @@
       <x:c r="J36" t="str"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="24" t="str"/>
+      <x:c r="A37" s="22" t="str"/>
       <x:c r="B37" t="str"/>
       <x:c r="C37" t="str"/>
-      <x:c r="D37" s="24" t="str"/>
+      <x:c r="D37" s="22" t="str"/>
       <x:c r="E37" t="str"/>
       <x:c r="F37" t="str"/>
       <x:c r="G37" t="str"/>
@@ -1358,10 +2988,10 @@
       <x:c r="J37" t="str"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="24" t="str"/>
+      <x:c r="A38" s="22" t="str"/>
       <x:c r="B38" t="str"/>
       <x:c r="C38" t="str"/>
-      <x:c r="D38" s="24" t="str"/>
+      <x:c r="D38" s="22" t="str"/>
       <x:c r="E38" t="str"/>
       <x:c r="F38" t="str"/>
       <x:c r="G38" t="str"/>
@@ -1370,10 +3000,10 @@
       <x:c r="J38" t="str"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="24" t="str"/>
+      <x:c r="A39" s="22" t="str"/>
       <x:c r="B39" t="str"/>
       <x:c r="C39" t="str"/>
-      <x:c r="D39" s="24" t="str"/>
+      <x:c r="D39" s="22" t="str"/>
       <x:c r="E39" t="str"/>
       <x:c r="F39" t="str"/>
       <x:c r="G39" t="str"/>
@@ -1382,10 +3012,10 @@
       <x:c r="J39" t="str"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="24" t="str"/>
+      <x:c r="A40" s="22" t="str"/>
       <x:c r="B40" t="str"/>
       <x:c r="C40" t="str"/>
-      <x:c r="D40" s="24" t="str"/>
+      <x:c r="D40" s="22" t="str"/>
       <x:c r="E40" t="str"/>
       <x:c r="F40" t="str"/>
       <x:c r="G40" t="str"/>
@@ -1394,10 +3024,10 @@
       <x:c r="J40" t="str"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="24" t="str"/>
+      <x:c r="A41" s="22" t="str"/>
       <x:c r="B41" t="str"/>
       <x:c r="C41" t="str"/>
-      <x:c r="D41" s="24" t="str"/>
+      <x:c r="D41" s="22" t="str"/>
       <x:c r="E41" t="str"/>
       <x:c r="F41" t="str"/>
       <x:c r="G41" t="str"/>
@@ -1406,10 +3036,10 @@
       <x:c r="J41" t="str"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="24" t="str"/>
+      <x:c r="A42" s="22" t="str"/>
       <x:c r="B42" t="str"/>
       <x:c r="C42" t="str"/>
-      <x:c r="D42" s="24" t="str"/>
+      <x:c r="D42" s="22" t="str"/>
       <x:c r="E42" t="str"/>
       <x:c r="F42" t="str"/>
       <x:c r="G42" t="str"/>
@@ -1418,10 +3048,10 @@
       <x:c r="J42" t="str"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="24" t="str"/>
+      <x:c r="A43" s="22" t="str"/>
       <x:c r="B43" t="str"/>
       <x:c r="C43" t="str"/>
-      <x:c r="D43" s="24" t="str"/>
+      <x:c r="D43" s="22" t="str"/>
       <x:c r="E43" t="str"/>
       <x:c r="F43" t="str"/>
       <x:c r="G43" t="str"/>
@@ -1430,10 +3060,10 @@
       <x:c r="J43" t="str"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="24" t="str"/>
+      <x:c r="A44" s="22" t="str"/>
       <x:c r="B44" t="str"/>
       <x:c r="C44" t="str"/>
-      <x:c r="D44" s="24" t="str"/>
+      <x:c r="D44" s="22" t="str"/>
       <x:c r="E44" t="str"/>
       <x:c r="F44" t="str"/>
       <x:c r="G44" t="str"/>
@@ -1442,10 +3072,10 @@
       <x:c r="J44" t="str"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="24" t="str"/>
+      <x:c r="A45" s="22" t="str"/>
       <x:c r="B45" t="str"/>
       <x:c r="C45" t="str"/>
-      <x:c r="D45" s="24" t="str"/>
+      <x:c r="D45" s="22" t="str"/>
       <x:c r="E45" t="str"/>
       <x:c r="F45" t="str"/>
       <x:c r="G45" t="str"/>
@@ -1454,10 +3084,10 @@
       <x:c r="J45" t="str"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="24" t="str"/>
+      <x:c r="A46" s="22" t="str"/>
       <x:c r="B46" t="str"/>
       <x:c r="C46" t="str"/>
-      <x:c r="D46" s="24" t="str"/>
+      <x:c r="D46" s="22" t="str"/>
       <x:c r="E46" t="str"/>
       <x:c r="F46" t="str"/>
       <x:c r="G46" t="str"/>
@@ -1466,10 +3096,10 @@
       <x:c r="J46" t="str"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="24" t="str"/>
+      <x:c r="A47" s="22" t="str"/>
       <x:c r="B47" t="str"/>
       <x:c r="C47" t="str"/>
-      <x:c r="D47" s="24" t="str"/>
+      <x:c r="D47" s="22" t="str"/>
       <x:c r="E47" t="str"/>
       <x:c r="F47" t="str"/>
       <x:c r="G47" t="str"/>
@@ -1478,10 +3108,10 @@
       <x:c r="J47" t="str"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="24" t="str"/>
+      <x:c r="A48" s="22" t="str"/>
       <x:c r="B48" t="str"/>
       <x:c r="C48" t="str"/>
-      <x:c r="D48" s="24" t="str"/>
+      <x:c r="D48" s="22" t="str"/>
       <x:c r="E48" t="str"/>
       <x:c r="F48" t="str"/>
       <x:c r="G48" t="str"/>
@@ -1490,10 +3120,10 @@
       <x:c r="J48" t="str"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="24" t="str"/>
+      <x:c r="A49" s="22" t="str"/>
       <x:c r="B49" t="str"/>
       <x:c r="C49" t="str"/>
-      <x:c r="D49" s="24" t="str"/>
+      <x:c r="D49" s="22" t="str"/>
       <x:c r="E49" t="str"/>
       <x:c r="F49" t="str"/>
       <x:c r="G49" t="str"/>
@@ -1502,10 +3132,10 @@
       <x:c r="J49" t="str"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="24" t="str"/>
+      <x:c r="A50" s="22" t="str"/>
       <x:c r="B50" t="str"/>
       <x:c r="C50" t="str"/>
-      <x:c r="D50" s="24" t="str"/>
+      <x:c r="D50" s="22" t="str"/>
       <x:c r="E50" t="str"/>
       <x:c r="F50" t="str"/>
       <x:c r="G50" t="str"/>
@@ -1514,10 +3144,10 @@
       <x:c r="J50" t="str"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="24" t="str"/>
+      <x:c r="A51" s="22" t="str"/>
       <x:c r="B51" t="str"/>
       <x:c r="C51" t="str"/>
-      <x:c r="D51" s="24" t="str"/>
+      <x:c r="D51" s="22" t="str"/>
       <x:c r="E51" t="str"/>
       <x:c r="F51" t="str"/>
       <x:c r="G51" t="str"/>
@@ -1526,10 +3156,10 @@
       <x:c r="J51" t="str"/>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="24" t="str"/>
+      <x:c r="A52" s="22" t="str"/>
       <x:c r="B52" t="str"/>
       <x:c r="C52" t="str"/>
-      <x:c r="D52" s="24" t="str"/>
+      <x:c r="D52" s="22" t="str"/>
       <x:c r="E52" t="str"/>
       <x:c r="F52" t="str"/>
       <x:c r="G52" t="str"/>
@@ -1538,10 +3168,10 @@
       <x:c r="J52" t="str"/>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="24" t="str"/>
+      <x:c r="A53" s="22" t="str"/>
       <x:c r="B53" t="str"/>
       <x:c r="C53" t="str"/>
-      <x:c r="D53" s="24" t="str"/>
+      <x:c r="D53" s="22" t="str"/>
       <x:c r="E53" t="str"/>
       <x:c r="F53" t="str"/>
       <x:c r="G53" t="str"/>
@@ -1550,10 +3180,10 @@
       <x:c r="J53" t="str"/>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="24" t="str"/>
+      <x:c r="A54" s="22" t="str"/>
       <x:c r="B54" t="str"/>
       <x:c r="C54" t="str"/>
-      <x:c r="D54" s="24" t="str"/>
+      <x:c r="D54" s="22" t="str"/>
       <x:c r="E54" t="str"/>
       <x:c r="F54" t="str"/>
       <x:c r="G54" t="str"/>
@@ -1562,10 +3192,10 @@
       <x:c r="J54" t="str"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="24" t="str"/>
+      <x:c r="A55" s="22" t="str"/>
       <x:c r="B55" t="str"/>
       <x:c r="C55" t="str"/>
-      <x:c r="D55" s="24" t="str"/>
+      <x:c r="D55" s="22" t="str"/>
       <x:c r="E55" t="str"/>
       <x:c r="F55" t="str"/>
       <x:c r="G55" t="str"/>
@@ -1574,10 +3204,10 @@
       <x:c r="J55" t="str"/>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="24" t="str"/>
+      <x:c r="A56" s="22" t="str"/>
       <x:c r="B56" t="str"/>
       <x:c r="C56" t="str"/>
-      <x:c r="D56" s="24" t="str"/>
+      <x:c r="D56" s="22" t="str"/>
       <x:c r="E56" t="str"/>
       <x:c r="F56" t="str"/>
       <x:c r="G56" t="str"/>
@@ -1586,10 +3216,10 @@
       <x:c r="J56" t="str"/>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="24" t="str"/>
+      <x:c r="A57" s="22" t="str"/>
       <x:c r="B57" t="str"/>
       <x:c r="C57" t="str"/>
-      <x:c r="D57" s="24" t="str"/>
+      <x:c r="D57" s="22" t="str"/>
       <x:c r="E57" t="str"/>
       <x:c r="F57" t="str"/>
       <x:c r="G57" t="str"/>
@@ -1598,10 +3228,10 @@
       <x:c r="J57" t="str"/>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="24" t="str"/>
+      <x:c r="A58" s="22" t="str"/>
       <x:c r="B58" t="str"/>
       <x:c r="C58" t="str"/>
-      <x:c r="D58" s="24" t="str"/>
+      <x:c r="D58" s="22" t="str"/>
       <x:c r="E58" t="str"/>
       <x:c r="F58" t="str"/>
       <x:c r="G58" t="str"/>
@@ -1610,10 +3240,10 @@
       <x:c r="J58" t="str"/>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="24" t="str"/>
+      <x:c r="A59" s="22" t="str"/>
       <x:c r="B59" t="str"/>
       <x:c r="C59" t="str"/>
-      <x:c r="D59" s="24" t="str"/>
+      <x:c r="D59" s="22" t="str"/>
       <x:c r="E59" t="str"/>
       <x:c r="F59" t="str"/>
       <x:c r="G59" t="str"/>
@@ -1622,10 +3252,10 @@
       <x:c r="J59" t="str"/>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="24" t="str"/>
+      <x:c r="A60" s="22" t="str"/>
       <x:c r="B60" t="str"/>
       <x:c r="C60" t="str"/>
-      <x:c r="D60" s="24" t="str"/>
+      <x:c r="D60" s="22" t="str"/>
       <x:c r="E60" t="str"/>
       <x:c r="F60" t="str"/>
       <x:c r="G60" t="str"/>
@@ -1634,10 +3264,10 @@
       <x:c r="J60" t="str"/>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="24" t="str"/>
+      <x:c r="A61" s="22" t="str"/>
       <x:c r="B61" t="str"/>
       <x:c r="C61" t="str"/>
-      <x:c r="D61" s="24" t="str"/>
+      <x:c r="D61" s="22" t="str"/>
       <x:c r="E61" t="str"/>
       <x:c r="F61" t="str"/>
       <x:c r="G61" t="str"/>
@@ -1646,10 +3276,10 @@
       <x:c r="J61" t="str"/>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="24" t="str"/>
+      <x:c r="A62" s="22" t="str"/>
       <x:c r="B62" t="str"/>
       <x:c r="C62" t="str"/>
-      <x:c r="D62" s="24" t="str"/>
+      <x:c r="D62" s="22" t="str"/>
       <x:c r="E62" t="str"/>
       <x:c r="F62" t="str"/>
       <x:c r="G62" t="str"/>
@@ -1658,10 +3288,10 @@
       <x:c r="J62" t="str"/>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="24" t="str"/>
+      <x:c r="A63" s="22" t="str"/>
       <x:c r="B63" t="str"/>
       <x:c r="C63" t="str"/>
-      <x:c r="D63" s="24" t="str"/>
+      <x:c r="D63" s="22" t="str"/>
       <x:c r="E63" t="str"/>
       <x:c r="F63" t="str"/>
       <x:c r="G63" t="str"/>
@@ -1670,10 +3300,10 @@
       <x:c r="J63" t="str"/>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="24" t="str"/>
+      <x:c r="A64" s="22" t="str"/>
       <x:c r="B64" t="str"/>
       <x:c r="C64" t="str"/>
-      <x:c r="D64" s="24" t="str"/>
+      <x:c r="D64" s="22" t="str"/>
       <x:c r="E64" t="str"/>
       <x:c r="F64" t="str"/>
       <x:c r="G64" t="str"/>
@@ -1682,10 +3312,10 @@
       <x:c r="J64" t="str"/>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="24" t="str"/>
+      <x:c r="A65" s="22" t="str"/>
       <x:c r="B65" t="str"/>
       <x:c r="C65" t="str"/>
-      <x:c r="D65" s="24" t="str"/>
+      <x:c r="D65" s="22" t="str"/>
       <x:c r="E65" t="str"/>
       <x:c r="F65" t="str"/>
       <x:c r="G65" t="str"/>
@@ -1694,10 +3324,10 @@
       <x:c r="J65" t="str"/>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="24" t="str"/>
+      <x:c r="A66" s="22" t="str"/>
       <x:c r="B66" t="str"/>
       <x:c r="C66" t="str"/>
-      <x:c r="D66" s="24" t="str"/>
+      <x:c r="D66" s="22" t="str"/>
       <x:c r="E66" t="str"/>
       <x:c r="F66" t="str"/>
       <x:c r="G66" t="str"/>
@@ -1706,10 +3336,10 @@
       <x:c r="J66" t="str"/>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="24" t="str"/>
+      <x:c r="A67" s="22" t="str"/>
       <x:c r="B67" t="str"/>
       <x:c r="C67" t="str"/>
-      <x:c r="D67" s="24" t="str"/>
+      <x:c r="D67" s="22" t="str"/>
       <x:c r="E67" t="str"/>
       <x:c r="F67" t="str"/>
       <x:c r="G67" t="str"/>
@@ -1718,10 +3348,10 @@
       <x:c r="J67" t="str"/>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="24" t="str"/>
+      <x:c r="A68" s="22" t="str"/>
       <x:c r="B68" t="str"/>
       <x:c r="C68" t="str"/>
-      <x:c r="D68" s="24" t="str"/>
+      <x:c r="D68" s="22" t="str"/>
       <x:c r="E68" t="str"/>
       <x:c r="F68" t="str"/>
       <x:c r="G68" t="str"/>
@@ -1730,10 +3360,10 @@
       <x:c r="J68" t="str"/>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="24" t="str"/>
+      <x:c r="A69" s="22" t="str"/>
       <x:c r="B69" t="str"/>
       <x:c r="C69" t="str"/>
-      <x:c r="D69" s="24" t="str"/>
+      <x:c r="D69" s="22" t="str"/>
       <x:c r="E69" t="str"/>
       <x:c r="F69" t="str"/>
       <x:c r="G69" t="str"/>
@@ -1742,10 +3372,10 @@
       <x:c r="J69" t="str"/>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="24" t="str"/>
+      <x:c r="A70" s="22" t="str"/>
       <x:c r="B70" t="str"/>
       <x:c r="C70" t="str"/>
-      <x:c r="D70" s="24" t="str"/>
+      <x:c r="D70" s="22" t="str"/>
       <x:c r="E70" t="str"/>
       <x:c r="F70" t="str"/>
       <x:c r="G70" t="str"/>
@@ -1754,10 +3384,10 @@
       <x:c r="J70" t="str"/>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="24" t="str"/>
+      <x:c r="A71" s="22" t="str"/>
       <x:c r="B71" t="str"/>
       <x:c r="C71" t="str"/>
-      <x:c r="D71" s="24" t="str"/>
+      <x:c r="D71" s="22" t="str"/>
       <x:c r="E71" t="str"/>
       <x:c r="F71" t="str"/>
       <x:c r="G71" t="str"/>
@@ -1766,10 +3396,10 @@
       <x:c r="J71" t="str"/>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="24" t="str"/>
+      <x:c r="A72" s="22" t="str"/>
       <x:c r="B72" t="str"/>
       <x:c r="C72" t="str"/>
-      <x:c r="D72" s="24" t="str"/>
+      <x:c r="D72" s="22" t="str"/>
       <x:c r="E72" t="str"/>
       <x:c r="F72" t="str"/>
       <x:c r="G72" t="str"/>
@@ -1778,10 +3408,10 @@
       <x:c r="J72" t="str"/>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="24" t="str"/>
+      <x:c r="A73" s="22" t="str"/>
       <x:c r="B73" t="str"/>
       <x:c r="C73" t="str"/>
-      <x:c r="D73" s="24" t="str"/>
+      <x:c r="D73" s="22" t="str"/>
       <x:c r="E73" t="str"/>
       <x:c r="F73" t="str"/>
       <x:c r="G73" t="str"/>
@@ -1790,10 +3420,10 @@
       <x:c r="J73" t="str"/>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="24" t="str"/>
+      <x:c r="A74" s="22" t="str"/>
       <x:c r="B74" t="str"/>
       <x:c r="C74" t="str"/>
-      <x:c r="D74" s="24" t="str"/>
+      <x:c r="D74" s="22" t="str"/>
       <x:c r="E74" t="str"/>
       <x:c r="F74" t="str"/>
       <x:c r="G74" t="str"/>
@@ -1802,10 +3432,10 @@
       <x:c r="J74" t="str"/>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" s="24" t="str"/>
+      <x:c r="A75" s="22" t="str"/>
       <x:c r="B75" t="str"/>
       <x:c r="C75" t="str"/>
-      <x:c r="D75" s="24" t="str"/>
+      <x:c r="D75" s="22" t="str"/>
       <x:c r="E75" t="str"/>
       <x:c r="F75" t="str"/>
       <x:c r="G75" t="str"/>
@@ -1814,10 +3444,10 @@
       <x:c r="J75" t="str"/>
     </x:row>
     <x:row r="76">
-      <x:c r="A76" s="24" t="str"/>
+      <x:c r="A76" s="22" t="str"/>
       <x:c r="B76" t="str"/>
       <x:c r="C76" t="str"/>
-      <x:c r="D76" s="24" t="str"/>
+      <x:c r="D76" s="22" t="str"/>
       <x:c r="E76" t="str"/>
       <x:c r="F76" t="str"/>
       <x:c r="G76" t="str"/>
@@ -1826,10 +3456,10 @@
       <x:c r="J76" t="str"/>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" s="24" t="str"/>
+      <x:c r="A77" s="22" t="str"/>
       <x:c r="B77" t="str"/>
       <x:c r="C77" t="str"/>
-      <x:c r="D77" s="24" t="str"/>
+      <x:c r="D77" s="22" t="str"/>
       <x:c r="E77" t="str"/>
       <x:c r="F77" t="str"/>
       <x:c r="G77" t="str"/>
@@ -1838,10 +3468,10 @@
       <x:c r="J77" t="str"/>
     </x:row>
     <x:row r="78">
-      <x:c r="A78" s="24" t="str"/>
+      <x:c r="A78" s="22" t="str"/>
       <x:c r="B78" t="str"/>
       <x:c r="C78" t="str"/>
-      <x:c r="D78" s="24" t="str"/>
+      <x:c r="D78" s="22" t="str"/>
       <x:c r="E78" t="str"/>
       <x:c r="F78" t="str"/>
       <x:c r="G78" t="str"/>
@@ -1850,10 +3480,10 @@
       <x:c r="J78" t="str"/>
     </x:row>
     <x:row r="79">
-      <x:c r="A79" s="24" t="str"/>
+      <x:c r="A79" s="22" t="str"/>
       <x:c r="B79" t="str"/>
       <x:c r="C79" t="str"/>
-      <x:c r="D79" s="24" t="str"/>
+      <x:c r="D79" s="22" t="str"/>
       <x:c r="E79" t="str"/>
       <x:c r="F79" t="str"/>
       <x:c r="G79" t="str"/>
@@ -1862,10 +3492,10 @@
       <x:c r="J79" t="str"/>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" s="24" t="str"/>
+      <x:c r="A80" s="22" t="str"/>
       <x:c r="B80" t="str"/>
       <x:c r="C80" t="str"/>
-      <x:c r="D80" s="24" t="str"/>
+      <x:c r="D80" s="22" t="str"/>
       <x:c r="E80" t="str"/>
       <x:c r="F80" t="str"/>
       <x:c r="G80" t="str"/>
@@ -1874,10 +3504,10 @@
       <x:c r="J80" t="str"/>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" s="24" t="str"/>
+      <x:c r="A81" s="22" t="str"/>
       <x:c r="B81" t="str"/>
       <x:c r="C81" t="str"/>
-      <x:c r="D81" s="24" t="str"/>
+      <x:c r="D81" s="22" t="str"/>
       <x:c r="E81" t="str"/>
       <x:c r="F81" t="str"/>
       <x:c r="G81" t="str"/>
@@ -1886,10 +3516,10 @@
       <x:c r="J81" t="str"/>
     </x:row>
     <x:row r="82">
-      <x:c r="A82" s="24" t="str"/>
+      <x:c r="A82" s="22" t="str"/>
       <x:c r="B82" t="str"/>
       <x:c r="C82" t="str"/>
-      <x:c r="D82" s="24" t="str"/>
+      <x:c r="D82" s="22" t="str"/>
       <x:c r="E82" t="str"/>
       <x:c r="F82" t="str"/>
       <x:c r="G82" t="str"/>
@@ -1898,10 +3528,10 @@
       <x:c r="J82" t="str"/>
     </x:row>
     <x:row r="83">
-      <x:c r="A83" s="24" t="str"/>
+      <x:c r="A83" s="22" t="str"/>
       <x:c r="B83" t="str"/>
       <x:c r="C83" t="str"/>
-      <x:c r="D83" s="24" t="str"/>
+      <x:c r="D83" s="22" t="str"/>
       <x:c r="E83" t="str"/>
       <x:c r="F83" t="str"/>
       <x:c r="G83" t="str"/>
@@ -1910,10 +3540,10 @@
       <x:c r="J83" t="str"/>
     </x:row>
     <x:row r="84">
-      <x:c r="A84" s="24" t="str"/>
+      <x:c r="A84" s="22" t="str"/>
       <x:c r="B84" t="str"/>
       <x:c r="C84" t="str"/>
-      <x:c r="D84" s="24" t="str"/>
+      <x:c r="D84" s="22" t="str"/>
       <x:c r="E84" t="str"/>
       <x:c r="F84" t="str"/>
       <x:c r="G84" t="str"/>
@@ -1922,10 +3552,10 @@
       <x:c r="J84" t="str"/>
     </x:row>
     <x:row r="85">
-      <x:c r="A85" s="24" t="str"/>
+      <x:c r="A85" s="22" t="str"/>
       <x:c r="B85" t="str"/>
       <x:c r="C85" t="str"/>
-      <x:c r="D85" s="24" t="str"/>
+      <x:c r="D85" s="22" t="str"/>
       <x:c r="E85" t="str"/>
       <x:c r="F85" t="str"/>
       <x:c r="G85" t="str"/>
@@ -1934,10 +3564,10 @@
       <x:c r="J85" t="str"/>
     </x:row>
     <x:row r="86">
-      <x:c r="A86" s="24" t="str"/>
+      <x:c r="A86" s="22" t="str"/>
       <x:c r="B86" t="str"/>
       <x:c r="C86" t="str"/>
-      <x:c r="D86" s="24" t="str"/>
+      <x:c r="D86" s="22" t="str"/>
       <x:c r="E86" t="str"/>
       <x:c r="F86" t="str"/>
       <x:c r="G86" t="str"/>
@@ -1946,10 +3576,10 @@
       <x:c r="J86" t="str"/>
     </x:row>
     <x:row r="87">
-      <x:c r="A87" s="24" t="str"/>
+      <x:c r="A87" s="22" t="str"/>
       <x:c r="B87" t="str"/>
       <x:c r="C87" t="str"/>
-      <x:c r="D87" s="24" t="str"/>
+      <x:c r="D87" s="22" t="str"/>
       <x:c r="E87" t="str"/>
       <x:c r="F87" t="str"/>
       <x:c r="G87" t="str"/>
@@ -1958,10 +3588,10 @@
       <x:c r="J87" t="str"/>
     </x:row>
     <x:row r="88">
-      <x:c r="A88" s="24" t="str"/>
+      <x:c r="A88" s="22" t="str"/>
       <x:c r="B88" t="str"/>
       <x:c r="C88" t="str"/>
-      <x:c r="D88" s="24" t="str"/>
+      <x:c r="D88" s="22" t="str"/>
       <x:c r="E88" t="str"/>
       <x:c r="F88" t="str"/>
       <x:c r="G88" t="str"/>
@@ -1970,10 +3600,10 @@
       <x:c r="J88" t="str"/>
     </x:row>
     <x:row r="89">
-      <x:c r="A89" s="24" t="str"/>
+      <x:c r="A89" s="22" t="str"/>
       <x:c r="B89" t="str"/>
       <x:c r="C89" t="str"/>
-      <x:c r="D89" s="24" t="str"/>
+      <x:c r="D89" s="22" t="str"/>
       <x:c r="E89" t="str"/>
       <x:c r="F89" t="str"/>
       <x:c r="G89" t="str"/>
@@ -1982,10 +3612,10 @@
       <x:c r="J89" t="str"/>
     </x:row>
     <x:row r="90">
-      <x:c r="A90" s="24" t="str"/>
+      <x:c r="A90" s="22" t="str"/>
       <x:c r="B90" t="str"/>
       <x:c r="C90" t="str"/>
-      <x:c r="D90" s="24" t="str"/>
+      <x:c r="D90" s="22" t="str"/>
       <x:c r="E90" t="str"/>
       <x:c r="F90" t="str"/>
       <x:c r="G90" t="str"/>
@@ -1994,10 +3624,10 @@
       <x:c r="J90" t="str"/>
     </x:row>
     <x:row r="91">
-      <x:c r="A91" s="24" t="str"/>
+      <x:c r="A91" s="22" t="str"/>
       <x:c r="B91" t="str"/>
       <x:c r="C91" t="str"/>
-      <x:c r="D91" s="24" t="str"/>
+      <x:c r="D91" s="22" t="str"/>
       <x:c r="E91" t="str"/>
       <x:c r="F91" t="str"/>
       <x:c r="G91" t="str"/>
@@ -2006,10 +3636,10 @@
       <x:c r="J91" t="str"/>
     </x:row>
     <x:row r="92">
-      <x:c r="A92" s="24" t="str"/>
+      <x:c r="A92" s="22" t="str"/>
       <x:c r="B92" t="str"/>
       <x:c r="C92" t="str"/>
-      <x:c r="D92" s="24" t="str"/>
+      <x:c r="D92" s="22" t="str"/>
       <x:c r="E92" t="str"/>
       <x:c r="F92" t="str"/>
       <x:c r="G92" t="str"/>
@@ -2018,10 +3648,10 @@
       <x:c r="J92" t="str"/>
     </x:row>
     <x:row r="93">
-      <x:c r="A93" s="24" t="str"/>
+      <x:c r="A93" s="22" t="str"/>
       <x:c r="B93" t="str"/>
       <x:c r="C93" t="str"/>
-      <x:c r="D93" s="24" t="str"/>
+      <x:c r="D93" s="22" t="str"/>
       <x:c r="E93" t="str"/>
       <x:c r="F93" t="str"/>
       <x:c r="G93" t="str"/>
@@ -2030,10 +3660,10 @@
       <x:c r="J93" t="str"/>
     </x:row>
     <x:row r="94">
-      <x:c r="A94" s="24" t="str"/>
+      <x:c r="A94" s="22" t="str"/>
       <x:c r="B94" t="str"/>
       <x:c r="C94" t="str"/>
-      <x:c r="D94" s="24" t="str"/>
+      <x:c r="D94" s="22" t="str"/>
       <x:c r="E94" t="str"/>
       <x:c r="F94" t="str"/>
       <x:c r="G94" t="str"/>
@@ -2042,10 +3672,10 @@
       <x:c r="J94" t="str"/>
     </x:row>
     <x:row r="95">
-      <x:c r="A95" s="24" t="str"/>
+      <x:c r="A95" s="22" t="str"/>
       <x:c r="B95" t="str"/>
       <x:c r="C95" t="str"/>
-      <x:c r="D95" s="24" t="str"/>
+      <x:c r="D95" s="22" t="str"/>
       <x:c r="E95" t="str"/>
       <x:c r="F95" t="str"/>
       <x:c r="G95" t="str"/>
@@ -2054,10 +3684,10 @@
       <x:c r="J95" t="str"/>
     </x:row>
     <x:row r="96">
-      <x:c r="A96" s="24" t="str"/>
+      <x:c r="A96" s="22" t="str"/>
       <x:c r="B96" t="str"/>
       <x:c r="C96" t="str"/>
-      <x:c r="D96" s="24" t="str"/>
+      <x:c r="D96" s="22" t="str"/>
       <x:c r="E96" t="str"/>
       <x:c r="F96" t="str"/>
       <x:c r="G96" t="str"/>
@@ -2066,10 +3696,10 @@
       <x:c r="J96" t="str"/>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" s="24" t="str"/>
+      <x:c r="A97" s="22" t="str"/>
       <x:c r="B97" t="str"/>
       <x:c r="C97" t="str"/>
-      <x:c r="D97" s="24" t="str"/>
+      <x:c r="D97" s="22" t="str"/>
       <x:c r="E97" t="str"/>
       <x:c r="F97" t="str"/>
       <x:c r="G97" t="str"/>
@@ -2078,10 +3708,10 @@
       <x:c r="J97" t="str"/>
     </x:row>
     <x:row r="98">
-      <x:c r="A98" s="24" t="str"/>
+      <x:c r="A98" s="22" t="str"/>
       <x:c r="B98" t="str"/>
       <x:c r="C98" t="str"/>
-      <x:c r="D98" s="24" t="str"/>
+      <x:c r="D98" s="22" t="str"/>
       <x:c r="E98" t="str"/>
       <x:c r="F98" t="str"/>
       <x:c r="G98" t="str"/>
@@ -2090,10 +3720,10 @@
       <x:c r="J98" t="str"/>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" s="24" t="str"/>
+      <x:c r="A99" s="22" t="str"/>
       <x:c r="B99" t="str"/>
       <x:c r="C99" t="str"/>
-      <x:c r="D99" s="24" t="str"/>
+      <x:c r="D99" s="22" t="str"/>
       <x:c r="E99" t="str"/>
       <x:c r="F99" t="str"/>
       <x:c r="G99" t="str"/>
@@ -2102,10 +3732,10 @@
       <x:c r="J99" t="str"/>
     </x:row>
     <x:row r="100">
-      <x:c r="A100" s="24" t="str"/>
+      <x:c r="A100" s="22" t="str"/>
       <x:c r="B100" t="str"/>
       <x:c r="C100" t="str"/>
-      <x:c r="D100" s="24" t="str"/>
+      <x:c r="D100" s="22" t="str"/>
       <x:c r="E100" t="str"/>
       <x:c r="F100" t="str"/>
       <x:c r="G100" t="str"/>
@@ -2114,10 +3744,10 @@
       <x:c r="J100" t="str"/>
     </x:row>
     <x:row r="101">
-      <x:c r="A101" s="24" t="str"/>
+      <x:c r="A101" s="22" t="str"/>
       <x:c r="B101" t="str"/>
       <x:c r="C101" t="str"/>
-      <x:c r="D101" s="24" t="str"/>
+      <x:c r="D101" s="22" t="str"/>
       <x:c r="E101" t="str"/>
       <x:c r="F101" t="str"/>
       <x:c r="G101" t="str"/>
@@ -2126,10 +3756,10 @@
       <x:c r="J101" t="str"/>
     </x:row>
     <x:row r="102">
-      <x:c r="A102" s="24" t="str"/>
+      <x:c r="A102" s="22" t="str"/>
       <x:c r="B102" t="str"/>
       <x:c r="C102" t="str"/>
-      <x:c r="D102" s="24" t="str"/>
+      <x:c r="D102" s="22" t="str"/>
       <x:c r="E102" t="str"/>
       <x:c r="F102" t="str"/>
       <x:c r="G102" t="str"/>
@@ -2138,10 +3768,10 @@
       <x:c r="J102" t="str"/>
     </x:row>
     <x:row r="103">
-      <x:c r="A103" s="24" t="str"/>
+      <x:c r="A103" s="22" t="str"/>
       <x:c r="B103" t="str"/>
       <x:c r="C103" t="str"/>
-      <x:c r="D103" s="24" t="str"/>
+      <x:c r="D103" s="22" t="str"/>
       <x:c r="E103" t="str"/>
       <x:c r="F103" t="str"/>
       <x:c r="G103" t="str"/>
@@ -2150,10 +3780,10 @@
       <x:c r="J103" t="str"/>
     </x:row>
     <x:row r="104">
-      <x:c r="A104" s="24" t="str"/>
+      <x:c r="A104" s="22" t="str"/>
       <x:c r="B104" t="str"/>
       <x:c r="C104" t="str"/>
-      <x:c r="D104" s="24" t="str"/>
+      <x:c r="D104" s="22" t="str"/>
       <x:c r="E104" t="str"/>
       <x:c r="F104" t="str"/>
       <x:c r="G104" t="str"/>
@@ -2162,10 +3792,10 @@
       <x:c r="J104" t="str"/>
     </x:row>
     <x:row r="105">
-      <x:c r="A105" s="24" t="str"/>
+      <x:c r="A105" s="22" t="str"/>
       <x:c r="B105" t="str"/>
       <x:c r="C105" t="str"/>
-      <x:c r="D105" s="24" t="str"/>
+      <x:c r="D105" s="22" t="str"/>
       <x:c r="E105" t="str"/>
       <x:c r="F105" t="str"/>
       <x:c r="G105" t="str"/>
@@ -2174,10 +3804,10 @@
       <x:c r="J105" t="str"/>
     </x:row>
     <x:row r="106">
-      <x:c r="A106" s="24" t="str"/>
+      <x:c r="A106" s="22" t="str"/>
       <x:c r="B106" t="str"/>
       <x:c r="C106" t="str"/>
-      <x:c r="D106" s="24" t="str"/>
+      <x:c r="D106" s="22" t="str"/>
       <x:c r="E106" t="str"/>
       <x:c r="F106" t="str"/>
       <x:c r="G106" t="str"/>
@@ -2186,10 +3816,10 @@
       <x:c r="J106" t="str"/>
     </x:row>
     <x:row r="107">
-      <x:c r="A107" s="24" t="str"/>
+      <x:c r="A107" s="22" t="str"/>
       <x:c r="B107" t="str"/>
       <x:c r="C107" t="str"/>
-      <x:c r="D107" s="24" t="str"/>
+      <x:c r="D107" s="22" t="str"/>
       <x:c r="E107" t="str"/>
       <x:c r="F107" t="str"/>
       <x:c r="G107" t="str"/>
@@ -2198,10 +3828,10 @@
       <x:c r="J107" t="str"/>
     </x:row>
     <x:row r="108">
-      <x:c r="A108" s="24" t="str"/>
+      <x:c r="A108" s="22" t="str"/>
       <x:c r="B108" t="str"/>
       <x:c r="C108" t="str"/>
-      <x:c r="D108" s="24" t="str"/>
+      <x:c r="D108" s="22" t="str"/>
       <x:c r="E108" t="str"/>
       <x:c r="F108" t="str"/>
       <x:c r="G108" t="str"/>
@@ -2210,10 +3840,10 @@
       <x:c r="J108" t="str"/>
     </x:row>
     <x:row r="109">
-      <x:c r="A109" s="24" t="str"/>
+      <x:c r="A109" s="22" t="str"/>
       <x:c r="B109" t="str"/>
       <x:c r="C109" t="str"/>
-      <x:c r="D109" s="24" t="str"/>
+      <x:c r="D109" s="22" t="str"/>
       <x:c r="E109" t="str"/>
       <x:c r="F109" t="str"/>
       <x:c r="G109" t="str"/>
@@ -2222,10 +3852,10 @@
       <x:c r="J109" t="str"/>
     </x:row>
     <x:row r="110">
-      <x:c r="A110" s="24" t="str"/>
+      <x:c r="A110" s="22" t="str"/>
       <x:c r="B110" t="str"/>
       <x:c r="C110" t="str"/>
-      <x:c r="D110" s="24" t="str"/>
+      <x:c r="D110" s="22" t="str"/>
       <x:c r="E110" t="str"/>
       <x:c r="F110" t="str"/>
       <x:c r="G110" t="str"/>
@@ -2234,10 +3864,10 @@
       <x:c r="J110" t="str"/>
     </x:row>
     <x:row r="111">
-      <x:c r="A111" s="24" t="str"/>
+      <x:c r="A111" s="22" t="str"/>
       <x:c r="B111" t="str"/>
       <x:c r="C111" t="str"/>
-      <x:c r="D111" s="24" t="str"/>
+      <x:c r="D111" s="22" t="str"/>
       <x:c r="E111" t="str"/>
       <x:c r="F111" t="str"/>
       <x:c r="G111" t="str"/>
@@ -2246,10 +3876,10 @@
       <x:c r="J111" t="str"/>
     </x:row>
     <x:row r="112">
-      <x:c r="A112" s="24" t="str"/>
+      <x:c r="A112" s="22" t="str"/>
       <x:c r="B112" t="str"/>
       <x:c r="C112" t="str"/>
-      <x:c r="D112" s="24" t="str"/>
+      <x:c r="D112" s="22" t="str"/>
       <x:c r="E112" t="str"/>
       <x:c r="F112" t="str"/>
       <x:c r="G112" t="str"/>
@@ -2258,10 +3888,10 @@
       <x:c r="J112" t="str"/>
     </x:row>
     <x:row r="113">
-      <x:c r="A113" s="24" t="str"/>
+      <x:c r="A113" s="22" t="str"/>
       <x:c r="B113" t="str"/>
       <x:c r="C113" t="str"/>
-      <x:c r="D113" s="24" t="str"/>
+      <x:c r="D113" s="22" t="str"/>
       <x:c r="E113" t="str"/>
       <x:c r="F113" t="str"/>
       <x:c r="G113" t="str"/>
@@ -2270,10 +3900,10 @@
       <x:c r="J113" t="str"/>
     </x:row>
     <x:row r="114">
-      <x:c r="A114" s="24" t="str"/>
+      <x:c r="A114" s="22" t="str"/>
       <x:c r="B114" t="str"/>
       <x:c r="C114" t="str"/>
-      <x:c r="D114" s="24" t="str"/>
+      <x:c r="D114" s="22" t="str"/>
       <x:c r="E114" t="str"/>
       <x:c r="F114" t="str"/>
       <x:c r="G114" t="str"/>
@@ -2282,10 +3912,10 @@
       <x:c r="J114" t="str"/>
     </x:row>
     <x:row r="115">
-      <x:c r="A115" s="24" t="str"/>
+      <x:c r="A115" s="22" t="str"/>
       <x:c r="B115" t="str"/>
       <x:c r="C115" t="str"/>
-      <x:c r="D115" s="24" t="str"/>
+      <x:c r="D115" s="22" t="str"/>
       <x:c r="E115" t="str"/>
       <x:c r="F115" t="str"/>
       <x:c r="G115" t="str"/>
@@ -2294,10 +3924,10 @@
       <x:c r="J115" t="str"/>
     </x:row>
     <x:row r="116">
-      <x:c r="A116" s="24" t="str"/>
+      <x:c r="A116" s="22" t="str"/>
       <x:c r="B116" t="str"/>
       <x:c r="C116" t="str"/>
-      <x:c r="D116" s="24" t="str"/>
+      <x:c r="D116" s="22" t="str"/>
       <x:c r="E116" t="str"/>
       <x:c r="F116" t="str"/>
       <x:c r="G116" t="str"/>
@@ -2306,10 +3936,10 @@
       <x:c r="J116" t="str"/>
     </x:row>
     <x:row r="117">
-      <x:c r="A117" s="24" t="str"/>
+      <x:c r="A117" s="22" t="str"/>
       <x:c r="B117" t="str"/>
       <x:c r="C117" t="str"/>
-      <x:c r="D117" s="24" t="str"/>
+      <x:c r="D117" s="22" t="str"/>
       <x:c r="E117" t="str"/>
       <x:c r="F117" t="str"/>
       <x:c r="G117" t="str"/>
@@ -2318,10 +3948,10 @@
       <x:c r="J117" t="str"/>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" s="24" t="str"/>
+      <x:c r="A118" s="22" t="str"/>
       <x:c r="B118" t="str"/>
       <x:c r="C118" t="str"/>
-      <x:c r="D118" s="24" t="str"/>
+      <x:c r="D118" s="22" t="str"/>
       <x:c r="E118" t="str"/>
       <x:c r="F118" t="str"/>
       <x:c r="G118" t="str"/>
@@ -2330,10 +3960,10 @@
       <x:c r="J118" t="str"/>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" s="24" t="str"/>
+      <x:c r="A119" s="22" t="str"/>
       <x:c r="B119" t="str"/>
       <x:c r="C119" t="str"/>
-      <x:c r="D119" s="24" t="str"/>
+      <x:c r="D119" s="22" t="str"/>
       <x:c r="E119" t="str"/>
       <x:c r="F119" t="str"/>
       <x:c r="G119" t="str"/>
@@ -2342,10 +3972,10 @@
       <x:c r="J119" t="str"/>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" s="24" t="str"/>
+      <x:c r="A120" s="22" t="str"/>
       <x:c r="B120" t="str"/>
       <x:c r="C120" t="str"/>
-      <x:c r="D120" s="24" t="str"/>
+      <x:c r="D120" s="22" t="str"/>
       <x:c r="E120" t="str"/>
       <x:c r="F120" t="str"/>
       <x:c r="G120" t="str"/>
@@ -2354,10 +3984,10 @@
       <x:c r="J120" t="str"/>
     </x:row>
     <x:row r="121">
-      <x:c r="A121" s="24" t="str"/>
+      <x:c r="A121" s="22" t="str"/>
       <x:c r="B121" t="str"/>
       <x:c r="C121" t="str"/>
-      <x:c r="D121" s="24" t="str"/>
+      <x:c r="D121" s="22" t="str"/>
       <x:c r="E121" t="str"/>
       <x:c r="F121" t="str"/>
       <x:c r="G121" t="str"/>
@@ -2366,10 +3996,10 @@
       <x:c r="J121" t="str"/>
     </x:row>
     <x:row r="122">
-      <x:c r="A122" s="24" t="str"/>
+      <x:c r="A122" s="22" t="str"/>
       <x:c r="B122" t="str"/>
       <x:c r="C122" t="str"/>
-      <x:c r="D122" s="24" t="str"/>
+      <x:c r="D122" s="22" t="str"/>
       <x:c r="E122" t="str"/>
       <x:c r="F122" t="str"/>
       <x:c r="G122" t="str"/>
@@ -2378,10 +4008,10 @@
       <x:c r="J122" t="str"/>
     </x:row>
     <x:row r="123">
-      <x:c r="A123" s="24" t="str"/>
+      <x:c r="A123" s="22" t="str"/>
       <x:c r="B123" t="str"/>
       <x:c r="C123" t="str"/>
-      <x:c r="D123" s="24" t="str"/>
+      <x:c r="D123" s="22" t="str"/>
       <x:c r="E123" t="str"/>
       <x:c r="F123" t="str"/>
       <x:c r="G123" t="str"/>
@@ -2390,10 +4020,10 @@
       <x:c r="J123" t="str"/>
     </x:row>
     <x:row r="124">
-      <x:c r="A124" s="24" t="str"/>
+      <x:c r="A124" s="22" t="str"/>
       <x:c r="B124" t="str"/>
       <x:c r="C124" t="str"/>
-      <x:c r="D124" s="24" t="str"/>
+      <x:c r="D124" s="22" t="str"/>
       <x:c r="E124" t="str"/>
       <x:c r="F124" t="str"/>
       <x:c r="G124" t="str"/>
@@ -2402,10 +4032,10 @@
       <x:c r="J124" t="str"/>
     </x:row>
     <x:row r="125">
-      <x:c r="A125" s="24" t="str"/>
+      <x:c r="A125" s="22" t="str"/>
       <x:c r="B125" t="str"/>
       <x:c r="C125" t="str"/>
-      <x:c r="D125" s="24" t="str"/>
+      <x:c r="D125" s="22" t="str"/>
       <x:c r="E125" t="str"/>
       <x:c r="F125" t="str"/>
       <x:c r="G125" t="str"/>
@@ -2414,10 +4044,10 @@
       <x:c r="J125" t="str"/>
     </x:row>
     <x:row r="126">
-      <x:c r="A126" s="24" t="str"/>
+      <x:c r="A126" s="22" t="str"/>
       <x:c r="B126" t="str"/>
       <x:c r="C126" t="str"/>
-      <x:c r="D126" s="24" t="str"/>
+      <x:c r="D126" s="22" t="str"/>
       <x:c r="E126" t="str"/>
       <x:c r="F126" t="str"/>
       <x:c r="G126" t="str"/>
@@ -2426,10 +4056,10 @@
       <x:c r="J126" t="str"/>
     </x:row>
     <x:row r="127">
-      <x:c r="A127" s="24" t="str"/>
+      <x:c r="A127" s="22" t="str"/>
       <x:c r="B127" t="str"/>
       <x:c r="C127" t="str"/>
-      <x:c r="D127" s="24" t="str"/>
+      <x:c r="D127" s="22" t="str"/>
       <x:c r="E127" t="str"/>
       <x:c r="F127" t="str"/>
       <x:c r="G127" t="str"/>
@@ -2438,10 +4068,10 @@
       <x:c r="J127" t="str"/>
     </x:row>
     <x:row r="128">
-      <x:c r="A128" s="24" t="str"/>
+      <x:c r="A128" s="22" t="str"/>
       <x:c r="B128" t="str"/>
       <x:c r="C128" t="str"/>
-      <x:c r="D128" s="24" t="str"/>
+      <x:c r="D128" s="22" t="str"/>
       <x:c r="E128" t="str"/>
       <x:c r="F128" t="str"/>
       <x:c r="G128" t="str"/>
@@ -2450,10 +4080,10 @@
       <x:c r="J128" t="str"/>
     </x:row>
     <x:row r="129">
-      <x:c r="A129" s="24" t="str"/>
+      <x:c r="A129" s="22" t="str"/>
       <x:c r="B129" t="str"/>
       <x:c r="C129" t="str"/>
-      <x:c r="D129" s="24" t="str"/>
+      <x:c r="D129" s="22" t="str"/>
       <x:c r="E129" t="str"/>
       <x:c r="F129" t="str"/>
       <x:c r="G129" t="str"/>
@@ -2462,10 +4092,10 @@
       <x:c r="J129" t="str"/>
     </x:row>
     <x:row r="130">
-      <x:c r="A130" s="24" t="str"/>
+      <x:c r="A130" s="22" t="str"/>
       <x:c r="B130" t="str"/>
       <x:c r="C130" t="str"/>
-      <x:c r="D130" s="24" t="str"/>
+      <x:c r="D130" s="22" t="str"/>
       <x:c r="E130" t="str"/>
       <x:c r="F130" t="str"/>
       <x:c r="G130" t="str"/>
@@ -2474,10 +4104,10 @@
       <x:c r="J130" t="str"/>
     </x:row>
     <x:row r="131">
-      <x:c r="A131" s="24" t="str"/>
+      <x:c r="A131" s="22" t="str"/>
       <x:c r="B131" t="str"/>
       <x:c r="C131" t="str"/>
-      <x:c r="D131" s="24" t="str"/>
+      <x:c r="D131" s="22" t="str"/>
       <x:c r="E131" t="str"/>
       <x:c r="F131" t="str"/>
       <x:c r="G131" t="str"/>
@@ -2486,10 +4116,10 @@
       <x:c r="J131" t="str"/>
     </x:row>
     <x:row r="132">
-      <x:c r="A132" s="24" t="str"/>
+      <x:c r="A132" s="22" t="str"/>
       <x:c r="B132" t="str"/>
       <x:c r="C132" t="str"/>
-      <x:c r="D132" s="24" t="str"/>
+      <x:c r="D132" s="22" t="str"/>
       <x:c r="E132" t="str"/>
       <x:c r="F132" t="str"/>
       <x:c r="G132" t="str"/>
@@ -2498,10 +4128,10 @@
       <x:c r="J132" t="str"/>
     </x:row>
     <x:row r="133">
-      <x:c r="A133" s="24" t="str"/>
+      <x:c r="A133" s="22" t="str"/>
       <x:c r="B133" t="str"/>
       <x:c r="C133" t="str"/>
-      <x:c r="D133" s="24" t="str"/>
+      <x:c r="D133" s="22" t="str"/>
       <x:c r="E133" t="str"/>
       <x:c r="F133" t="str"/>
       <x:c r="G133" t="str"/>
@@ -2510,10 +4140,10 @@
       <x:c r="J133" t="str"/>
     </x:row>
     <x:row r="134">
-      <x:c r="A134" s="24" t="str"/>
+      <x:c r="A134" s="22" t="str"/>
       <x:c r="B134" t="str"/>
       <x:c r="C134" t="str"/>
-      <x:c r="D134" s="24" t="str"/>
+      <x:c r="D134" s="22" t="str"/>
       <x:c r="E134" t="str"/>
       <x:c r="F134" t="str"/>
       <x:c r="G134" t="str"/>
@@ -2522,10 +4152,10 @@
       <x:c r="J134" t="str"/>
     </x:row>
     <x:row r="135">
-      <x:c r="A135" s="24" t="str"/>
+      <x:c r="A135" s="22" t="str"/>
       <x:c r="B135" t="str"/>
       <x:c r="C135" t="str"/>
-      <x:c r="D135" s="24" t="str"/>
+      <x:c r="D135" s="22" t="str"/>
       <x:c r="E135" t="str"/>
       <x:c r="F135" t="str"/>
       <x:c r="G135" t="str"/>
@@ -2534,10 +4164,10 @@
       <x:c r="J135" t="str"/>
     </x:row>
     <x:row r="136">
-      <x:c r="A136" s="24" t="str"/>
+      <x:c r="A136" s="22" t="str"/>
       <x:c r="B136" t="str"/>
       <x:c r="C136" t="str"/>
-      <x:c r="D136" s="24" t="str"/>
+      <x:c r="D136" s="22" t="str"/>
       <x:c r="E136" t="str"/>
       <x:c r="F136" t="str"/>
       <x:c r="G136" t="str"/>
@@ -2546,10 +4176,10 @@
       <x:c r="J136" t="str"/>
     </x:row>
     <x:row r="137">
-      <x:c r="A137" s="24" t="str"/>
+      <x:c r="A137" s="22" t="str"/>
       <x:c r="B137" t="str"/>
       <x:c r="C137" t="str"/>
-      <x:c r="D137" s="24" t="str"/>
+      <x:c r="D137" s="22" t="str"/>
       <x:c r="E137" t="str"/>
       <x:c r="F137" t="str"/>
       <x:c r="G137" t="str"/>
@@ -2558,10 +4188,10 @@
       <x:c r="J137" t="str"/>
     </x:row>
     <x:row r="138">
-      <x:c r="A138" s="24" t="str"/>
+      <x:c r="A138" s="22" t="str"/>
       <x:c r="B138" t="str"/>
       <x:c r="C138" t="str"/>
-      <x:c r="D138" s="24" t="str"/>
+      <x:c r="D138" s="22" t="str"/>
       <x:c r="E138" t="str"/>
       <x:c r="F138" t="str"/>
       <x:c r="G138" t="str"/>
@@ -2570,10 +4200,10 @@
       <x:c r="J138" t="str"/>
     </x:row>
     <x:row r="139">
-      <x:c r="A139" s="24" t="str"/>
+      <x:c r="A139" s="22" t="str"/>
       <x:c r="B139" t="str"/>
       <x:c r="C139" t="str"/>
-      <x:c r="D139" s="24" t="str"/>
+      <x:c r="D139" s="22" t="str"/>
       <x:c r="E139" t="str"/>
       <x:c r="F139" t="str"/>
       <x:c r="G139" t="str"/>
@@ -2582,10 +4212,10 @@
       <x:c r="J139" t="str"/>
     </x:row>
     <x:row r="140">
-      <x:c r="A140" s="24" t="str"/>
+      <x:c r="A140" s="22" t="str"/>
       <x:c r="B140" t="str"/>
       <x:c r="C140" t="str"/>
-      <x:c r="D140" s="24" t="str"/>
+      <x:c r="D140" s="22" t="str"/>
       <x:c r="E140" t="str"/>
       <x:c r="F140" t="str"/>
       <x:c r="G140" t="str"/>
@@ -2594,10 +4224,10 @@
       <x:c r="J140" t="str"/>
     </x:row>
     <x:row r="141">
-      <x:c r="A141" s="24" t="str"/>
+      <x:c r="A141" s="22" t="str"/>
       <x:c r="B141" t="str"/>
       <x:c r="C141" t="str"/>
-      <x:c r="D141" s="24" t="str"/>
+      <x:c r="D141" s="22" t="str"/>
       <x:c r="E141" t="str"/>
       <x:c r="F141" t="str"/>
       <x:c r="G141" t="str"/>
@@ -2606,10 +4236,10 @@
       <x:c r="J141" t="str"/>
     </x:row>
     <x:row r="142">
-      <x:c r="A142" s="24" t="str"/>
+      <x:c r="A142" s="22" t="str"/>
       <x:c r="B142" t="str"/>
       <x:c r="C142" t="str"/>
-      <x:c r="D142" s="24" t="str"/>
+      <x:c r="D142" s="22" t="str"/>
       <x:c r="E142" t="str"/>
       <x:c r="F142" t="str"/>
       <x:c r="G142" t="str"/>
@@ -2618,10 +4248,10 @@
       <x:c r="J142" t="str"/>
     </x:row>
     <x:row r="143">
-      <x:c r="A143" s="24" t="str"/>
+      <x:c r="A143" s="22" t="str"/>
       <x:c r="B143" t="str"/>
       <x:c r="C143" t="str"/>
-      <x:c r="D143" s="24" t="str"/>
+      <x:c r="D143" s="22" t="str"/>
       <x:c r="E143" t="str"/>
       <x:c r="F143" t="str"/>
       <x:c r="G143" t="str"/>
@@ -2630,10 +4260,10 @@
       <x:c r="J143" t="str"/>
     </x:row>
     <x:row r="144">
-      <x:c r="A144" s="24" t="str"/>
+      <x:c r="A144" s="22" t="str"/>
       <x:c r="B144" t="str"/>
       <x:c r="C144" t="str"/>
-      <x:c r="D144" s="24" t="str"/>
+      <x:c r="D144" s="22" t="str"/>
       <x:c r="E144" t="str"/>
       <x:c r="F144" t="str"/>
       <x:c r="G144" t="str"/>
@@ -2642,10 +4272,10 @@
       <x:c r="J144" t="str"/>
     </x:row>
     <x:row r="145">
-      <x:c r="A145" s="24" t="str"/>
+      <x:c r="A145" s="22" t="str"/>
       <x:c r="B145" t="str"/>
       <x:c r="C145" t="str"/>
-      <x:c r="D145" s="24" t="str"/>
+      <x:c r="D145" s="22" t="str"/>
       <x:c r="E145" t="str"/>
       <x:c r="F145" t="str"/>
       <x:c r="G145" t="str"/>
@@ -2654,10 +4284,10 @@
       <x:c r="J145" t="str"/>
     </x:row>
     <x:row r="146">
-      <x:c r="A146" s="24" t="str"/>
+      <x:c r="A146" s="22" t="str"/>
       <x:c r="B146" t="str"/>
       <x:c r="C146" t="str"/>
-      <x:c r="D146" s="24" t="str"/>
+      <x:c r="D146" s="22" t="str"/>
       <x:c r="E146" t="str"/>
       <x:c r="F146" t="str"/>
       <x:c r="G146" t="str"/>
@@ -2666,10 +4296,10 @@
       <x:c r="J146" t="str"/>
     </x:row>
     <x:row r="147">
-      <x:c r="A147" s="24" t="str"/>
+      <x:c r="A147" s="22" t="str"/>
       <x:c r="B147" t="str"/>
       <x:c r="C147" t="str"/>
-      <x:c r="D147" s="24" t="str"/>
+      <x:c r="D147" s="22" t="str"/>
       <x:c r="E147" t="str"/>
       <x:c r="F147" t="str"/>
       <x:c r="G147" t="str"/>
@@ -2678,10 +4308,10 @@
       <x:c r="J147" t="str"/>
     </x:row>
     <x:row r="148">
-      <x:c r="A148" s="24" t="str"/>
+      <x:c r="A148" s="22" t="str"/>
       <x:c r="B148" t="str"/>
       <x:c r="C148" t="str"/>
-      <x:c r="D148" s="24" t="str"/>
+      <x:c r="D148" s="22" t="str"/>
       <x:c r="E148" t="str"/>
       <x:c r="F148" t="str"/>
       <x:c r="G148" t="str"/>
@@ -2690,10 +4320,10 @@
       <x:c r="J148" t="str"/>
     </x:row>
     <x:row r="149">
-      <x:c r="A149" s="24" t="str"/>
+      <x:c r="A149" s="22" t="str"/>
       <x:c r="B149" t="str"/>
       <x:c r="C149" t="str"/>
-      <x:c r="D149" s="24" t="str"/>
+      <x:c r="D149" s="22" t="str"/>
       <x:c r="E149" t="str"/>
       <x:c r="F149" t="str"/>
       <x:c r="G149" t="str"/>
@@ -2702,10 +4332,10 @@
       <x:c r="J149" t="str"/>
     </x:row>
     <x:row r="150">
-      <x:c r="A150" s="24" t="str"/>
+      <x:c r="A150" s="22" t="str"/>
       <x:c r="B150" t="str"/>
       <x:c r="C150" t="str"/>
-      <x:c r="D150" s="24" t="str"/>
+      <x:c r="D150" s="22" t="str"/>
       <x:c r="E150" t="str"/>
       <x:c r="F150" t="str"/>
       <x:c r="G150" t="str"/>
@@ -2714,10 +4344,10 @@
       <x:c r="J150" t="str"/>
     </x:row>
     <x:row r="151">
-      <x:c r="A151" s="24" t="str"/>
+      <x:c r="A151" s="22" t="str"/>
       <x:c r="B151" t="str"/>
       <x:c r="C151" t="str"/>
-      <x:c r="D151" s="24" t="str"/>
+      <x:c r="D151" s="22" t="str"/>
       <x:c r="E151" t="str"/>
       <x:c r="F151" t="str"/>
       <x:c r="G151" t="str"/>
@@ -2726,10 +4356,10 @@
       <x:c r="J151" t="str"/>
     </x:row>
     <x:row r="152">
-      <x:c r="A152" s="24" t="str"/>
+      <x:c r="A152" s="22" t="str"/>
       <x:c r="B152" t="str"/>
       <x:c r="C152" t="str"/>
-      <x:c r="D152" s="24" t="str"/>
+      <x:c r="D152" s="22" t="str"/>
       <x:c r="E152" t="str"/>
       <x:c r="F152" t="str"/>
       <x:c r="G152" t="str"/>
@@ -2738,10 +4368,10 @@
       <x:c r="J152" t="str"/>
     </x:row>
     <x:row r="153">
-      <x:c r="A153" s="24" t="str"/>
+      <x:c r="A153" s="22" t="str"/>
       <x:c r="B153" t="str"/>
       <x:c r="C153" t="str"/>
-      <x:c r="D153" s="24" t="str"/>
+      <x:c r="D153" s="22" t="str"/>
       <x:c r="E153" t="str"/>
       <x:c r="F153" t="str"/>
       <x:c r="G153" t="str"/>
@@ -2750,10 +4380,10 @@
       <x:c r="J153" t="str"/>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="24" t="str"/>
+      <x:c r="A154" s="22" t="str"/>
       <x:c r="B154" t="str"/>
       <x:c r="C154" t="str"/>
-      <x:c r="D154" s="24" t="str"/>
+      <x:c r="D154" s="22" t="str"/>
       <x:c r="E154" t="str"/>
       <x:c r="F154" t="str"/>
       <x:c r="G154" t="str"/>
@@ -2762,10 +4392,10 @@
       <x:c r="J154" t="str"/>
     </x:row>
     <x:row r="155">
-      <x:c r="A155" s="24" t="str"/>
+      <x:c r="A155" s="22" t="str"/>
       <x:c r="B155" t="str"/>
       <x:c r="C155" t="str"/>
-      <x:c r="D155" s="24" t="str"/>
+      <x:c r="D155" s="22" t="str"/>
       <x:c r="E155" t="str"/>
       <x:c r="F155" t="str"/>
       <x:c r="G155" t="str"/>
@@ -2774,10 +4404,10 @@
       <x:c r="J155" t="str"/>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="24" t="str"/>
+      <x:c r="A156" s="22" t="str"/>
       <x:c r="B156" t="str"/>
       <x:c r="C156" t="str"/>
-      <x:c r="D156" s="24" t="str"/>
+      <x:c r="D156" s="22" t="str"/>
       <x:c r="E156" t="str"/>
       <x:c r="F156" t="str"/>
       <x:c r="G156" t="str"/>
@@ -2786,10 +4416,10 @@
       <x:c r="J156" t="str"/>
     </x:row>
     <x:row r="157">
-      <x:c r="A157" s="24" t="str"/>
+      <x:c r="A157" s="22" t="str"/>
       <x:c r="B157" t="str"/>
       <x:c r="C157" t="str"/>
-      <x:c r="D157" s="24" t="str"/>
+      <x:c r="D157" s="22" t="str"/>
       <x:c r="E157" t="str"/>
       <x:c r="F157" t="str"/>
       <x:c r="G157" t="str"/>
@@ -2798,10 +4428,10 @@
       <x:c r="J157" t="str"/>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="24" t="str"/>
+      <x:c r="A158" s="22" t="str"/>
       <x:c r="B158" t="str"/>
       <x:c r="C158" t="str"/>
-      <x:c r="D158" s="24" t="str"/>
+      <x:c r="D158" s="22" t="str"/>
       <x:c r="E158" t="str"/>
       <x:c r="F158" t="str"/>
       <x:c r="G158" t="str"/>
@@ -2810,10 +4440,10 @@
       <x:c r="J158" t="str"/>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="24" t="str"/>
+      <x:c r="A159" s="22" t="str"/>
       <x:c r="B159" t="str"/>
       <x:c r="C159" t="str"/>
-      <x:c r="D159" s="24" t="str"/>
+      <x:c r="D159" s="22" t="str"/>
       <x:c r="E159" t="str"/>
       <x:c r="F159" t="str"/>
       <x:c r="G159" t="str"/>
@@ -2822,10 +4452,10 @@
       <x:c r="J159" t="str"/>
     </x:row>
     <x:row r="160">
-      <x:c r="A160" s="24" t="str"/>
+      <x:c r="A160" s="22" t="str"/>
       <x:c r="B160" t="str"/>
       <x:c r="C160" t="str"/>
-      <x:c r="D160" s="24" t="str"/>
+      <x:c r="D160" s="22" t="str"/>
       <x:c r="E160" t="str"/>
       <x:c r="F160" t="str"/>
       <x:c r="G160" t="str"/>
@@ -2834,10 +4464,10 @@
       <x:c r="J160" t="str"/>
     </x:row>
     <x:row r="161">
-      <x:c r="A161" s="24" t="str"/>
+      <x:c r="A161" s="22" t="str"/>
       <x:c r="B161" t="str"/>
       <x:c r="C161" t="str"/>
-      <x:c r="D161" s="24" t="str"/>
+      <x:c r="D161" s="22" t="str"/>
       <x:c r="E161" t="str"/>
       <x:c r="F161" t="str"/>
       <x:c r="G161" t="str"/>
@@ -2846,10 +4476,10 @@
       <x:c r="J161" t="str"/>
     </x:row>
     <x:row r="162">
-      <x:c r="A162" s="24" t="str"/>
+      <x:c r="A162" s="22" t="str"/>
       <x:c r="B162" t="str"/>
       <x:c r="C162" t="str"/>
-      <x:c r="D162" s="24" t="str"/>
+      <x:c r="D162" s="22" t="str"/>
       <x:c r="E162" t="str"/>
       <x:c r="F162" t="str"/>
       <x:c r="G162" t="str"/>
@@ -2858,10 +4488,10 @@
       <x:c r="J162" t="str"/>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="24" t="str"/>
+      <x:c r="A163" s="22" t="str"/>
       <x:c r="B163" t="str"/>
       <x:c r="C163" t="str"/>
-      <x:c r="D163" s="24" t="str"/>
+      <x:c r="D163" s="22" t="str"/>
       <x:c r="E163" t="str"/>
       <x:c r="F163" t="str"/>
       <x:c r="G163" t="str"/>
@@ -2870,10 +4500,10 @@
       <x:c r="J163" t="str"/>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="24" t="str"/>
+      <x:c r="A164" s="22" t="str"/>
       <x:c r="B164" t="str"/>
       <x:c r="C164" t="str"/>
-      <x:c r="D164" s="24" t="str"/>
+      <x:c r="D164" s="22" t="str"/>
       <x:c r="E164" t="str"/>
       <x:c r="F164" t="str"/>
       <x:c r="G164" t="str"/>
@@ -2882,10 +4512,10 @@
       <x:c r="J164" t="str"/>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="24" t="str"/>
+      <x:c r="A165" s="22" t="str"/>
       <x:c r="B165" t="str"/>
       <x:c r="C165" t="str"/>
-      <x:c r="D165" s="24" t="str"/>
+      <x:c r="D165" s="22" t="str"/>
       <x:c r="E165" t="str"/>
       <x:c r="F165" t="str"/>
       <x:c r="G165" t="str"/>
@@ -2894,10 +4524,10 @@
       <x:c r="J165" t="str"/>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="24" t="str"/>
+      <x:c r="A166" s="22" t="str"/>
       <x:c r="B166" t="str"/>
       <x:c r="C166" t="str"/>
-      <x:c r="D166" s="24" t="str"/>
+      <x:c r="D166" s="22" t="str"/>
       <x:c r="E166" t="str"/>
       <x:c r="F166" t="str"/>
       <x:c r="G166" t="str"/>
@@ -2906,10 +4536,10 @@
       <x:c r="J166" t="str"/>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="24" t="str"/>
+      <x:c r="A167" s="22" t="str"/>
       <x:c r="B167" t="str"/>
       <x:c r="C167" t="str"/>
-      <x:c r="D167" s="24" t="str"/>
+      <x:c r="D167" s="22" t="str"/>
       <x:c r="E167" t="str"/>
       <x:c r="F167" t="str"/>
       <x:c r="G167" t="str"/>
@@ -2918,10 +4548,10 @@
       <x:c r="J167" t="str"/>
     </x:row>
     <x:row r="168">
-      <x:c r="A168" s="24" t="str"/>
+      <x:c r="A168" s="22" t="str"/>
       <x:c r="B168" t="str"/>
       <x:c r="C168" t="str"/>
-      <x:c r="D168" s="24" t="str"/>
+      <x:c r="D168" s="22" t="str"/>
       <x:c r="E168" t="str"/>
       <x:c r="F168" t="str"/>
       <x:c r="G168" t="str"/>
@@ -2930,10 +4560,10 @@
       <x:c r="J168" t="str"/>
     </x:row>
     <x:row r="169">
-      <x:c r="A169" s="24" t="str"/>
+      <x:c r="A169" s="22" t="str"/>
       <x:c r="B169" t="str"/>
       <x:c r="C169" t="str"/>
-      <x:c r="D169" s="24" t="str"/>
+      <x:c r="D169" s="22" t="str"/>
       <x:c r="E169" t="str"/>
       <x:c r="F169" t="str"/>
       <x:c r="G169" t="str"/>
@@ -2942,10 +4572,10 @@
       <x:c r="J169" t="str"/>
     </x:row>
     <x:row r="170">
-      <x:c r="A170" s="24" t="str"/>
+      <x:c r="A170" s="22" t="str"/>
       <x:c r="B170" t="str"/>
       <x:c r="C170" t="str"/>
-      <x:c r="D170" s="24" t="str"/>
+      <x:c r="D170" s="22" t="str"/>
       <x:c r="E170" t="str"/>
       <x:c r="F170" t="str"/>
       <x:c r="G170" t="str"/>
@@ -2954,10 +4584,10 @@
       <x:c r="J170" t="str"/>
     </x:row>
     <x:row r="171">
-      <x:c r="A171" s="24" t="str"/>
+      <x:c r="A171" s="22" t="str"/>
       <x:c r="B171" t="str"/>
       <x:c r="C171" t="str"/>
-      <x:c r="D171" s="24" t="str"/>
+      <x:c r="D171" s="22" t="str"/>
       <x:c r="E171" t="str"/>
       <x:c r="F171" t="str"/>
       <x:c r="G171" t="str"/>
@@ -2966,10 +4596,10 @@
       <x:c r="J171" t="str"/>
     </x:row>
     <x:row r="172">
-      <x:c r="A172" s="24" t="str"/>
+      <x:c r="A172" s="22" t="str"/>
       <x:c r="B172" t="str"/>
       <x:c r="C172" t="str"/>
-      <x:c r="D172" s="24" t="str"/>
+      <x:c r="D172" s="22" t="str"/>
       <x:c r="E172" t="str"/>
       <x:c r="F172" t="str"/>
       <x:c r="G172" t="str"/>
@@ -2978,10 +4608,10 @@
       <x:c r="J172" t="str"/>
     </x:row>
     <x:row r="173">
-      <x:c r="A173" s="24" t="str"/>
+      <x:c r="A173" s="22" t="str"/>
       <x:c r="B173" t="str"/>
       <x:c r="C173" t="str"/>
-      <x:c r="D173" s="24" t="str"/>
+      <x:c r="D173" s="22" t="str"/>
       <x:c r="E173" t="str"/>
       <x:c r="F173" t="str"/>
       <x:c r="G173" t="str"/>
@@ -2990,10 +4620,10 @@
       <x:c r="J173" t="str"/>
     </x:row>
     <x:row r="174">
-      <x:c r="A174" s="24" t="str"/>
+      <x:c r="A174" s="22" t="str"/>
       <x:c r="B174" t="str"/>
       <x:c r="C174" t="str"/>
-      <x:c r="D174" s="24" t="str"/>
+      <x:c r="D174" s="22" t="str"/>
       <x:c r="E174" t="str"/>
       <x:c r="F174" t="str"/>
       <x:c r="G174" t="str"/>
@@ -3002,10 +4632,10 @@
       <x:c r="J174" t="str"/>
     </x:row>
     <x:row r="175">
-      <x:c r="A175" s="24" t="str"/>
+      <x:c r="A175" s="22" t="str"/>
       <x:c r="B175" t="str"/>
       <x:c r="C175" t="str"/>
-      <x:c r="D175" s="24" t="str"/>
+      <x:c r="D175" s="22" t="str"/>
       <x:c r="E175" t="str"/>
       <x:c r="F175" t="str"/>
       <x:c r="G175" t="str"/>
@@ -3014,10 +4644,10 @@
       <x:c r="J175" t="str"/>
     </x:row>
     <x:row r="176">
-      <x:c r="A176" s="24" t="str"/>
+      <x:c r="A176" s="22" t="str"/>
       <x:c r="B176" t="str"/>
       <x:c r="C176" t="str"/>
-      <x:c r="D176" s="24" t="str"/>
+      <x:c r="D176" s="22" t="str"/>
       <x:c r="E176" t="str"/>
       <x:c r="F176" t="str"/>
       <x:c r="G176" t="str"/>
@@ -3026,10 +4656,10 @@
       <x:c r="J176" t="str"/>
     </x:row>
     <x:row r="177">
-      <x:c r="A177" s="24" t="str"/>
+      <x:c r="A177" s="22" t="str"/>
       <x:c r="B177" t="str"/>
       <x:c r="C177" t="str"/>
-      <x:c r="D177" s="24" t="str"/>
+      <x:c r="D177" s="22" t="str"/>
       <x:c r="E177" t="str"/>
       <x:c r="F177" t="str"/>
       <x:c r="G177" t="str"/>
@@ -3038,10 +4668,10 @@
       <x:c r="J177" t="str"/>
     </x:row>
     <x:row r="178">
-      <x:c r="A178" s="24" t="str"/>
+      <x:c r="A178" s="22" t="str"/>
       <x:c r="B178" t="str"/>
       <x:c r="C178" t="str"/>
-      <x:c r="D178" s="24" t="str"/>
+      <x:c r="D178" s="22" t="str"/>
       <x:c r="E178" t="str"/>
       <x:c r="F178" t="str"/>
       <x:c r="G178" t="str"/>
@@ -3050,10 +4680,10 @@
       <x:c r="J178" t="str"/>
     </x:row>
     <x:row r="179">
-      <x:c r="A179" s="24" t="str"/>
+      <x:c r="A179" s="22" t="str"/>
       <x:c r="B179" t="str"/>
       <x:c r="C179" t="str"/>
-      <x:c r="D179" s="24" t="str"/>
+      <x:c r="D179" s="22" t="str"/>
       <x:c r="E179" t="str"/>
       <x:c r="F179" t="str"/>
       <x:c r="G179" t="str"/>
@@ -3062,10 +4692,10 @@
       <x:c r="J179" t="str"/>
     </x:row>
     <x:row r="180">
-      <x:c r="A180" s="24" t="str"/>
+      <x:c r="A180" s="22" t="str"/>
       <x:c r="B180" t="str"/>
       <x:c r="C180" t="str"/>
-      <x:c r="D180" s="24" t="str"/>
+      <x:c r="D180" s="22" t="str"/>
       <x:c r="E180" t="str"/>
       <x:c r="F180" t="str"/>
       <x:c r="G180" t="str"/>
@@ -3074,10 +4704,10 @@
       <x:c r="J180" t="str"/>
     </x:row>
     <x:row r="181">
-      <x:c r="A181" s="24" t="str"/>
+      <x:c r="A181" s="22" t="str"/>
       <x:c r="B181" t="str"/>
       <x:c r="C181" t="str"/>
-      <x:c r="D181" s="24" t="str"/>
+      <x:c r="D181" s="22" t="str"/>
       <x:c r="E181" t="str"/>
       <x:c r="F181" t="str"/>
       <x:c r="G181" t="str"/>
@@ -3086,10 +4716,10 @@
       <x:c r="J181" t="str"/>
     </x:row>
     <x:row r="182">
-      <x:c r="A182" s="24" t="str"/>
+      <x:c r="A182" s="22" t="str"/>
       <x:c r="B182" t="str"/>
       <x:c r="C182" t="str"/>
-      <x:c r="D182" s="24" t="str"/>
+      <x:c r="D182" s="22" t="str"/>
       <x:c r="E182" t="str"/>
       <x:c r="F182" t="str"/>
       <x:c r="G182" t="str"/>
@@ -3098,10 +4728,10 @@
       <x:c r="J182" t="str"/>
     </x:row>
     <x:row r="183">
-      <x:c r="A183" s="24" t="str"/>
+      <x:c r="A183" s="22" t="str"/>
       <x:c r="B183" t="str"/>
       <x:c r="C183" t="str"/>
-      <x:c r="D183" s="24" t="str"/>
+      <x:c r="D183" s="22" t="str"/>
       <x:c r="E183" t="str"/>
       <x:c r="F183" t="str"/>
       <x:c r="G183" t="str"/>
@@ -3110,10 +4740,10 @@
       <x:c r="J183" t="str"/>
     </x:row>
     <x:row r="184">
-      <x:c r="A184" s="24" t="str"/>
+      <x:c r="A184" s="22" t="str"/>
       <x:c r="B184" t="str"/>
       <x:c r="C184" t="str"/>
-      <x:c r="D184" s="24" t="str"/>
+      <x:c r="D184" s="22" t="str"/>
       <x:c r="E184" t="str"/>
       <x:c r="F184" t="str"/>
       <x:c r="G184" t="str"/>
@@ -3122,10 +4752,10 @@
       <x:c r="J184" t="str"/>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" s="24" t="str"/>
+      <x:c r="A185" s="22" t="str"/>
       <x:c r="B185" t="str"/>
       <x:c r="C185" t="str"/>
-      <x:c r="D185" s="24" t="str"/>
+      <x:c r="D185" s="22" t="str"/>
       <x:c r="E185" t="str"/>
       <x:c r="F185" t="str"/>
       <x:c r="G185" t="str"/>
@@ -3134,10 +4764,10 @@
       <x:c r="J185" t="str"/>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" s="24" t="str"/>
+      <x:c r="A186" s="22" t="str"/>
       <x:c r="B186" t="str"/>
       <x:c r="C186" t="str"/>
-      <x:c r="D186" s="24" t="str"/>
+      <x:c r="D186" s="22" t="str"/>
       <x:c r="E186" t="str"/>
       <x:c r="F186" t="str"/>
       <x:c r="G186" t="str"/>
@@ -3146,10 +4776,10 @@
       <x:c r="J186" t="str"/>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" s="24" t="str"/>
+      <x:c r="A187" s="22" t="str"/>
       <x:c r="B187" t="str"/>
       <x:c r="C187" t="str"/>
-      <x:c r="D187" s="24" t="str"/>
+      <x:c r="D187" s="22" t="str"/>
       <x:c r="E187" t="str"/>
       <x:c r="F187" t="str"/>
       <x:c r="G187" t="str"/>
@@ -3158,10 +4788,10 @@
       <x:c r="J187" t="str"/>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" s="24" t="str"/>
+      <x:c r="A188" s="22" t="str"/>
       <x:c r="B188" t="str"/>
       <x:c r="C188" t="str"/>
-      <x:c r="D188" s="24" t="str"/>
+      <x:c r="D188" s="22" t="str"/>
       <x:c r="E188" t="str"/>
       <x:c r="F188" t="str"/>
       <x:c r="G188" t="str"/>
@@ -3170,10 +4800,10 @@
       <x:c r="J188" t="str"/>
     </x:row>
     <x:row r="189">
-      <x:c r="A189" s="24" t="str"/>
+      <x:c r="A189" s="22" t="str"/>
       <x:c r="B189" t="str"/>
       <x:c r="C189" t="str"/>
-      <x:c r="D189" s="24" t="str"/>
+      <x:c r="D189" s="22" t="str"/>
       <x:c r="E189" t="str"/>
       <x:c r="F189" t="str"/>
       <x:c r="G189" t="str"/>
@@ -3182,10 +4812,10 @@
       <x:c r="J189" t="str"/>
     </x:row>
     <x:row r="190">
-      <x:c r="A190" s="24" t="str"/>
+      <x:c r="A190" s="22" t="str"/>
       <x:c r="B190" t="str"/>
       <x:c r="C190" t="str"/>
-      <x:c r="D190" s="24" t="str"/>
+      <x:c r="D190" s="22" t="str"/>
       <x:c r="E190" t="str"/>
       <x:c r="F190" t="str"/>
       <x:c r="G190" t="str"/>
@@ -3194,10 +4824,10 @@
       <x:c r="J190" t="str"/>
     </x:row>
     <x:row r="191">
-      <x:c r="A191" s="24" t="str"/>
+      <x:c r="A191" s="22" t="str"/>
       <x:c r="B191" t="str"/>
       <x:c r="C191" t="str"/>
-      <x:c r="D191" s="24" t="str"/>
+      <x:c r="D191" s="22" t="str"/>
       <x:c r="E191" t="str"/>
       <x:c r="F191" t="str"/>
       <x:c r="G191" t="str"/>
@@ -3206,10 +4836,10 @@
       <x:c r="J191" t="str"/>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" s="24" t="str"/>
+      <x:c r="A192" s="22" t="str"/>
       <x:c r="B192" t="str"/>
       <x:c r="C192" t="str"/>
-      <x:c r="D192" s="24" t="str"/>
+      <x:c r="D192" s="22" t="str"/>
       <x:c r="E192" t="str"/>
       <x:c r="F192" t="str"/>
       <x:c r="G192" t="str"/>
@@ -3218,10 +4848,10 @@
       <x:c r="J192" t="str"/>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" s="24" t="str"/>
+      <x:c r="A193" s="22" t="str"/>
       <x:c r="B193" t="str"/>
       <x:c r="C193" t="str"/>
-      <x:c r="D193" s="24" t="str"/>
+      <x:c r="D193" s="22" t="str"/>
       <x:c r="E193" t="str"/>
       <x:c r="F193" t="str"/>
       <x:c r="G193" t="str"/>
@@ -3230,10 +4860,10 @@
       <x:c r="J193" t="str"/>
     </x:row>
     <x:row r="194">
-      <x:c r="A194" s="24" t="str"/>
+      <x:c r="A194" s="22" t="str"/>
       <x:c r="B194" t="str"/>
       <x:c r="C194" t="str"/>
-      <x:c r="D194" s="24" t="str"/>
+      <x:c r="D194" s="22" t="str"/>
       <x:c r="E194" t="str"/>
       <x:c r="F194" t="str"/>
       <x:c r="G194" t="str"/>
@@ -3242,10 +4872,10 @@
       <x:c r="J194" t="str"/>
     </x:row>
     <x:row r="195">
-      <x:c r="A195" s="24" t="str"/>
+      <x:c r="A195" s="22" t="str"/>
       <x:c r="B195" t="str"/>
       <x:c r="C195" t="str"/>
-      <x:c r="D195" s="24" t="str"/>
+      <x:c r="D195" s="22" t="str"/>
       <x:c r="E195" t="str"/>
       <x:c r="F195" t="str"/>
       <x:c r="G195" t="str"/>
@@ -3254,10 +4884,10 @@
       <x:c r="J195" t="str"/>
     </x:row>
     <x:row r="196">
-      <x:c r="A196" s="24" t="str"/>
+      <x:c r="A196" s="22" t="str"/>
       <x:c r="B196" t="str"/>
       <x:c r="C196" t="str"/>
-      <x:c r="D196" s="24" t="str"/>
+      <x:c r="D196" s="22" t="str"/>
       <x:c r="E196" t="str"/>
       <x:c r="F196" t="str"/>
       <x:c r="G196" t="str"/>
@@ -3266,10 +4896,10 @@
       <x:c r="J196" t="str"/>
     </x:row>
     <x:row r="197">
-      <x:c r="A197" s="24" t="str"/>
+      <x:c r="A197" s="22" t="str"/>
       <x:c r="B197" t="str"/>
       <x:c r="C197" t="str"/>
-      <x:c r="D197" s="24" t="str"/>
+      <x:c r="D197" s="22" t="str"/>
       <x:c r="E197" t="str"/>
       <x:c r="F197" t="str"/>
       <x:c r="G197" t="str"/>
@@ -3278,10 +4908,10 @@
       <x:c r="J197" t="str"/>
     </x:row>
     <x:row r="198">
-      <x:c r="A198" s="24" t="str"/>
+      <x:c r="A198" s="22" t="str"/>
       <x:c r="B198" t="str"/>
       <x:c r="C198" t="str"/>
-      <x:c r="D198" s="24" t="str"/>
+      <x:c r="D198" s="22" t="str"/>
       <x:c r="E198" t="str"/>
       <x:c r="F198" t="str"/>
       <x:c r="G198" t="str"/>
@@ -3290,10 +4920,10 @@
       <x:c r="J198" t="str"/>
     </x:row>
     <x:row r="199">
-      <x:c r="A199" s="24" t="str"/>
+      <x:c r="A199" s="22" t="str"/>
       <x:c r="B199" t="str"/>
       <x:c r="C199" t="str"/>
-      <x:c r="D199" s="24" t="str"/>
+      <x:c r="D199" s="22" t="str"/>
       <x:c r="E199" t="str"/>
       <x:c r="F199" t="str"/>
       <x:c r="G199" t="str"/>
@@ -3302,10 +4932,10 @@
       <x:c r="J199" t="str"/>
     </x:row>
     <x:row r="200">
-      <x:c r="A200" s="24" t="str"/>
+      <x:c r="A200" s="22" t="str"/>
       <x:c r="B200" t="str"/>
       <x:c r="C200" t="str"/>
-      <x:c r="D200" s="24" t="str"/>
+      <x:c r="D200" s="22" t="str"/>
       <x:c r="E200" t="str"/>
       <x:c r="F200" t="str"/>
       <x:c r="G200" t="str"/>
@@ -3314,10 +4944,10 @@
       <x:c r="J200" t="str"/>
     </x:row>
     <x:row r="201">
-      <x:c r="A201" s="24" t="str"/>
+      <x:c r="A201" s="22" t="str"/>
       <x:c r="B201" t="str"/>
       <x:c r="C201" t="str"/>
-      <x:c r="D201" s="24" t="str"/>
+      <x:c r="D201" s="22" t="str"/>
       <x:c r="E201" t="str"/>
       <x:c r="F201" t="str"/>
       <x:c r="G201" t="str"/>
@@ -3326,10 +4956,10 @@
       <x:c r="J201" t="str"/>
     </x:row>
     <x:row r="202">
-      <x:c r="A202" s="24" t="str"/>
+      <x:c r="A202" s="22" t="str"/>
       <x:c r="B202" t="str"/>
       <x:c r="C202" t="str"/>
-      <x:c r="D202" s="24" t="str"/>
+      <x:c r="D202" s="22" t="str"/>
       <x:c r="E202" t="str"/>
       <x:c r="F202" t="str"/>
       <x:c r="G202" t="str"/>
@@ -3338,10 +4968,10 @@
       <x:c r="J202" t="str"/>
     </x:row>
     <x:row r="203">
-      <x:c r="A203" s="24" t="str"/>
+      <x:c r="A203" s="22" t="str"/>
       <x:c r="B203" t="str"/>
       <x:c r="C203" t="str"/>
-      <x:c r="D203" s="24" t="str"/>
+      <x:c r="D203" s="22" t="str"/>
       <x:c r="E203" t="str"/>
       <x:c r="F203" t="str"/>
       <x:c r="G203" t="str"/>
@@ -3350,10 +4980,10 @@
       <x:c r="J203" t="str"/>
     </x:row>
     <x:row r="204">
-      <x:c r="A204" s="24" t="str"/>
+      <x:c r="A204" s="22" t="str"/>
       <x:c r="B204" t="str"/>
       <x:c r="C204" t="str"/>
-      <x:c r="D204" s="24" t="str"/>
+      <x:c r="D204" s="22" t="str"/>
       <x:c r="E204" t="str"/>
       <x:c r="F204" t="str"/>
       <x:c r="G204" t="str"/>
@@ -3362,10 +4992,10 @@
       <x:c r="J204" t="str"/>
     </x:row>
     <x:row r="205">
-      <x:c r="A205" s="24" t="str"/>
+      <x:c r="A205" s="22" t="str"/>
       <x:c r="B205" t="str"/>
       <x:c r="C205" t="str"/>
-      <x:c r="D205" s="24" t="str"/>
+      <x:c r="D205" s="22" t="str"/>
       <x:c r="E205" t="str"/>
       <x:c r="F205" t="str"/>
       <x:c r="G205" t="str"/>
@@ -3374,10 +5004,10 @@
       <x:c r="J205" t="str"/>
     </x:row>
     <x:row r="206">
-      <x:c r="A206" s="24" t="str"/>
+      <x:c r="A206" s="22" t="str"/>
       <x:c r="B206" t="str"/>
       <x:c r="C206" t="str"/>
-      <x:c r="D206" s="24" t="str"/>
+      <x:c r="D206" s="22" t="str"/>
       <x:c r="E206" t="str"/>
       <x:c r="F206" t="str"/>
       <x:c r="G206" t="str"/>
@@ -3386,10 +5016,10 @@
       <x:c r="J206" t="str"/>
     </x:row>
     <x:row r="207">
-      <x:c r="A207" s="24" t="str"/>
+      <x:c r="A207" s="22" t="str"/>
       <x:c r="B207" t="str"/>
       <x:c r="C207" t="str"/>
-      <x:c r="D207" s="24" t="str"/>
+      <x:c r="D207" s="22" t="str"/>
       <x:c r="E207" t="str"/>
       <x:c r="F207" t="str"/>
       <x:c r="G207" t="str"/>
@@ -3398,10 +5028,10 @@
       <x:c r="J207" t="str"/>
     </x:row>
     <x:row r="208">
-      <x:c r="A208" s="24" t="str"/>
+      <x:c r="A208" s="22" t="str"/>
       <x:c r="B208" t="str"/>
       <x:c r="C208" t="str"/>
-      <x:c r="D208" s="24" t="str"/>
+      <x:c r="D208" s="22" t="str"/>
       <x:c r="E208" t="str"/>
       <x:c r="F208" t="str"/>
       <x:c r="G208" t="str"/>
@@ -3410,10 +5040,10 @@
       <x:c r="J208" t="str"/>
     </x:row>
     <x:row r="209">
-      <x:c r="A209" s="24" t="str"/>
+      <x:c r="A209" s="22" t="str"/>
       <x:c r="B209" t="str"/>
       <x:c r="C209" t="str"/>
-      <x:c r="D209" s="24" t="str"/>
+      <x:c r="D209" s="22" t="str"/>
       <x:c r="E209" t="str"/>
       <x:c r="F209" t="str"/>
       <x:c r="G209" t="str"/>
@@ -3422,10 +5052,10 @@
       <x:c r="J209" t="str"/>
     </x:row>
     <x:row r="210">
-      <x:c r="A210" s="24" t="str"/>
+      <x:c r="A210" s="22" t="str"/>
       <x:c r="B210" t="str"/>
       <x:c r="C210" t="str"/>
-      <x:c r="D210" s="24" t="str"/>
+      <x:c r="D210" s="22" t="str"/>
       <x:c r="E210" t="str"/>
       <x:c r="F210" t="str"/>
       <x:c r="G210" t="str"/>
@@ -3434,10 +5064,10 @@
       <x:c r="J210" t="str"/>
     </x:row>
     <x:row r="211">
-      <x:c r="A211" s="24" t="str"/>
+      <x:c r="A211" s="22" t="str"/>
       <x:c r="B211" t="str"/>
       <x:c r="C211" t="str"/>
-      <x:c r="D211" s="24" t="str"/>
+      <x:c r="D211" s="22" t="str"/>
       <x:c r="E211" t="str"/>
       <x:c r="F211" t="str"/>
       <x:c r="G211" t="str"/>
@@ -3446,10 +5076,10 @@
       <x:c r="J211" t="str"/>
     </x:row>
     <x:row r="212">
-      <x:c r="A212" s="24" t="str"/>
+      <x:c r="A212" s="22" t="str"/>
       <x:c r="B212" t="str"/>
       <x:c r="C212" t="str"/>
-      <x:c r="D212" s="24" t="str"/>
+      <x:c r="D212" s="22" t="str"/>
       <x:c r="E212" t="str"/>
       <x:c r="F212" t="str"/>
       <x:c r="G212" t="str"/>
@@ -3458,10 +5088,10 @@
       <x:c r="J212" t="str"/>
     </x:row>
     <x:row r="213">
-      <x:c r="A213" s="24" t="str"/>
+      <x:c r="A213" s="22" t="str"/>
       <x:c r="B213" t="str"/>
       <x:c r="C213" t="str"/>
-      <x:c r="D213" s="24" t="str"/>
+      <x:c r="D213" s="22" t="str"/>
       <x:c r="E213" t="str"/>
       <x:c r="F213" t="str"/>
       <x:c r="G213" t="str"/>
@@ -3470,10 +5100,10 @@
       <x:c r="J213" t="str"/>
     </x:row>
     <x:row r="214">
-      <x:c r="A214" s="24" t="str"/>
+      <x:c r="A214" s="22" t="str"/>
       <x:c r="B214" t="str"/>
       <x:c r="C214" t="str"/>
-      <x:c r="D214" s="24" t="str"/>
+      <x:c r="D214" s="22" t="str"/>
       <x:c r="E214" t="str"/>
       <x:c r="F214" t="str"/>
       <x:c r="G214" t="str"/>
@@ -3482,10 +5112,10 @@
       <x:c r="J214" t="str"/>
     </x:row>
     <x:row r="215">
-      <x:c r="A215" s="24" t="str"/>
+      <x:c r="A215" s="22" t="str"/>
       <x:c r="B215" t="str"/>
       <x:c r="C215" t="str"/>
-      <x:c r="D215" s="24" t="str"/>
+      <x:c r="D215" s="22" t="str"/>
       <x:c r="E215" t="str"/>
       <x:c r="F215" t="str"/>
       <x:c r="G215" t="str"/>
@@ -3494,10 +5124,10 @@
       <x:c r="J215" t="str"/>
     </x:row>
     <x:row r="216">
-      <x:c r="A216" s="24" t="str"/>
+      <x:c r="A216" s="22" t="str"/>
       <x:c r="B216" t="str"/>
       <x:c r="C216" t="str"/>
-      <x:c r="D216" s="24" t="str"/>
+      <x:c r="D216" s="22" t="str"/>
       <x:c r="E216" t="str"/>
       <x:c r="F216" t="str"/>
       <x:c r="G216" t="str"/>
@@ -3506,10 +5136,10 @@
       <x:c r="J216" t="str"/>
     </x:row>
     <x:row r="217">
-      <x:c r="A217" s="24" t="str"/>
+      <x:c r="A217" s="22" t="str"/>
       <x:c r="B217" t="str"/>
       <x:c r="C217" t="str"/>
-      <x:c r="D217" s="24" t="str"/>
+      <x:c r="D217" s="22" t="str"/>
       <x:c r="E217" t="str"/>
       <x:c r="F217" t="str"/>
       <x:c r="G217" t="str"/>
@@ -3518,10 +5148,10 @@
       <x:c r="J217" t="str"/>
     </x:row>
     <x:row r="218">
-      <x:c r="A218" s="24" t="str"/>
+      <x:c r="A218" s="22" t="str"/>
       <x:c r="B218" t="str"/>
       <x:c r="C218" t="str"/>
-      <x:c r="D218" s="24" t="str"/>
+      <x:c r="D218" s="22" t="str"/>
       <x:c r="E218" t="str"/>
       <x:c r="F218" t="str"/>
       <x:c r="G218" t="str"/>
@@ -3530,10 +5160,10 @@
       <x:c r="J218" t="str"/>
     </x:row>
     <x:row r="219">
-      <x:c r="A219" s="24" t="str"/>
+      <x:c r="A219" s="22" t="str"/>
       <x:c r="B219" t="str"/>
       <x:c r="C219" t="str"/>
-      <x:c r="D219" s="24" t="str"/>
+      <x:c r="D219" s="22" t="str"/>
       <x:c r="E219" t="str"/>
       <x:c r="F219" t="str"/>
       <x:c r="G219" t="str"/>
@@ -3542,10 +5172,10 @@
       <x:c r="J219" t="str"/>
     </x:row>
     <x:row r="220">
-      <x:c r="A220" s="24" t="str"/>
+      <x:c r="A220" s="22" t="str"/>
       <x:c r="B220" t="str"/>
       <x:c r="C220" t="str"/>
-      <x:c r="D220" s="24" t="str"/>
+      <x:c r="D220" s="22" t="str"/>
       <x:c r="E220" t="str"/>
       <x:c r="F220" t="str"/>
       <x:c r="G220" t="str"/>
@@ -3554,10 +5184,10 @@
       <x:c r="J220" t="str"/>
     </x:row>
     <x:row r="221">
-      <x:c r="A221" s="24" t="str"/>
+      <x:c r="A221" s="22" t="str"/>
       <x:c r="B221" t="str"/>
       <x:c r="C221" t="str"/>
-      <x:c r="D221" s="24" t="str"/>
+      <x:c r="D221" s="22" t="str"/>
       <x:c r="E221" t="str"/>
       <x:c r="F221" t="str"/>
       <x:c r="G221" t="str"/>
@@ -3566,10 +5196,10 @@
       <x:c r="J221" t="str"/>
     </x:row>
     <x:row r="222">
-      <x:c r="A222" s="24" t="str"/>
+      <x:c r="A222" s="22" t="str"/>
       <x:c r="B222" t="str"/>
       <x:c r="C222" t="str"/>
-      <x:c r="D222" s="24" t="str"/>
+      <x:c r="D222" s="22" t="str"/>
       <x:c r="E222" t="str"/>
       <x:c r="F222" t="str"/>
       <x:c r="G222" t="str"/>
@@ -3578,10 +5208,10 @@
       <x:c r="J222" t="str"/>
     </x:row>
     <x:row r="223">
-      <x:c r="A223" s="24" t="str"/>
+      <x:c r="A223" s="22" t="str"/>
       <x:c r="B223" t="str"/>
       <x:c r="C223" t="str"/>
-      <x:c r="D223" s="24" t="str"/>
+      <x:c r="D223" s="22" t="str"/>
       <x:c r="E223" t="str"/>
       <x:c r="F223" t="str"/>
       <x:c r="G223" t="str"/>
@@ -3590,10 +5220,10 @@
       <x:c r="J223" t="str"/>
     </x:row>
     <x:row r="224">
-      <x:c r="A224" s="24" t="str"/>
+      <x:c r="A224" s="22" t="str"/>
       <x:c r="B224" t="str"/>
       <x:c r="C224" t="str"/>
-      <x:c r="D224" s="24" t="str"/>
+      <x:c r="D224" s="22" t="str"/>
       <x:c r="E224" t="str"/>
       <x:c r="F224" t="str"/>
       <x:c r="G224" t="str"/>
@@ -3602,10 +5232,10 @@
       <x:c r="J224" t="str"/>
     </x:row>
     <x:row r="225">
-      <x:c r="A225" s="24" t="str"/>
+      <x:c r="A225" s="22" t="str"/>
       <x:c r="B225" t="str"/>
       <x:c r="C225" t="str"/>
-      <x:c r="D225" s="24" t="str"/>
+      <x:c r="D225" s="22" t="str"/>
       <x:c r="E225" t="str"/>
       <x:c r="F225" t="str"/>
       <x:c r="G225" t="str"/>
@@ -3614,10 +5244,10 @@
       <x:c r="J225" t="str"/>
     </x:row>
     <x:row r="226">
-      <x:c r="A226" s="24" t="str"/>
+      <x:c r="A226" s="22" t="str"/>
       <x:c r="B226" t="str"/>
       <x:c r="C226" t="str"/>
-      <x:c r="D226" s="24" t="str"/>
+      <x:c r="D226" s="22" t="str"/>
       <x:c r="E226" t="str"/>
       <x:c r="F226" t="str"/>
       <x:c r="G226" t="str"/>
@@ -3626,10 +5256,10 @@
       <x:c r="J226" t="str"/>
     </x:row>
     <x:row r="227">
-      <x:c r="A227" s="24" t="str"/>
+      <x:c r="A227" s="22" t="str"/>
       <x:c r="B227" t="str"/>
       <x:c r="C227" t="str"/>
-      <x:c r="D227" s="24" t="str"/>
+      <x:c r="D227" s="22" t="str"/>
       <x:c r="E227" t="str"/>
       <x:c r="F227" t="str"/>
       <x:c r="G227" t="str"/>
@@ -3638,10 +5268,10 @@
       <x:c r="J227" t="str"/>
     </x:row>
     <x:row r="228">
-      <x:c r="A228" s="24" t="str"/>
+      <x:c r="A228" s="22" t="str"/>
       <x:c r="B228" t="str"/>
       <x:c r="C228" t="str"/>
-      <x:c r="D228" s="24" t="str"/>
+      <x:c r="D228" s="22" t="str"/>
       <x:c r="E228" t="str"/>
       <x:c r="F228" t="str"/>
       <x:c r="G228" t="str"/>
@@ -3650,10 +5280,10 @@
       <x:c r="J228" t="str"/>
     </x:row>
     <x:row r="229">
-      <x:c r="A229" s="24" t="str"/>
+      <x:c r="A229" s="22" t="str"/>
       <x:c r="B229" t="str"/>
       <x:c r="C229" t="str"/>
-      <x:c r="D229" s="24" t="str"/>
+      <x:c r="D229" s="22" t="str"/>
       <x:c r="E229" t="str"/>
       <x:c r="F229" t="str"/>
       <x:c r="G229" t="str"/>
@@ -3662,10 +5292,10 @@
       <x:c r="J229" t="str"/>
     </x:row>
     <x:row r="230">
-      <x:c r="A230" s="24" t="str"/>
+      <x:c r="A230" s="22" t="str"/>
       <x:c r="B230" t="str"/>
       <x:c r="C230" t="str"/>
-      <x:c r="D230" s="24" t="str"/>
+      <x:c r="D230" s="22" t="str"/>
       <x:c r="E230" t="str"/>
       <x:c r="F230" t="str"/>
       <x:c r="G230" t="str"/>
@@ -3674,10 +5304,10 @@
       <x:c r="J230" t="str"/>
     </x:row>
     <x:row r="231">
-      <x:c r="A231" s="24" t="str"/>
+      <x:c r="A231" s="22" t="str"/>
       <x:c r="B231" t="str"/>
       <x:c r="C231" t="str"/>
-      <x:c r="D231" s="24" t="str"/>
+      <x:c r="D231" s="22" t="str"/>
       <x:c r="E231" t="str"/>
       <x:c r="F231" t="str"/>
       <x:c r="G231" t="str"/>
@@ -3686,10 +5316,10 @@
       <x:c r="J231" t="str"/>
     </x:row>
     <x:row r="232">
-      <x:c r="A232" s="24" t="str"/>
+      <x:c r="A232" s="22" t="str"/>
       <x:c r="B232" t="str"/>
       <x:c r="C232" t="str"/>
-      <x:c r="D232" s="24" t="str"/>
+      <x:c r="D232" s="22" t="str"/>
       <x:c r="E232" t="str"/>
       <x:c r="F232" t="str"/>
       <x:c r="G232" t="str"/>
@@ -3698,10 +5328,10 @@
       <x:c r="J232" t="str"/>
     </x:row>
     <x:row r="233">
-      <x:c r="A233" s="24" t="str"/>
+      <x:c r="A233" s="22" t="str"/>
       <x:c r="B233" t="str"/>
       <x:c r="C233" t="str"/>
-      <x:c r="D233" s="24" t="str"/>
+      <x:c r="D233" s="22" t="str"/>
       <x:c r="E233" t="str"/>
       <x:c r="F233" t="str"/>
       <x:c r="G233" t="str"/>
@@ -3710,10 +5340,10 @@
       <x:c r="J233" t="str"/>
     </x:row>
     <x:row r="234">
-      <x:c r="A234" s="24" t="str"/>
+      <x:c r="A234" s="22" t="str"/>
       <x:c r="B234" t="str"/>
       <x:c r="C234" t="str"/>
-      <x:c r="D234" s="24" t="str"/>
+      <x:c r="D234" s="22" t="str"/>
       <x:c r="E234" t="str"/>
       <x:c r="F234" t="str"/>
       <x:c r="G234" t="str"/>
@@ -3722,10 +5352,10 @@
       <x:c r="J234" t="str"/>
     </x:row>
     <x:row r="235">
-      <x:c r="A235" s="24" t="str"/>
+      <x:c r="A235" s="22" t="str"/>
       <x:c r="B235" t="str"/>
       <x:c r="C235" t="str"/>
-      <x:c r="D235" s="24" t="str"/>
+      <x:c r="D235" s="22" t="str"/>
       <x:c r="E235" t="str"/>
       <x:c r="F235" t="str"/>
       <x:c r="G235" t="str"/>
@@ -3734,10 +5364,10 @@
       <x:c r="J235" t="str"/>
     </x:row>
     <x:row r="236">
-      <x:c r="A236" s="24" t="str"/>
+      <x:c r="A236" s="22" t="str"/>
       <x:c r="B236" t="str"/>
       <x:c r="C236" t="str"/>
-      <x:c r="D236" s="24" t="str"/>
+      <x:c r="D236" s="22" t="str"/>
       <x:c r="E236" t="str"/>
       <x:c r="F236" t="str"/>
       <x:c r="G236" t="str"/>
@@ -3746,10 +5376,10 @@
       <x:c r="J236" t="str"/>
     </x:row>
     <x:row r="237">
-      <x:c r="A237" s="24" t="str"/>
+      <x:c r="A237" s="22" t="str"/>
       <x:c r="B237" t="str"/>
       <x:c r="C237" t="str"/>
-      <x:c r="D237" s="24" t="str"/>
+      <x:c r="D237" s="22" t="str"/>
       <x:c r="E237" t="str"/>
       <x:c r="F237" t="str"/>
       <x:c r="G237" t="str"/>
@@ -3758,10 +5388,10 @@
       <x:c r="J237" t="str"/>
     </x:row>
     <x:row r="238">
-      <x:c r="A238" s="24" t="str"/>
+      <x:c r="A238" s="22" t="str"/>
       <x:c r="B238" t="str"/>
       <x:c r="C238" t="str"/>
-      <x:c r="D238" s="24" t="str"/>
+      <x:c r="D238" s="22" t="str"/>
       <x:c r="E238" t="str"/>
       <x:c r="F238" t="str"/>
       <x:c r="G238" t="str"/>
@@ -3770,10 +5400,10 @@
       <x:c r="J238" t="str"/>
     </x:row>
     <x:row r="239">
-      <x:c r="A239" s="24" t="str"/>
+      <x:c r="A239" s="22" t="str"/>
       <x:c r="B239" t="str"/>
       <x:c r="C239" t="str"/>
-      <x:c r="D239" s="24" t="str"/>
+      <x:c r="D239" s="22" t="str"/>
       <x:c r="E239" t="str"/>
       <x:c r="F239" t="str"/>
       <x:c r="G239" t="str"/>
@@ -3782,10 +5412,10 @@
       <x:c r="J239" t="str"/>
     </x:row>
     <x:row r="240">
-      <x:c r="A240" s="24" t="str"/>
+      <x:c r="A240" s="22" t="str"/>
       <x:c r="B240" t="str"/>
       <x:c r="C240" t="str"/>
-      <x:c r="D240" s="24" t="str"/>
+      <x:c r="D240" s="22" t="str"/>
       <x:c r="E240" t="str"/>
       <x:c r="F240" t="str"/>
       <x:c r="G240" t="str"/>
@@ -3794,10 +5424,10 @@
       <x:c r="J240" t="str"/>
     </x:row>
     <x:row r="241">
-      <x:c r="A241" s="24" t="str"/>
+      <x:c r="A241" s="22" t="str"/>
       <x:c r="B241" t="str"/>
       <x:c r="C241" t="str"/>
-      <x:c r="D241" s="24" t="str"/>
+      <x:c r="D241" s="22" t="str"/>
       <x:c r="E241" t="str"/>
       <x:c r="F241" t="str"/>
       <x:c r="G241" t="str"/>
@@ -3806,10 +5436,10 @@
       <x:c r="J241" t="str"/>
     </x:row>
     <x:row r="242">
-      <x:c r="A242" s="24" t="str"/>
+      <x:c r="A242" s="22" t="str"/>
       <x:c r="B242" t="str"/>
       <x:c r="C242" t="str"/>
-      <x:c r="D242" s="24" t="str"/>
+      <x:c r="D242" s="22" t="str"/>
       <x:c r="E242" t="str"/>
       <x:c r="F242" t="str"/>
       <x:c r="G242" t="str"/>
@@ -3818,10 +5448,10 @@
       <x:c r="J242" t="str"/>
     </x:row>
     <x:row r="243">
-      <x:c r="A243" s="24" t="str"/>
+      <x:c r="A243" s="22" t="str"/>
       <x:c r="B243" t="str"/>
       <x:c r="C243" t="str"/>
-      <x:c r="D243" s="24" t="str"/>
+      <x:c r="D243" s="22" t="str"/>
       <x:c r="E243" t="str"/>
       <x:c r="F243" t="str"/>
       <x:c r="G243" t="str"/>
@@ -3830,10 +5460,10 @@
       <x:c r="J243" t="str"/>
     </x:row>
     <x:row r="244">
-      <x:c r="A244" s="24" t="str"/>
+      <x:c r="A244" s="22" t="str"/>
       <x:c r="B244" t="str"/>
       <x:c r="C244" t="str"/>
-      <x:c r="D244" s="24" t="str"/>
+      <x:c r="D244" s="22" t="str"/>
       <x:c r="E244" t="str"/>
       <x:c r="F244" t="str"/>
       <x:c r="G244" t="str"/>
@@ -3842,10 +5472,10 @@
       <x:c r="J244" t="str"/>
     </x:row>
     <x:row r="245">
-      <x:c r="A245" s="24" t="str"/>
+      <x:c r="A245" s="22" t="str"/>
       <x:c r="B245" t="str"/>
       <x:c r="C245" t="str"/>
-      <x:c r="D245" s="24" t="str"/>
+      <x:c r="D245" s="22" t="str"/>
       <x:c r="E245" t="str"/>
       <x:c r="F245" t="str"/>
       <x:c r="G245" t="str"/>
@@ -3854,10 +5484,10 @@
       <x:c r="J245" t="str"/>
     </x:row>
     <x:row r="246">
-      <x:c r="A246" s="24" t="str"/>
+      <x:c r="A246" s="22" t="str"/>
       <x:c r="B246" t="str"/>
       <x:c r="C246" t="str"/>
-      <x:c r="D246" s="24" t="str"/>
+      <x:c r="D246" s="22" t="str"/>
       <x:c r="E246" t="str"/>
       <x:c r="F246" t="str"/>
       <x:c r="G246" t="str"/>
@@ -3866,10 +5496,10 @@
       <x:c r="J246" t="str"/>
     </x:row>
     <x:row r="247">
-      <x:c r="A247" s="24" t="str"/>
+      <x:c r="A247" s="22" t="str"/>
       <x:c r="B247" t="str"/>
       <x:c r="C247" t="str"/>
-      <x:c r="D247" s="24" t="str"/>
+      <x:c r="D247" s="22" t="str"/>
       <x:c r="E247" t="str"/>
       <x:c r="F247" t="str"/>
       <x:c r="G247" t="str"/>
@@ -3878,10 +5508,10 @@
       <x:c r="J247" t="str"/>
     </x:row>
     <x:row r="248">
-      <x:c r="A248" s="24" t="str"/>
+      <x:c r="A248" s="22" t="str"/>
       <x:c r="B248" t="str"/>
       <x:c r="C248" t="str"/>
-      <x:c r="D248" s="24" t="str"/>
+      <x:c r="D248" s="22" t="str"/>
       <x:c r="E248" t="str"/>
       <x:c r="F248" t="str"/>
       <x:c r="G248" t="str"/>
@@ -3890,10 +5520,10 @@
       <x:c r="J248" t="str"/>
     </x:row>
     <x:row r="249">
-      <x:c r="A249" s="24" t="str"/>
+      <x:c r="A249" s="22" t="str"/>
       <x:c r="B249" t="str"/>
       <x:c r="C249" t="str"/>
-      <x:c r="D249" s="24" t="str"/>
+      <x:c r="D249" s="22" t="str"/>
       <x:c r="E249" t="str"/>
       <x:c r="F249" t="str"/>
       <x:c r="G249" t="str"/>
@@ -3902,10 +5532,10 @@
       <x:c r="J249" t="str"/>
     </x:row>
     <x:row r="250">
-      <x:c r="A250" s="24" t="str"/>
+      <x:c r="A250" s="22" t="str"/>
       <x:c r="B250" t="str"/>
       <x:c r="C250" t="str"/>
-      <x:c r="D250" s="24" t="str"/>
+      <x:c r="D250" s="22" t="str"/>
       <x:c r="E250" t="str"/>
       <x:c r="F250" t="str"/>
       <x:c r="G250" t="str"/>
@@ -3914,10 +5544,10 @@
       <x:c r="J250" t="str"/>
     </x:row>
     <x:row r="251">
-      <x:c r="A251" s="24" t="str"/>
+      <x:c r="A251" s="22" t="str"/>
       <x:c r="B251" t="str"/>
       <x:c r="C251" t="str"/>
-      <x:c r="D251" s="24" t="str"/>
+      <x:c r="D251" s="22" t="str"/>
       <x:c r="E251" t="str"/>
       <x:c r="F251" t="str"/>
       <x:c r="G251" t="str"/>
@@ -3926,10 +5556,10 @@
       <x:c r="J251" t="str"/>
     </x:row>
     <x:row r="252">
-      <x:c r="A252" s="24" t="str"/>
+      <x:c r="A252" s="22" t="str"/>
       <x:c r="B252" t="str"/>
       <x:c r="C252" t="str"/>
-      <x:c r="D252" s="24" t="str"/>
+      <x:c r="D252" s="22" t="str"/>
       <x:c r="E252" t="str"/>
       <x:c r="F252" t="str"/>
       <x:c r="G252" t="str"/>
@@ -3938,10 +5568,10 @@
       <x:c r="J252" t="str"/>
     </x:row>
     <x:row r="253">
-      <x:c r="A253" s="24" t="str"/>
+      <x:c r="A253" s="22" t="str"/>
       <x:c r="B253" t="str"/>
       <x:c r="C253" t="str"/>
-      <x:c r="D253" s="24" t="str"/>
+      <x:c r="D253" s="22" t="str"/>
       <x:c r="E253" t="str"/>
       <x:c r="F253" t="str"/>
       <x:c r="G253" t="str"/>
@@ -3950,10 +5580,10 @@
       <x:c r="J253" t="str"/>
     </x:row>
     <x:row r="254">
-      <x:c r="A254" s="24" t="str"/>
+      <x:c r="A254" s="22" t="str"/>
       <x:c r="B254" t="str"/>
       <x:c r="C254" t="str"/>
-      <x:c r="D254" s="24" t="str"/>
+      <x:c r="D254" s="22" t="str"/>
       <x:c r="E254" t="str"/>
       <x:c r="F254" t="str"/>
       <x:c r="G254" t="str"/>
@@ -3962,10 +5592,10 @@
       <x:c r="J254" t="str"/>
     </x:row>
     <x:row r="255">
-      <x:c r="A255" s="24" t="str"/>
+      <x:c r="A255" s="22" t="str"/>
       <x:c r="B255" t="str"/>
       <x:c r="C255" t="str"/>
-      <x:c r="D255" s="24" t="str"/>
+      <x:c r="D255" s="22" t="str"/>
       <x:c r="E255" t="str"/>
       <x:c r="F255" t="str"/>
       <x:c r="G255" t="str"/>
@@ -3974,10 +5604,10 @@
       <x:c r="J255" t="str"/>
     </x:row>
     <x:row r="256">
-      <x:c r="A256" s="24" t="str"/>
+      <x:c r="A256" s="22" t="str"/>
       <x:c r="B256" t="str"/>
       <x:c r="C256" t="str"/>
-      <x:c r="D256" s="24" t="str"/>
+      <x:c r="D256" s="22" t="str"/>
       <x:c r="E256" t="str"/>
       <x:c r="F256" t="str"/>
       <x:c r="G256" t="str"/>
@@ -3986,10 +5616,10 @@
       <x:c r="J256" t="str"/>
     </x:row>
     <x:row r="257">
-      <x:c r="A257" s="24" t="str"/>
+      <x:c r="A257" s="22" t="str"/>
       <x:c r="B257" t="str"/>
       <x:c r="C257" t="str"/>
-      <x:c r="D257" s="24" t="str"/>
+      <x:c r="D257" s="22" t="str"/>
       <x:c r="E257" t="str"/>
       <x:c r="F257" t="str"/>
       <x:c r="G257" t="str"/>
@@ -3998,10 +5628,10 @@
       <x:c r="J257" t="str"/>
     </x:row>
     <x:row r="258">
-      <x:c r="A258" s="24" t="str"/>
+      <x:c r="A258" s="22" t="str"/>
       <x:c r="B258" t="str"/>
       <x:c r="C258" t="str"/>
-      <x:c r="D258" s="24" t="str"/>
+      <x:c r="D258" s="22" t="str"/>
       <x:c r="E258" t="str"/>
       <x:c r="F258" t="str"/>
       <x:c r="G258" t="str"/>
@@ -4010,10 +5640,10 @@
       <x:c r="J258" t="str"/>
     </x:row>
     <x:row r="259">
-      <x:c r="A259" s="24" t="str"/>
+      <x:c r="A259" s="22" t="str"/>
       <x:c r="B259" t="str"/>
       <x:c r="C259" t="str"/>
-      <x:c r="D259" s="24" t="str"/>
+      <x:c r="D259" s="22" t="str"/>
       <x:c r="E259" t="str"/>
       <x:c r="F259" t="str"/>
       <x:c r="G259" t="str"/>
@@ -4022,10 +5652,10 @@
       <x:c r="J259" t="str"/>
     </x:row>
     <x:row r="260">
-      <x:c r="A260" s="24" t="str"/>
+      <x:c r="A260" s="22" t="str"/>
       <x:c r="B260" t="str"/>
       <x:c r="C260" t="str"/>
-      <x:c r="D260" s="24" t="str"/>
+      <x:c r="D260" s="22" t="str"/>
       <x:c r="E260" t="str"/>
       <x:c r="F260" t="str"/>
       <x:c r="G260" t="str"/>
@@ -4034,10 +5664,10 @@
       <x:c r="J260" t="str"/>
     </x:row>
     <x:row r="261">
-      <x:c r="A261" s="24" t="str"/>
+      <x:c r="A261" s="22" t="str"/>
       <x:c r="B261" t="str"/>
       <x:c r="C261" t="str"/>
-      <x:c r="D261" s="24" t="str"/>
+      <x:c r="D261" s="22" t="str"/>
       <x:c r="E261" t="str"/>
       <x:c r="F261" t="str"/>
       <x:c r="G261" t="str"/>
@@ -4046,10 +5676,10 @@
       <x:c r="J261" t="str"/>
     </x:row>
     <x:row r="262">
-      <x:c r="A262" s="24" t="str"/>
+      <x:c r="A262" s="22" t="str"/>
       <x:c r="B262" t="str"/>
       <x:c r="C262" t="str"/>
-      <x:c r="D262" s="24" t="str"/>
+      <x:c r="D262" s="22" t="str"/>
       <x:c r="E262" t="str"/>
       <x:c r="F262" t="str"/>
       <x:c r="G262" t="str"/>
@@ -4058,10 +5688,10 @@
       <x:c r="J262" t="str"/>
     </x:row>
     <x:row r="263">
-      <x:c r="A263" s="24" t="str"/>
+      <x:c r="A263" s="22" t="str"/>
       <x:c r="B263" t="str"/>
       <x:c r="C263" t="str"/>
-      <x:c r="D263" s="24" t="str"/>
+      <x:c r="D263" s="22" t="str"/>
       <x:c r="E263" t="str"/>
       <x:c r="F263" t="str"/>
       <x:c r="G263" t="str"/>
@@ -4070,10 +5700,10 @@
       <x:c r="J263" t="str"/>
     </x:row>
     <x:row r="264">
-      <x:c r="A264" s="24" t="str"/>
+      <x:c r="A264" s="22" t="str"/>
       <x:c r="B264" t="str"/>
       <x:c r="C264" t="str"/>
-      <x:c r="D264" s="24" t="str"/>
+      <x:c r="D264" s="22" t="str"/>
       <x:c r="E264" t="str"/>
       <x:c r="F264" t="str"/>
       <x:c r="G264" t="str"/>
@@ -4082,10 +5712,10 @@
       <x:c r="J264" t="str"/>
     </x:row>
     <x:row r="265">
-      <x:c r="A265" s="24" t="str"/>
+      <x:c r="A265" s="22" t="str"/>
       <x:c r="B265" t="str"/>
       <x:c r="C265" t="str"/>
-      <x:c r="D265" s="24" t="str"/>
+      <x:c r="D265" s="22" t="str"/>
       <x:c r="E265" t="str"/>
       <x:c r="F265" t="str"/>
       <x:c r="G265" t="str"/>
@@ -4094,10 +5724,10 @@
       <x:c r="J265" t="str"/>
     </x:row>
     <x:row r="266">
-      <x:c r="A266" s="24" t="str"/>
+      <x:c r="A266" s="22" t="str"/>
       <x:c r="B266" t="str"/>
       <x:c r="C266" t="str"/>
-      <x:c r="D266" s="24" t="str"/>
+      <x:c r="D266" s="22" t="str"/>
       <x:c r="E266" t="str"/>
       <x:c r="F266" t="str"/>
       <x:c r="G266" t="str"/>
@@ -4106,10 +5736,10 @@
       <x:c r="J266" t="str"/>
     </x:row>
     <x:row r="267">
-      <x:c r="A267" s="24" t="str"/>
+      <x:c r="A267" s="22" t="str"/>
       <x:c r="B267" t="str"/>
       <x:c r="C267" t="str"/>
-      <x:c r="D267" s="24" t="str"/>
+      <x:c r="D267" s="22" t="str"/>
       <x:c r="E267" t="str"/>
       <x:c r="F267" t="str"/>
       <x:c r="G267" t="str"/>
@@ -4118,10 +5748,10 @@
       <x:c r="J267" t="str"/>
     </x:row>
     <x:row r="268">
-      <x:c r="A268" s="24" t="str"/>
+      <x:c r="A268" s="22" t="str"/>
       <x:c r="B268" t="str"/>
       <x:c r="C268" t="str"/>
-      <x:c r="D268" s="24" t="str"/>
+      <x:c r="D268" s="22" t="str"/>
       <x:c r="E268" t="str"/>
       <x:c r="F268" t="str"/>
       <x:c r="G268" t="str"/>
@@ -4130,10 +5760,10 @@
       <x:c r="J268" t="str"/>
     </x:row>
     <x:row r="269">
-      <x:c r="A269" s="24" t="str"/>
+      <x:c r="A269" s="22" t="str"/>
       <x:c r="B269" t="str"/>
       <x:c r="C269" t="str"/>
-      <x:c r="D269" s="24" t="str"/>
+      <x:c r="D269" s="22" t="str"/>
       <x:c r="E269" t="str"/>
       <x:c r="F269" t="str"/>
       <x:c r="G269" t="str"/>
@@ -4142,10 +5772,10 @@
       <x:c r="J269" t="str"/>
     </x:row>
     <x:row r="270">
-      <x:c r="A270" s="24" t="str"/>
+      <x:c r="A270" s="22" t="str"/>
       <x:c r="B270" t="str"/>
       <x:c r="C270" t="str"/>
-      <x:c r="D270" s="24" t="str"/>
+      <x:c r="D270" s="22" t="str"/>
       <x:c r="E270" t="str"/>
       <x:c r="F270" t="str"/>
       <x:c r="G270" t="str"/>
@@ -4154,10 +5784,10 @@
       <x:c r="J270" t="str"/>
     </x:row>
     <x:row r="271">
-      <x:c r="A271" s="24" t="str"/>
+      <x:c r="A271" s="22" t="str"/>
       <x:c r="B271" t="str"/>
       <x:c r="C271" t="str"/>
-      <x:c r="D271" s="24" t="str"/>
+      <x:c r="D271" s="22" t="str"/>
       <x:c r="E271" t="str"/>
       <x:c r="F271" t="str"/>
       <x:c r="G271" t="str"/>
@@ -4166,10 +5796,10 @@
       <x:c r="J271" t="str"/>
     </x:row>
     <x:row r="272">
-      <x:c r="A272" s="24" t="str"/>
+      <x:c r="A272" s="22" t="str"/>
       <x:c r="B272" t="str"/>
       <x:c r="C272" t="str"/>
-      <x:c r="D272" s="24" t="str"/>
+      <x:c r="D272" s="22" t="str"/>
       <x:c r="E272" t="str"/>
       <x:c r="F272" t="str"/>
       <x:c r="G272" t="str"/>
@@ -4178,10 +5808,10 @@
       <x:c r="J272" t="str"/>
     </x:row>
     <x:row r="273">
-      <x:c r="A273" s="24" t="str"/>
+      <x:c r="A273" s="22" t="str"/>
       <x:c r="B273" t="str"/>
       <x:c r="C273" t="str"/>
-      <x:c r="D273" s="24" t="str"/>
+      <x:c r="D273" s="22" t="str"/>
       <x:c r="E273" t="str"/>
       <x:c r="F273" t="str"/>
       <x:c r="G273" t="str"/>
@@ -4190,10 +5820,10 @@
       <x:c r="J273" t="str"/>
     </x:row>
     <x:row r="274">
-      <x:c r="A274" s="24" t="str"/>
+      <x:c r="A274" s="22" t="str"/>
       <x:c r="B274" t="str"/>
       <x:c r="C274" t="str"/>
-      <x:c r="D274" s="24" t="str"/>
+      <x:c r="D274" s="22" t="str"/>
       <x:c r="E274" t="str"/>
       <x:c r="F274" t="str"/>
       <x:c r="G274" t="str"/>
@@ -4202,10 +5832,10 @@
       <x:c r="J274" t="str"/>
     </x:row>
     <x:row r="275">
-      <x:c r="A275" s="24" t="str"/>
+      <x:c r="A275" s="22" t="str"/>
       <x:c r="B275" t="str"/>
       <x:c r="C275" t="str"/>
-      <x:c r="D275" s="24" t="str"/>
+      <x:c r="D275" s="22" t="str"/>
       <x:c r="E275" t="str"/>
       <x:c r="F275" t="str"/>
       <x:c r="G275" t="str"/>
@@ -4214,10 +5844,10 @@
       <x:c r="J275" t="str"/>
     </x:row>
     <x:row r="276">
-      <x:c r="A276" s="24" t="str"/>
+      <x:c r="A276" s="22" t="str"/>
       <x:c r="B276" t="str"/>
       <x:c r="C276" t="str"/>
-      <x:c r="D276" s="24" t="str"/>
+      <x:c r="D276" s="22" t="str"/>
       <x:c r="E276" t="str"/>
       <x:c r="F276" t="str"/>
       <x:c r="G276" t="str"/>
@@ -4226,10 +5856,10 @@
       <x:c r="J276" t="str"/>
     </x:row>
     <x:row r="277">
-      <x:c r="A277" s="24" t="str"/>
+      <x:c r="A277" s="22" t="str"/>
       <x:c r="B277" t="str"/>
       <x:c r="C277" t="str"/>
-      <x:c r="D277" s="24" t="str"/>
+      <x:c r="D277" s="22" t="str"/>
       <x:c r="E277" t="str"/>
       <x:c r="F277" t="str"/>
       <x:c r="G277" t="str"/>
@@ -4238,10 +5868,10 @@
       <x:c r="J277" t="str"/>
     </x:row>
     <x:row r="278">
-      <x:c r="A278" s="24" t="str"/>
+      <x:c r="A278" s="22" t="str"/>
       <x:c r="B278" t="str"/>
       <x:c r="C278" t="str"/>
-      <x:c r="D278" s="24" t="str"/>
+      <x:c r="D278" s="22" t="str"/>
       <x:c r="E278" t="str"/>
       <x:c r="F278" t="str"/>
       <x:c r="G278" t="str"/>
@@ -4250,10 +5880,10 @@
       <x:c r="J278" t="str"/>
     </x:row>
     <x:row r="279">
-      <x:c r="A279" s="24" t="str"/>
+      <x:c r="A279" s="22" t="str"/>
       <x:c r="B279" t="str"/>
       <x:c r="C279" t="str"/>
-      <x:c r="D279" s="24" t="str"/>
+      <x:c r="D279" s="22" t="str"/>
       <x:c r="E279" t="str"/>
       <x:c r="F279" t="str"/>
       <x:c r="G279" t="str"/>
@@ -4262,10 +5892,10 @@
       <x:c r="J279" t="str"/>
     </x:row>
     <x:row r="280">
-      <x:c r="A280" s="24" t="str"/>
+      <x:c r="A280" s="22" t="str"/>
       <x:c r="B280" t="str"/>
       <x:c r="C280" t="str"/>
-      <x:c r="D280" s="24" t="str"/>
+      <x:c r="D280" s="22" t="str"/>
       <x:c r="E280" t="str"/>
       <x:c r="F280" t="str"/>
       <x:c r="G280" t="str"/>
@@ -4274,10 +5904,10 @@
       <x:c r="J280" t="str"/>
     </x:row>
     <x:row r="281">
-      <x:c r="A281" s="24" t="str"/>
+      <x:c r="A281" s="22" t="str"/>
       <x:c r="B281" t="str"/>
       <x:c r="C281" t="str"/>
-      <x:c r="D281" s="24" t="str"/>
+      <x:c r="D281" s="22" t="str"/>
       <x:c r="E281" t="str"/>
       <x:c r="F281" t="str"/>
       <x:c r="G281" t="str"/>
@@ -4286,10 +5916,10 @@
       <x:c r="J281" t="str"/>
     </x:row>
     <x:row r="282">
-      <x:c r="A282" s="24" t="str"/>
+      <x:c r="A282" s="22" t="str"/>
       <x:c r="B282" t="str"/>
       <x:c r="C282" t="str"/>
-      <x:c r="D282" s="24" t="str"/>
+      <x:c r="D282" s="22" t="str"/>
       <x:c r="E282" t="str"/>
       <x:c r="F282" t="str"/>
       <x:c r="G282" t="str"/>
@@ -4298,10 +5928,10 @@
       <x:c r="J282" t="str"/>
     </x:row>
     <x:row r="283">
-      <x:c r="A283" s="24" t="str"/>
+      <x:c r="A283" s="22" t="str"/>
       <x:c r="B283" t="str"/>
       <x:c r="C283" t="str"/>
-      <x:c r="D283" s="24" t="str"/>
+      <x:c r="D283" s="22" t="str"/>
       <x:c r="E283" t="str"/>
       <x:c r="F283" t="str"/>
       <x:c r="G283" t="str"/>
@@ -4310,10 +5940,10 @@
       <x:c r="J283" t="str"/>
     </x:row>
     <x:row r="284">
-      <x:c r="A284" s="24" t="str"/>
+      <x:c r="A284" s="22" t="str"/>
       <x:c r="B284" t="str"/>
       <x:c r="C284" t="str"/>
-      <x:c r="D284" s="24" t="str"/>
+      <x:c r="D284" s="22" t="str"/>
       <x:c r="E284" t="str"/>
       <x:c r="F284" t="str"/>
       <x:c r="G284" t="str"/>
@@ -4322,10 +5952,10 @@
       <x:c r="J284" t="str"/>
     </x:row>
     <x:row r="285">
-      <x:c r="A285" s="24" t="str"/>
+      <x:c r="A285" s="22" t="str"/>
       <x:c r="B285" t="str"/>
       <x:c r="C285" t="str"/>
-      <x:c r="D285" s="24" t="str"/>
+      <x:c r="D285" s="22" t="str"/>
       <x:c r="E285" t="str"/>
       <x:c r="F285" t="str"/>
       <x:c r="G285" t="str"/>
@@ -4334,10 +5964,10 @@
       <x:c r="J285" t="str"/>
     </x:row>
     <x:row r="286">
-      <x:c r="A286" s="24" t="str"/>
+      <x:c r="A286" s="22" t="str"/>
       <x:c r="B286" t="str"/>
       <x:c r="C286" t="str"/>
-      <x:c r="D286" s="24" t="str"/>
+      <x:c r="D286" s="22" t="str"/>
       <x:c r="E286" t="str"/>
       <x:c r="F286" t="str"/>
       <x:c r="G286" t="str"/>
@@ -4346,10 +5976,10 @@
       <x:c r="J286" t="str"/>
     </x:row>
     <x:row r="287">
-      <x:c r="A287" s="24" t="str"/>
+      <x:c r="A287" s="22" t="str"/>
       <x:c r="B287" t="str"/>
       <x:c r="C287" t="str"/>
-      <x:c r="D287" s="24" t="str"/>
+      <x:c r="D287" s="22" t="str"/>
       <x:c r="E287" t="str"/>
       <x:c r="F287" t="str"/>
       <x:c r="G287" t="str"/>
@@ -4358,10 +5988,10 @@
       <x:c r="J287" t="str"/>
     </x:row>
     <x:row r="288">
-      <x:c r="A288" s="24" t="str"/>
+      <x:c r="A288" s="22" t="str"/>
       <x:c r="B288" t="str"/>
       <x:c r="C288" t="str"/>
-      <x:c r="D288" s="24" t="str"/>
+      <x:c r="D288" s="22" t="str"/>
       <x:c r="E288" t="str"/>
       <x:c r="F288" t="str"/>
       <x:c r="G288" t="str"/>
@@ -4370,10 +6000,10 @@
       <x:c r="J288" t="str"/>
     </x:row>
     <x:row r="289">
-      <x:c r="A289" s="24" t="str"/>
+      <x:c r="A289" s="22" t="str"/>
       <x:c r="B289" t="str"/>
       <x:c r="C289" t="str"/>
-      <x:c r="D289" s="24" t="str"/>
+      <x:c r="D289" s="22" t="str"/>
       <x:c r="E289" t="str"/>
       <x:c r="F289" t="str"/>
       <x:c r="G289" t="str"/>
@@ -4382,10 +6012,10 @@
       <x:c r="J289" t="str"/>
     </x:row>
     <x:row r="290">
-      <x:c r="A290" s="24" t="str"/>
+      <x:c r="A290" s="22" t="str"/>
       <x:c r="B290" t="str"/>
       <x:c r="C290" t="str"/>
-      <x:c r="D290" s="24" t="str"/>
+      <x:c r="D290" s="22" t="str"/>
       <x:c r="E290" t="str"/>
       <x:c r="F290" t="str"/>
       <x:c r="G290" t="str"/>
@@ -4394,10 +6024,10 @@
       <x:c r="J290" t="str"/>
     </x:row>
     <x:row r="291">
-      <x:c r="A291" s="24" t="str"/>
+      <x:c r="A291" s="22" t="str"/>
       <x:c r="B291" t="str"/>
       <x:c r="C291" t="str"/>
-      <x:c r="D291" s="24" t="str"/>
+      <x:c r="D291" s="22" t="str"/>
       <x:c r="E291" t="str"/>
       <x:c r="F291" t="str"/>
       <x:c r="G291" t="str"/>
@@ -4406,10 +6036,10 @@
       <x:c r="J291" t="str"/>
     </x:row>
     <x:row r="292">
-      <x:c r="A292" s="24" t="str"/>
+      <x:c r="A292" s="22" t="str"/>
       <x:c r="B292" t="str"/>
       <x:c r="C292" t="str"/>
-      <x:c r="D292" s="24" t="str"/>
+      <x:c r="D292" s="22" t="str"/>
       <x:c r="E292" t="str"/>
       <x:c r="F292" t="str"/>
       <x:c r="G292" t="str"/>
@@ -4418,10 +6048,10 @@
       <x:c r="J292" t="str"/>
     </x:row>
     <x:row r="293">
-      <x:c r="A293" s="24" t="str"/>
+      <x:c r="A293" s="22" t="str"/>
       <x:c r="B293" t="str"/>
       <x:c r="C293" t="str"/>
-      <x:c r="D293" s="24" t="str"/>
+      <x:c r="D293" s="22" t="str"/>
       <x:c r="E293" t="str"/>
       <x:c r="F293" t="str"/>
       <x:c r="G293" t="str"/>
@@ -4430,10 +6060,10 @@
       <x:c r="J293" t="str"/>
     </x:row>
     <x:row r="294">
-      <x:c r="A294" s="24" t="str"/>
+      <x:c r="A294" s="22" t="str"/>
       <x:c r="B294" t="str"/>
       <x:c r="C294" t="str"/>
-      <x:c r="D294" s="24" t="str"/>
+      <x:c r="D294" s="22" t="str"/>
       <x:c r="E294" t="str"/>
       <x:c r="F294" t="str"/>
       <x:c r="G294" t="str"/>
@@ -4442,10 +6072,10 @@
       <x:c r="J294" t="str"/>
     </x:row>
     <x:row r="295">
-      <x:c r="A295" s="24" t="str"/>
+      <x:c r="A295" s="22" t="str"/>
       <x:c r="B295" t="str"/>
       <x:c r="C295" t="str"/>
-      <x:c r="D295" s="24" t="str"/>
+      <x:c r="D295" s="22" t="str"/>
       <x:c r="E295" t="str"/>
       <x:c r="F295" t="str"/>
       <x:c r="G295" t="str"/>
@@ -4454,10 +6084,10 @@
       <x:c r="J295" t="str"/>
     </x:row>
     <x:row r="296">
-      <x:c r="A296" s="24" t="str"/>
+      <x:c r="A296" s="22" t="str"/>
       <x:c r="B296" t="str"/>
       <x:c r="C296" t="str"/>
-      <x:c r="D296" s="24" t="str"/>
+      <x:c r="D296" s="22" t="str"/>
       <x:c r="E296" t="str"/>
       <x:c r="F296" t="str"/>
       <x:c r="G296" t="str"/>
@@ -4466,10 +6096,10 @@
       <x:c r="J296" t="str"/>
     </x:row>
     <x:row r="297">
-      <x:c r="A297" s="24" t="str"/>
+      <x:c r="A297" s="22" t="str"/>
       <x:c r="B297" t="str"/>
       <x:c r="C297" t="str"/>
-      <x:c r="D297" s="24" t="str"/>
+      <x:c r="D297" s="22" t="str"/>
       <x:c r="E297" t="str"/>
       <x:c r="F297" t="str"/>
       <x:c r="G297" t="str"/>
@@ -4478,10 +6108,10 @@
       <x:c r="J297" t="str"/>
     </x:row>
     <x:row r="298">
-      <x:c r="A298" s="24" t="str"/>
+      <x:c r="A298" s="22" t="str"/>
       <x:c r="B298" t="str"/>
       <x:c r="C298" t="str"/>
-      <x:c r="D298" s="24" t="str"/>
+      <x:c r="D298" s="22" t="str"/>
       <x:c r="E298" t="str"/>
       <x:c r="F298" t="str"/>
       <x:c r="G298" t="str"/>
@@ -4490,10 +6120,10 @@
       <x:c r="J298" t="str"/>
     </x:row>
     <x:row r="299">
-      <x:c r="A299" s="24" t="str"/>
+      <x:c r="A299" s="22" t="str"/>
       <x:c r="B299" t="str"/>
       <x:c r="C299" t="str"/>
-      <x:c r="D299" s="24" t="str"/>
+      <x:c r="D299" s="22" t="str"/>
       <x:c r="E299" t="str"/>
       <x:c r="F299" t="str"/>
       <x:c r="G299" t="str"/>
@@ -4502,10 +6132,10 @@
       <x:c r="J299" t="str"/>
     </x:row>
     <x:row r="300">
-      <x:c r="A300" s="24" t="str"/>
+      <x:c r="A300" s="22" t="str"/>
       <x:c r="B300" t="str"/>
       <x:c r="C300" t="str"/>
-      <x:c r="D300" s="24" t="str"/>
+      <x:c r="D300" s="22" t="str"/>
       <x:c r="E300" t="str"/>
       <x:c r="F300" t="str"/>
       <x:c r="G300" t="str"/>
@@ -4514,10 +6144,10 @@
       <x:c r="J300" t="str"/>
     </x:row>
     <x:row r="301">
-      <x:c r="A301" s="24" t="str"/>
+      <x:c r="A301" s="22" t="str"/>
       <x:c r="B301" t="str"/>
       <x:c r="C301" t="str"/>
-      <x:c r="D301" s="24" t="str"/>
+      <x:c r="D301" s="22" t="str"/>
       <x:c r="E301" t="str"/>
       <x:c r="F301" t="str"/>
       <x:c r="G301" t="str"/>
@@ -4526,10 +6156,10 @@
       <x:c r="J301" t="str"/>
     </x:row>
     <x:row r="302">
-      <x:c r="A302" s="24" t="str"/>
+      <x:c r="A302" s="22" t="str"/>
       <x:c r="B302" t="str"/>
       <x:c r="C302" t="str"/>
-      <x:c r="D302" s="24" t="str"/>
+      <x:c r="D302" s="22" t="str"/>
       <x:c r="E302" t="str"/>
       <x:c r="F302" t="str"/>
       <x:c r="G302" t="str"/>
@@ -4538,10 +6168,10 @@
       <x:c r="J302" t="str"/>
     </x:row>
     <x:row r="303">
-      <x:c r="A303" s="24" t="str"/>
+      <x:c r="A303" s="22" t="str"/>
       <x:c r="B303" t="str"/>
       <x:c r="C303" t="str"/>
-      <x:c r="D303" s="24" t="str"/>
+      <x:c r="D303" s="22" t="str"/>
       <x:c r="E303" t="str"/>
       <x:c r="F303" t="str"/>
       <x:c r="G303" t="str"/>
@@ -4550,10 +6180,10 @@
       <x:c r="J303" t="str"/>
     </x:row>
     <x:row r="304">
-      <x:c r="A304" s="24" t="str"/>
+      <x:c r="A304" s="22" t="str"/>
       <x:c r="B304" t="str"/>
       <x:c r="C304" t="str"/>
-      <x:c r="D304" s="24" t="str"/>
+      <x:c r="D304" s="22" t="str"/>
       <x:c r="E304" t="str"/>
       <x:c r="F304" t="str"/>
       <x:c r="G304" t="str"/>
@@ -4562,10 +6192,10 @@
       <x:c r="J304" t="str"/>
     </x:row>
     <x:row r="305">
-      <x:c r="A305" s="24" t="str"/>
+      <x:c r="A305" s="22" t="str"/>
       <x:c r="B305" t="str"/>
       <x:c r="C305" t="str"/>
-      <x:c r="D305" s="24" t="str"/>
+      <x:c r="D305" s="22" t="str"/>
       <x:c r="E305" t="str"/>
       <x:c r="F305" t="str"/>
       <x:c r="G305" t="str"/>
@@ -4574,10 +6204,10 @@
       <x:c r="J305" t="str"/>
     </x:row>
     <x:row r="306">
-      <x:c r="A306" s="24" t="str"/>
+      <x:c r="A306" s="22" t="str"/>
       <x:c r="B306" t="str"/>
       <x:c r="C306" t="str"/>
-      <x:c r="D306" s="24" t="str"/>
+      <x:c r="D306" s="22" t="str"/>
       <x:c r="E306" t="str"/>
       <x:c r="F306" t="str"/>
       <x:c r="G306" t="str"/>
@@ -4586,10 +6216,10 @@
       <x:c r="J306" t="str"/>
     </x:row>
     <x:row r="307">
-      <x:c r="A307" s="24" t="str"/>
+      <x:c r="A307" s="22" t="str"/>
       <x:c r="B307" t="str"/>
       <x:c r="C307" t="str"/>
-      <x:c r="D307" s="24" t="str"/>
+      <x:c r="D307" s="22" t="str"/>
       <x:c r="E307" t="str"/>
       <x:c r="F307" t="str"/>
       <x:c r="G307" t="str"/>
@@ -4598,10 +6228,10 @@
       <x:c r="J307" t="str"/>
     </x:row>
     <x:row r="308">
-      <x:c r="A308" s="24" t="str"/>
+      <x:c r="A308" s="22" t="str"/>
       <x:c r="B308" t="str"/>
       <x:c r="C308" t="str"/>
-      <x:c r="D308" s="24" t="str"/>
+      <x:c r="D308" s="22" t="str"/>
       <x:c r="E308" t="str"/>
       <x:c r="F308" t="str"/>
       <x:c r="G308" t="str"/>
@@ -4610,10 +6240,10 @@
       <x:c r="J308" t="str"/>
     </x:row>
     <x:row r="309">
-      <x:c r="A309" s="24" t="str"/>
+      <x:c r="A309" s="22" t="str"/>
       <x:c r="B309" t="str"/>
       <x:c r="C309" t="str"/>
-      <x:c r="D309" s="24" t="str"/>
+      <x:c r="D309" s="22" t="str"/>
       <x:c r="E309" t="str"/>
       <x:c r="F309" t="str"/>
       <x:c r="G309" t="str"/>
@@ -4622,10 +6252,10 @@
       <x:c r="J309" t="str"/>
     </x:row>
     <x:row r="310">
-      <x:c r="A310" s="24" t="str"/>
+      <x:c r="A310" s="22" t="str"/>
       <x:c r="B310" t="str"/>
       <x:c r="C310" t="str"/>
-      <x:c r="D310" s="24" t="str"/>
+      <x:c r="D310" s="22" t="str"/>
       <x:c r="E310" t="str"/>
       <x:c r="F310" t="str"/>
       <x:c r="G310" t="str"/>
@@ -4634,10 +6264,10 @@
       <x:c r="J310" t="str"/>
     </x:row>
     <x:row r="311">
-      <x:c r="A311" s="24" t="str"/>
+      <x:c r="A311" s="22" t="str"/>
       <x:c r="B311" t="str"/>
       <x:c r="C311" t="str"/>
-      <x:c r="D311" s="24" t="str"/>
+      <x:c r="D311" s="22" t="str"/>
       <x:c r="E311" t="str"/>
       <x:c r="F311" t="str"/>
       <x:c r="G311" t="str"/>
@@ -4646,10 +6276,10 @@
       <x:c r="J311" t="str"/>
     </x:row>
     <x:row r="312">
-      <x:c r="A312" s="24" t="str"/>
+      <x:c r="A312" s="22" t="str"/>
       <x:c r="B312" t="str"/>
       <x:c r="C312" t="str"/>
-      <x:c r="D312" s="24" t="str"/>
+      <x:c r="D312" s="22" t="str"/>
       <x:c r="E312" t="str"/>
       <x:c r="F312" t="str"/>
       <x:c r="G312" t="str"/>
@@ -4658,10 +6288,10 @@
       <x:c r="J312" t="str"/>
     </x:row>
     <x:row r="313">
-      <x:c r="A313" s="24" t="str"/>
+      <x:c r="A313" s="22" t="str"/>
       <x:c r="B313" t="str"/>
       <x:c r="C313" t="str"/>
-      <x:c r="D313" s="24" t="str"/>
+      <x:c r="D313" s="22" t="str"/>
       <x:c r="E313" t="str"/>
       <x:c r="F313" t="str"/>
       <x:c r="G313" t="str"/>
@@ -4670,10 +6300,10 @@
       <x:c r="J313" t="str"/>
     </x:row>
     <x:row r="314">
-      <x:c r="A314" s="24" t="str"/>
+      <x:c r="A314" s="22" t="str"/>
       <x:c r="B314" t="str"/>
       <x:c r="C314" t="str"/>
-      <x:c r="D314" s="24" t="str"/>
+      <x:c r="D314" s="22" t="str"/>
       <x:c r="E314" t="str"/>
       <x:c r="F314" t="str"/>
       <x:c r="G314" t="str"/>
@@ -4682,10 +6312,10 @@
       <x:c r="J314" t="str"/>
     </x:row>
     <x:row r="315">
-      <x:c r="A315" s="24" t="str"/>
+      <x:c r="A315" s="22" t="str"/>
       <x:c r="B315" t="str"/>
       <x:c r="C315" t="str"/>
-      <x:c r="D315" s="24" t="str"/>
+      <x:c r="D315" s="22" t="str"/>
       <x:c r="E315" t="str"/>
       <x:c r="F315" t="str"/>
       <x:c r="G315" t="str"/>
@@ -4694,10 +6324,10 @@
       <x:c r="J315" t="str"/>
     </x:row>
     <x:row r="316">
-      <x:c r="A316" s="24" t="str"/>
+      <x:c r="A316" s="22" t="str"/>
       <x:c r="B316" t="str"/>
       <x:c r="C316" t="str"/>
-      <x:c r="D316" s="24" t="str"/>
+      <x:c r="D316" s="22" t="str"/>
       <x:c r="E316" t="str"/>
       <x:c r="F316" t="str"/>
       <x:c r="G316" t="str"/>
@@ -4706,10 +6336,10 @@
       <x:c r="J316" t="str"/>
     </x:row>
     <x:row r="317">
-      <x:c r="A317" s="24" t="str"/>
+      <x:c r="A317" s="22" t="str"/>
       <x:c r="B317" t="str"/>
       <x:c r="C317" t="str"/>
-      <x:c r="D317" s="24" t="str"/>
+      <x:c r="D317" s="22" t="str"/>
       <x:c r="E317" t="str"/>
       <x:c r="F317" t="str"/>
       <x:c r="G317" t="str"/>
@@ -4718,10 +6348,10 @@
       <x:c r="J317" t="str"/>
     </x:row>
     <x:row r="318">
-      <x:c r="A318" s="24" t="str"/>
+      <x:c r="A318" s="22" t="str"/>
       <x:c r="B318" t="str"/>
       <x:c r="C318" t="str"/>
-      <x:c r="D318" s="24" t="str"/>
+      <x:c r="D318" s="22" t="str"/>
       <x:c r="E318" t="str"/>
       <x:c r="F318" t="str"/>
       <x:c r="G318" t="str"/>
@@ -4730,10 +6360,10 @@
       <x:c r="J318" t="str"/>
     </x:row>
     <x:row r="319">
-      <x:c r="A319" s="24" t="str"/>
+      <x:c r="A319" s="22" t="str"/>
       <x:c r="B319" t="str"/>
       <x:c r="C319" t="str"/>
-      <x:c r="D319" s="24" t="str"/>
+      <x:c r="D319" s="22" t="str"/>
       <x:c r="E319" t="str"/>
       <x:c r="F319" t="str"/>
       <x:c r="G319" t="str"/>
@@ -4742,10 +6372,10 @@
       <x:c r="J319" t="str"/>
     </x:row>
     <x:row r="320">
-      <x:c r="A320" s="24" t="str"/>
+      <x:c r="A320" s="22" t="str"/>
       <x:c r="B320" t="str"/>
       <x:c r="C320" t="str"/>
-      <x:c r="D320" s="24" t="str"/>
+      <x:c r="D320" s="22" t="str"/>
       <x:c r="E320" t="str"/>
       <x:c r="F320" t="str"/>
       <x:c r="G320" t="str"/>
@@ -4754,10 +6384,10 @@
       <x:c r="J320" t="str"/>
     </x:row>
     <x:row r="321">
-      <x:c r="A321" s="24" t="str"/>
+      <x:c r="A321" s="22" t="str"/>
       <x:c r="B321" t="str"/>
       <x:c r="C321" t="str"/>
-      <x:c r="D321" s="24" t="str"/>
+      <x:c r="D321" s="22" t="str"/>
       <x:c r="E321" t="str"/>
       <x:c r="F321" t="str"/>
       <x:c r="G321" t="str"/>
@@ -4766,10 +6396,10 @@
       <x:c r="J321" t="str"/>
     </x:row>
     <x:row r="322">
-      <x:c r="A322" s="24" t="str"/>
+      <x:c r="A322" s="22" t="str"/>
       <x:c r="B322" t="str"/>
       <x:c r="C322" t="str"/>
-      <x:c r="D322" s="24" t="str"/>
+      <x:c r="D322" s="22" t="str"/>
       <x:c r="E322" t="str"/>
       <x:c r="F322" t="str"/>
       <x:c r="G322" t="str"/>
@@ -4778,10 +6408,10 @@
       <x:c r="J322" t="str"/>
     </x:row>
     <x:row r="323">
-      <x:c r="A323" s="24" t="str"/>
+      <x:c r="A323" s="22" t="str"/>
       <x:c r="B323" t="str"/>
       <x:c r="C323" t="str"/>
-      <x:c r="D323" s="24" t="str"/>
+      <x:c r="D323" s="22" t="str"/>
       <x:c r="E323" t="str"/>
       <x:c r="F323" t="str"/>
       <x:c r="G323" t="str"/>
@@ -4790,10 +6420,10 @@
       <x:c r="J323" t="str"/>
     </x:row>
     <x:row r="324">
-      <x:c r="A324" s="24" t="str"/>
+      <x:c r="A324" s="22" t="str"/>
       <x:c r="B324" t="str"/>
       <x:c r="C324" t="str"/>
-      <x:c r="D324" s="24" t="str"/>
+      <x:c r="D324" s="22" t="str"/>
       <x:c r="E324" t="str"/>
       <x:c r="F324" t="str"/>
       <x:c r="G324" t="str"/>
@@ -4802,10 +6432,10 @@
       <x:c r="J324" t="str"/>
     </x:row>
     <x:row r="325">
-      <x:c r="A325" s="24" t="str"/>
+      <x:c r="A325" s="22" t="str"/>
       <x:c r="B325" t="str"/>
       <x:c r="C325" t="str"/>
-      <x:c r="D325" s="24" t="str"/>
+      <x:c r="D325" s="22" t="str"/>
       <x:c r="E325" t="str"/>
       <x:c r="F325" t="str"/>
       <x:c r="G325" t="str"/>
@@ -4814,10 +6444,10 @@
       <x:c r="J325" t="str"/>
     </x:row>
     <x:row r="326">
-      <x:c r="A326" s="24" t="str"/>
+      <x:c r="A326" s="22" t="str"/>
       <x:c r="B326" t="str"/>
       <x:c r="C326" t="str"/>
-      <x:c r="D326" s="24" t="str"/>
+      <x:c r="D326" s="22" t="str"/>
       <x:c r="E326" t="str"/>
       <x:c r="F326" t="str"/>
       <x:c r="G326" t="str"/>
@@ -4826,10 +6456,10 @@
       <x:c r="J326" t="str"/>
     </x:row>
     <x:row r="327">
-      <x:c r="A327" s="24" t="str"/>
+      <x:c r="A327" s="22" t="str"/>
       <x:c r="B327" t="str"/>
       <x:c r="C327" t="str"/>
-      <x:c r="D327" s="24" t="str"/>
+      <x:c r="D327" s="22" t="str"/>
       <x:c r="E327" t="str"/>
       <x:c r="F327" t="str"/>
       <x:c r="G327" t="str"/>
@@ -4838,10 +6468,10 @@
       <x:c r="J327" t="str"/>
     </x:row>
     <x:row r="328">
-      <x:c r="A328" s="24" t="str"/>
+      <x:c r="A328" s="22" t="str"/>
       <x:c r="B328" t="str"/>
       <x:c r="C328" t="str"/>
-      <x:c r="D328" s="24" t="str"/>
+      <x:c r="D328" s="22" t="str"/>
       <x:c r="E328" t="str"/>
       <x:c r="F328" t="str"/>
       <x:c r="G328" t="str"/>
@@ -4850,10 +6480,10 @@
       <x:c r="J328" t="str"/>
     </x:row>
     <x:row r="329">
-      <x:c r="A329" s="24" t="str"/>
+      <x:c r="A329" s="22" t="str"/>
       <x:c r="B329" t="str"/>
       <x:c r="C329" t="str"/>
-      <x:c r="D329" s="24" t="str"/>
+      <x:c r="D329" s="22" t="str"/>
       <x:c r="E329" t="str"/>
       <x:c r="F329" t="str"/>
       <x:c r="G329" t="str"/>
@@ -4862,10 +6492,10 @@
       <x:c r="J329" t="str"/>
     </x:row>
     <x:row r="330">
-      <x:c r="A330" s="24" t="str"/>
+      <x:c r="A330" s="22" t="str"/>
       <x:c r="B330" t="str"/>
       <x:c r="C330" t="str"/>
-      <x:c r="D330" s="24" t="str"/>
+      <x:c r="D330" s="22" t="str"/>
       <x:c r="E330" t="str"/>
       <x:c r="F330" t="str"/>
       <x:c r="G330" t="str"/>
@@ -4874,10 +6504,10 @@
       <x:c r="J330" t="str"/>
     </x:row>
     <x:row r="331">
-      <x:c r="A331" s="24" t="str"/>
+      <x:c r="A331" s="22" t="str"/>
       <x:c r="B331" t="str"/>
       <x:c r="C331" t="str"/>
-      <x:c r="D331" s="24" t="str"/>
+      <x:c r="D331" s="22" t="str"/>
       <x:c r="E331" t="str"/>
       <x:c r="F331" t="str"/>
       <x:c r="G331" t="str"/>
@@ -4886,10 +6516,10 @@
       <x:c r="J331" t="str"/>
     </x:row>
     <x:row r="332">
-      <x:c r="A332" s="24" t="str"/>
+      <x:c r="A332" s="22" t="str"/>
       <x:c r="B332" t="str"/>
       <x:c r="C332" t="str"/>
-      <x:c r="D332" s="24" t="str"/>
+      <x:c r="D332" s="22" t="str"/>
       <x:c r="E332" t="str"/>
       <x:c r="F332" t="str"/>
       <x:c r="G332" t="str"/>
@@ -4898,10 +6528,10 @@
       <x:c r="J332" t="str"/>
     </x:row>
     <x:row r="333">
-      <x:c r="A333" s="24" t="str"/>
+      <x:c r="A333" s="22" t="str"/>
       <x:c r="B333" t="str"/>
       <x:c r="C333" t="str"/>
-      <x:c r="D333" s="24" t="str"/>
+      <x:c r="D333" s="22" t="str"/>
       <x:c r="E333" t="str"/>
       <x:c r="F333" t="str"/>
       <x:c r="G333" t="str"/>
@@ -4910,10 +6540,10 @@
       <x:c r="J333" t="str"/>
     </x:row>
     <x:row r="334">
-      <x:c r="A334" s="24" t="str"/>
+      <x:c r="A334" s="22" t="str"/>
       <x:c r="B334" t="str"/>
       <x:c r="C334" t="str"/>
-      <x:c r="D334" s="24" t="str"/>
+      <x:c r="D334" s="22" t="str"/>
       <x:c r="E334" t="str"/>
       <x:c r="F334" t="str"/>
       <x:c r="G334" t="str"/>
@@ -4922,10 +6552,10 @@
       <x:c r="J334" t="str"/>
     </x:row>
     <x:row r="335">
-      <x:c r="A335" s="24" t="str"/>
+      <x:c r="A335" s="22" t="str"/>
       <x:c r="B335" t="str"/>
       <x:c r="C335" t="str"/>
-      <x:c r="D335" s="24" t="str"/>
+      <x:c r="D335" s="22" t="str"/>
       <x:c r="E335" t="str"/>
       <x:c r="F335" t="str"/>
       <x:c r="G335" t="str"/>
@@ -4934,10 +6564,10 @@
       <x:c r="J335" t="str"/>
     </x:row>
     <x:row r="336">
-      <x:c r="A336" s="24" t="str"/>
+      <x:c r="A336" s="22" t="str"/>
       <x:c r="B336" t="str"/>
       <x:c r="C336" t="str"/>
-      <x:c r="D336" s="24" t="str"/>
+      <x:c r="D336" s="22" t="str"/>
       <x:c r="E336" t="str"/>
       <x:c r="F336" t="str"/>
       <x:c r="G336" t="str"/>
@@ -4946,10 +6576,10 @@
       <x:c r="J336" t="str"/>
     </x:row>
     <x:row r="337">
-      <x:c r="A337" s="24" t="str"/>
+      <x:c r="A337" s="22" t="str"/>
       <x:c r="B337" t="str"/>
       <x:c r="C337" t="str"/>
-      <x:c r="D337" s="24" t="str"/>
+      <x:c r="D337" s="22" t="str"/>
       <x:c r="E337" t="str"/>
       <x:c r="F337" t="str"/>
       <x:c r="G337" t="str"/>
@@ -4958,10 +6588,10 @@
       <x:c r="J337" t="str"/>
     </x:row>
     <x:row r="338">
-      <x:c r="A338" s="24" t="str"/>
+      <x:c r="A338" s="22" t="str"/>
       <x:c r="B338" t="str"/>
       <x:c r="C338" t="str"/>
-      <x:c r="D338" s="24" t="str"/>
+      <x:c r="D338" s="22" t="str"/>
       <x:c r="E338" t="str"/>
       <x:c r="F338" t="str"/>
       <x:c r="G338" t="str"/>
@@ -4970,10 +6600,10 @@
       <x:c r="J338" t="str"/>
     </x:row>
     <x:row r="339">
-      <x:c r="A339" s="24" t="str"/>
+      <x:c r="A339" s="22" t="str"/>
       <x:c r="B339" t="str"/>
       <x:c r="C339" t="str"/>
-      <x:c r="D339" s="24" t="str"/>
+      <x:c r="D339" s="22" t="str"/>
       <x:c r="E339" t="str"/>
       <x:c r="F339" t="str"/>
       <x:c r="G339" t="str"/>
@@ -4982,10 +6612,10 @@
       <x:c r="J339" t="str"/>
     </x:row>
     <x:row r="340">
-      <x:c r="A340" s="24" t="str"/>
+      <x:c r="A340" s="22" t="str"/>
       <x:c r="B340" t="str"/>
       <x:c r="C340" t="str"/>
-      <x:c r="D340" s="24" t="str"/>
+      <x:c r="D340" s="22" t="str"/>
       <x:c r="E340" t="str"/>
       <x:c r="F340" t="str"/>
       <x:c r="G340" t="str"/>
@@ -4994,10 +6624,10 @@
       <x:c r="J340" t="str"/>
     </x:row>
     <x:row r="341">
-      <x:c r="A341" s="24" t="str"/>
+      <x:c r="A341" s="22" t="str"/>
       <x:c r="B341" t="str"/>
       <x:c r="C341" t="str"/>
-      <x:c r="D341" s="24" t="str"/>
+      <x:c r="D341" s="22" t="str"/>
       <x:c r="E341" t="str"/>
       <x:c r="F341" t="str"/>
       <x:c r="G341" t="str"/>
@@ -5006,10 +6636,10 @@
       <x:c r="J341" t="str"/>
     </x:row>
     <x:row r="342">
-      <x:c r="A342" s="24" t="str"/>
+      <x:c r="A342" s="22" t="str"/>
       <x:c r="B342" t="str"/>
       <x:c r="C342" t="str"/>
-      <x:c r="D342" s="24" t="str"/>
+      <x:c r="D342" s="22" t="str"/>
       <x:c r="E342" t="str"/>
       <x:c r="F342" t="str"/>
       <x:c r="G342" t="str"/>
@@ -5018,10 +6648,10 @@
       <x:c r="J342" t="str"/>
     </x:row>
     <x:row r="343">
-      <x:c r="A343" s="24" t="str"/>
+      <x:c r="A343" s="22" t="str"/>
       <x:c r="B343" t="str"/>
       <x:c r="C343" t="str"/>
-      <x:c r="D343" s="24" t="str"/>
+      <x:c r="D343" s="22" t="str"/>
       <x:c r="E343" t="str"/>
       <x:c r="F343" t="str"/>
       <x:c r="G343" t="str"/>
@@ -5030,10 +6660,10 @@
       <x:c r="J343" t="str"/>
     </x:row>
     <x:row r="344">
-      <x:c r="A344" s="24" t="str"/>
+      <x:c r="A344" s="22" t="str"/>
       <x:c r="B344" t="str"/>
       <x:c r="C344" t="str"/>
-      <x:c r="D344" s="24" t="str"/>
+      <x:c r="D344" s="22" t="str"/>
       <x:c r="E344" t="str"/>
       <x:c r="F344" t="str"/>
       <x:c r="G344" t="str"/>
@@ -5042,10 +6672,10 @@
       <x:c r="J344" t="str"/>
     </x:row>
     <x:row r="345">
-      <x:c r="A345" s="24" t="str"/>
+      <x:c r="A345" s="22" t="str"/>
       <x:c r="B345" t="str"/>
       <x:c r="C345" t="str"/>
-      <x:c r="D345" s="24" t="str"/>
+      <x:c r="D345" s="22" t="str"/>
       <x:c r="E345" t="str"/>
       <x:c r="F345" t="str"/>
       <x:c r="G345" t="str"/>
@@ -5054,10 +6684,10 @@
       <x:c r="J345" t="str"/>
     </x:row>
     <x:row r="346">
-      <x:c r="A346" s="24" t="str"/>
+      <x:c r="A346" s="22" t="str"/>
       <x:c r="B346" t="str"/>
       <x:c r="C346" t="str"/>
-      <x:c r="D346" s="24" t="str"/>
+      <x:c r="D346" s="22" t="str"/>
       <x:c r="E346" t="str"/>
       <x:c r="F346" t="str"/>
       <x:c r="G346" t="str"/>
@@ -5066,10 +6696,10 @@
       <x:c r="J346" t="str"/>
     </x:row>
     <x:row r="347">
-      <x:c r="A347" s="24" t="str"/>
+      <x:c r="A347" s="22" t="str"/>
       <x:c r="B347" t="str"/>
       <x:c r="C347" t="str"/>
-      <x:c r="D347" s="24" t="str"/>
+      <x:c r="D347" s="22" t="str"/>
       <x:c r="E347" t="str"/>
       <x:c r="F347" t="str"/>
       <x:c r="G347" t="str"/>
@@ -5078,10 +6708,10 @@
       <x:c r="J347" t="str"/>
     </x:row>
     <x:row r="348">
-      <x:c r="A348" s="24" t="str"/>
+      <x:c r="A348" s="22" t="str"/>
       <x:c r="B348" t="str"/>
       <x:c r="C348" t="str"/>
-      <x:c r="D348" s="24" t="str"/>
+      <x:c r="D348" s="22" t="str"/>
       <x:c r="E348" t="str"/>
       <x:c r="F348" t="str"/>
       <x:c r="G348" t="str"/>
@@ -5090,10 +6720,10 @@
       <x:c r="J348" t="str"/>
     </x:row>
     <x:row r="349">
-      <x:c r="A349" s="24" t="str"/>
+      <x:c r="A349" s="22" t="str"/>
       <x:c r="B349" t="str"/>
       <x:c r="C349" t="str"/>
-      <x:c r="D349" s="24" t="str"/>
+      <x:c r="D349" s="22" t="str"/>
       <x:c r="E349" t="str"/>
       <x:c r="F349" t="str"/>
       <x:c r="G349" t="str"/>
@@ -5102,10 +6732,10 @@
       <x:c r="J349" t="str"/>
     </x:row>
     <x:row r="350">
-      <x:c r="A350" s="24" t="str"/>
+      <x:c r="A350" s="22" t="str"/>
       <x:c r="B350" t="str"/>
       <x:c r="C350" t="str"/>
-      <x:c r="D350" s="24" t="str"/>
+      <x:c r="D350" s="22" t="str"/>
       <x:c r="E350" t="str"/>
       <x:c r="F350" t="str"/>
       <x:c r="G350" t="str"/>
@@ -5114,10 +6744,10 @@
       <x:c r="J350" t="str"/>
     </x:row>
     <x:row r="351">
-      <x:c r="A351" s="24" t="str"/>
+      <x:c r="A351" s="22" t="str"/>
       <x:c r="B351" t="str"/>
       <x:c r="C351" t="str"/>
-      <x:c r="D351" s="24" t="str"/>
+      <x:c r="D351" s="22" t="str"/>
       <x:c r="E351" t="str"/>
       <x:c r="F351" t="str"/>
       <x:c r="G351" t="str"/>
@@ -5126,10 +6756,10 @@
       <x:c r="J351" t="str"/>
     </x:row>
     <x:row r="352">
-      <x:c r="A352" s="24" t="str"/>
+      <x:c r="A352" s="22" t="str"/>
       <x:c r="B352" t="str"/>
       <x:c r="C352" t="str"/>
-      <x:c r="D352" s="24" t="str"/>
+      <x:c r="D352" s="22" t="str"/>
       <x:c r="E352" t="str"/>
       <x:c r="F352" t="str"/>
       <x:c r="G352" t="str"/>
@@ -5138,10 +6768,10 @@
       <x:c r="J352" t="str"/>
     </x:row>
     <x:row r="353">
-      <x:c r="A353" s="24" t="str"/>
+      <x:c r="A353" s="22" t="str"/>
       <x:c r="B353" t="str"/>
       <x:c r="C353" t="str"/>
-      <x:c r="D353" s="24" t="str"/>
+      <x:c r="D353" s="22" t="str"/>
       <x:c r="E353" t="str"/>
       <x:c r="F353" t="str"/>
       <x:c r="G353" t="str"/>
@@ -5150,10 +6780,10 @@
       <x:c r="J353" t="str"/>
     </x:row>
     <x:row r="354">
-      <x:c r="A354" s="24" t="str"/>
+      <x:c r="A354" s="22" t="str"/>
       <x:c r="B354" t="str"/>
       <x:c r="C354" t="str"/>
-      <x:c r="D354" s="24" t="str"/>
+      <x:c r="D354" s="22" t="str"/>
       <x:c r="E354" t="str"/>
       <x:c r="F354" t="str"/>
       <x:c r="G354" t="str"/>
@@ -5162,10 +6792,10 @@
       <x:c r="J354" t="str"/>
     </x:row>
     <x:row r="355">
-      <x:c r="A355" s="24" t="str"/>
+      <x:c r="A355" s="22" t="str"/>
       <x:c r="B355" t="str"/>
       <x:c r="C355" t="str"/>
-      <x:c r="D355" s="24" t="str"/>
+      <x:c r="D355" s="22" t="str"/>
       <x:c r="E355" t="str"/>
       <x:c r="F355" t="str"/>
       <x:c r="G355" t="str"/>
@@ -5174,10 +6804,10 @@
       <x:c r="J355" t="str"/>
     </x:row>
     <x:row r="356">
-      <x:c r="A356" s="24" t="str"/>
+      <x:c r="A356" s="22" t="str"/>
       <x:c r="B356" t="str"/>
       <x:c r="C356" t="str"/>
-      <x:c r="D356" s="24" t="str"/>
+      <x:c r="D356" s="22" t="str"/>
       <x:c r="E356" t="str"/>
       <x:c r="F356" t="str"/>
       <x:c r="G356" t="str"/>
@@ -5186,10 +6816,10 @@
       <x:c r="J356" t="str"/>
     </x:row>
     <x:row r="357">
-      <x:c r="A357" s="24" t="str"/>
+      <x:c r="A357" s="22" t="str"/>
       <x:c r="B357" t="str"/>
       <x:c r="C357" t="str"/>
-      <x:c r="D357" s="24" t="str"/>
+      <x:c r="D357" s="22" t="str"/>
       <x:c r="E357" t="str"/>
       <x:c r="F357" t="str"/>
       <x:c r="G357" t="str"/>
@@ -5198,10 +6828,10 @@
       <x:c r="J357" t="str"/>
     </x:row>
     <x:row r="358">
-      <x:c r="A358" s="24" t="str"/>
+      <x:c r="A358" s="22" t="str"/>
       <x:c r="B358" t="str"/>
       <x:c r="C358" t="str"/>
-      <x:c r="D358" s="24" t="str"/>
+      <x:c r="D358" s="22" t="str"/>
       <x:c r="E358" t="str"/>
       <x:c r="F358" t="str"/>
       <x:c r="G358" t="str"/>
@@ -5210,10 +6840,10 @@
       <x:c r="J358" t="str"/>
     </x:row>
     <x:row r="359">
-      <x:c r="A359" s="24" t="str"/>
+      <x:c r="A359" s="22" t="str"/>
       <x:c r="B359" t="str"/>
       <x:c r="C359" t="str"/>
-      <x:c r="D359" s="24" t="str"/>
+      <x:c r="D359" s="22" t="str"/>
       <x:c r="E359" t="str"/>
       <x:c r="F359" t="str"/>
       <x:c r="G359" t="str"/>
@@ -5222,10 +6852,10 @@
       <x:c r="J359" t="str"/>
     </x:row>
     <x:row r="360">
-      <x:c r="A360" s="24" t="str"/>
+      <x:c r="A360" s="22" t="str"/>
       <x:c r="B360" t="str"/>
       <x:c r="C360" t="str"/>
-      <x:c r="D360" s="24" t="str"/>
+      <x:c r="D360" s="22" t="str"/>
       <x:c r="E360" t="str"/>
       <x:c r="F360" t="str"/>
       <x:c r="G360" t="str"/>
@@ -5234,10 +6864,10 @@
       <x:c r="J360" t="str"/>
     </x:row>
     <x:row r="361">
-      <x:c r="A361" s="24" t="str"/>
+      <x:c r="A361" s="22" t="str"/>
       <x:c r="B361" t="str"/>
       <x:c r="C361" t="str"/>
-      <x:c r="D361" s="24" t="str"/>
+      <x:c r="D361" s="22" t="str"/>
       <x:c r="E361" t="str"/>
       <x:c r="F361" t="str"/>
       <x:c r="G361" t="str"/>
@@ -5246,10 +6876,10 @@
       <x:c r="J361" t="str"/>
     </x:row>
     <x:row r="362">
-      <x:c r="A362" s="24" t="str"/>
+      <x:c r="A362" s="22" t="str"/>
       <x:c r="B362" t="str"/>
       <x:c r="C362" t="str"/>
-      <x:c r="D362" s="24" t="str"/>
+      <x:c r="D362" s="22" t="str"/>
       <x:c r="E362" t="str"/>
       <x:c r="F362" t="str"/>
       <x:c r="G362" t="str"/>
@@ -5258,10 +6888,10 @@
       <x:c r="J362" t="str"/>
     </x:row>
     <x:row r="363">
-      <x:c r="A363" s="24" t="str"/>
+      <x:c r="A363" s="22" t="str"/>
       <x:c r="B363" t="str"/>
       <x:c r="C363" t="str"/>
-      <x:c r="D363" s="24" t="str"/>
+      <x:c r="D363" s="22" t="str"/>
       <x:c r="E363" t="str"/>
       <x:c r="F363" t="str"/>
       <x:c r="G363" t="str"/>
@@ -5270,10 +6900,10 @@
       <x:c r="J363" t="str"/>
     </x:row>
     <x:row r="364">
-      <x:c r="A364" s="24" t="str"/>
+      <x:c r="A364" s="22" t="str"/>
       <x:c r="B364" t="str"/>
       <x:c r="C364" t="str"/>
-      <x:c r="D364" s="24" t="str"/>
+      <x:c r="D364" s="22" t="str"/>
       <x:c r="E364" t="str"/>
       <x:c r="F364" t="str"/>
       <x:c r="G364" t="str"/>
@@ -5282,10 +6912,10 @@
       <x:c r="J364" t="str"/>
     </x:row>
     <x:row r="365">
-      <x:c r="A365" s="24" t="str"/>
+      <x:c r="A365" s="22" t="str"/>
       <x:c r="B365" t="str"/>
       <x:c r="C365" t="str"/>
-      <x:c r="D365" s="24" t="str"/>
+      <x:c r="D365" s="22" t="str"/>
       <x:c r="E365" t="str"/>
       <x:c r="F365" t="str"/>
       <x:c r="G365" t="str"/>
@@ -5294,10 +6924,10 @@
       <x:c r="J365" t="str"/>
     </x:row>
     <x:row r="366">
-      <x:c r="A366" s="24" t="str"/>
+      <x:c r="A366" s="22" t="str"/>
       <x:c r="B366" t="str"/>
       <x:c r="C366" t="str"/>
-      <x:c r="D366" s="24" t="str"/>
+      <x:c r="D366" s="22" t="str"/>
       <x:c r="E366" t="str"/>
       <x:c r="F366" t="str"/>
       <x:c r="G366" t="str"/>
@@ -5306,10 +6936,10 @@
       <x:c r="J366" t="str"/>
     </x:row>
     <x:row r="367">
-      <x:c r="A367" s="24" t="str"/>
+      <x:c r="A367" s="22" t="str"/>
       <x:c r="B367" t="str"/>
       <x:c r="C367" t="str"/>
-      <x:c r="D367" s="24" t="str"/>
+      <x:c r="D367" s="22" t="str"/>
       <x:c r="E367" t="str"/>
       <x:c r="F367" t="str"/>
       <x:c r="G367" t="str"/>
@@ -5318,10 +6948,10 @@
       <x:c r="J367" t="str"/>
     </x:row>
     <x:row r="368">
-      <x:c r="A368" s="24" t="str"/>
+      <x:c r="A368" s="22" t="str"/>
       <x:c r="B368" t="str"/>
       <x:c r="C368" t="str"/>
-      <x:c r="D368" s="24" t="str"/>
+      <x:c r="D368" s="22" t="str"/>
       <x:c r="E368" t="str"/>
       <x:c r="F368" t="str"/>
       <x:c r="G368" t="str"/>
@@ -5330,10 +6960,10 @@
       <x:c r="J368" t="str"/>
     </x:row>
     <x:row r="369">
-      <x:c r="A369" s="24" t="str"/>
+      <x:c r="A369" s="22" t="str"/>
       <x:c r="B369" t="str"/>
       <x:c r="C369" t="str"/>
-      <x:c r="D369" s="24" t="str"/>
+      <x:c r="D369" s="22" t="str"/>
       <x:c r="E369" t="str"/>
       <x:c r="F369" t="str"/>
       <x:c r="G369" t="str"/>
@@ -5342,10 +6972,10 @@
       <x:c r="J369" t="str"/>
     </x:row>
     <x:row r="370">
-      <x:c r="A370" s="24" t="str"/>
+      <x:c r="A370" s="22" t="str"/>
       <x:c r="B370" t="str"/>
       <x:c r="C370" t="str"/>
-      <x:c r="D370" s="24" t="str"/>
+      <x:c r="D370" s="22" t="str"/>
       <x:c r="E370" t="str"/>
       <x:c r="F370" t="str"/>
       <x:c r="G370" t="str"/>
@@ -5354,10 +6984,10 @@
       <x:c r="J370" t="str"/>
     </x:row>
     <x:row r="371">
-      <x:c r="A371" s="24" t="str"/>
+      <x:c r="A371" s="22" t="str"/>
       <x:c r="B371" t="str"/>
       <x:c r="C371" t="str"/>
-      <x:c r="D371" s="24" t="str"/>
+      <x:c r="D371" s="22" t="str"/>
       <x:c r="E371" t="str"/>
       <x:c r="F371" t="str"/>
       <x:c r="G371" t="str"/>
@@ -5366,10 +6996,10 @@
       <x:c r="J371" t="str"/>
     </x:row>
     <x:row r="372">
-      <x:c r="A372" s="24" t="str"/>
+      <x:c r="A372" s="22" t="str"/>
       <x:c r="B372" t="str"/>
       <x:c r="C372" t="str"/>
-      <x:c r="D372" s="24" t="str"/>
+      <x:c r="D372" s="22" t="str"/>
       <x:c r="E372" t="str"/>
       <x:c r="F372" t="str"/>
       <x:c r="G372" t="str"/>
@@ -5378,10 +7008,10 @@
       <x:c r="J372" t="str"/>
     </x:row>
     <x:row r="373">
-      <x:c r="A373" s="24" t="str"/>
+      <x:c r="A373" s="22" t="str"/>
       <x:c r="B373" t="str"/>
       <x:c r="C373" t="str"/>
-      <x:c r="D373" s="24" t="str"/>
+      <x:c r="D373" s="22" t="str"/>
       <x:c r="E373" t="str"/>
       <x:c r="F373" t="str"/>
       <x:c r="G373" t="str"/>
@@ -5390,10 +7020,10 @@
       <x:c r="J373" t="str"/>
     </x:row>
     <x:row r="374">
-      <x:c r="A374" s="24" t="str"/>
+      <x:c r="A374" s="22" t="str"/>
       <x:c r="B374" t="str"/>
       <x:c r="C374" t="str"/>
-      <x:c r="D374" s="24" t="str"/>
+      <x:c r="D374" s="22" t="str"/>
       <x:c r="E374" t="str"/>
       <x:c r="F374" t="str"/>
       <x:c r="G374" t="str"/>
@@ -5402,10 +7032,10 @@
       <x:c r="J374" t="str"/>
     </x:row>
     <x:row r="375">
-      <x:c r="A375" s="24" t="str"/>
+      <x:c r="A375" s="22" t="str"/>
       <x:c r="B375" t="str"/>
       <x:c r="C375" t="str"/>
-      <x:c r="D375" s="24" t="str"/>
+      <x:c r="D375" s="22" t="str"/>
       <x:c r="E375" t="str"/>
       <x:c r="F375" t="str"/>
       <x:c r="G375" t="str"/>
@@ -5414,10 +7044,10 @@
       <x:c r="J375" t="str"/>
     </x:row>
     <x:row r="376">
-      <x:c r="A376" s="24" t="str"/>
+      <x:c r="A376" s="22" t="str"/>
       <x:c r="B376" t="str"/>
       <x:c r="C376" t="str"/>
-      <x:c r="D376" s="24" t="str"/>
+      <x:c r="D376" s="22" t="str"/>
       <x:c r="E376" t="str"/>
       <x:c r="F376" t="str"/>
       <x:c r="G376" t="str"/>
@@ -5426,10 +7056,10 @@
       <x:c r="J376" t="str"/>
     </x:row>
     <x:row r="377">
-      <x:c r="A377" s="24" t="str"/>
+      <x:c r="A377" s="22" t="str"/>
       <x:c r="B377" t="str"/>
       <x:c r="C377" t="str"/>
-      <x:c r="D377" s="24" t="str"/>
+      <x:c r="D377" s="22" t="str"/>
       <x:c r="E377" t="str"/>
       <x:c r="F377" t="str"/>
       <x:c r="G377" t="str"/>
@@ -5438,10 +7068,10 @@
       <x:c r="J377" t="str"/>
     </x:row>
     <x:row r="378">
-      <x:c r="A378" s="24" t="str"/>
+      <x:c r="A378" s="22" t="str"/>
       <x:c r="B378" t="str"/>
       <x:c r="C378" t="str"/>
-      <x:c r="D378" s="24" t="str"/>
+      <x:c r="D378" s="22" t="str"/>
       <x:c r="E378" t="str"/>
       <x:c r="F378" t="str"/>
       <x:c r="G378" t="str"/>
@@ -5450,10 +7080,10 @@
       <x:c r="J378" t="str"/>
     </x:row>
     <x:row r="379">
-      <x:c r="A379" s="24" t="str"/>
+      <x:c r="A379" s="22" t="str"/>
       <x:c r="B379" t="str"/>
       <x:c r="C379" t="str"/>
-      <x:c r="D379" s="24" t="str"/>
+      <x:c r="D379" s="22" t="str"/>
       <x:c r="E379" t="str"/>
       <x:c r="F379" t="str"/>
       <x:c r="G379" t="str"/>
@@ -5462,10 +7092,10 @@
       <x:c r="J379" t="str"/>
     </x:row>
     <x:row r="380">
-      <x:c r="A380" s="24" t="str"/>
+      <x:c r="A380" s="22" t="str"/>
       <x:c r="B380" t="str"/>
       <x:c r="C380" t="str"/>
-      <x:c r="D380" s="24" t="str"/>
+      <x:c r="D380" s="22" t="str"/>
       <x:c r="E380" t="str"/>
       <x:c r="F380" t="str"/>
       <x:c r="G380" t="str"/>
@@ -5474,10 +7104,10 @@
       <x:c r="J380" t="str"/>
     </x:row>
     <x:row r="381">
-      <x:c r="A381" s="24" t="str"/>
+      <x:c r="A381" s="22" t="str"/>
       <x:c r="B381" t="str"/>
       <x:c r="C381" t="str"/>
-      <x:c r="D381" s="24" t="str"/>
+      <x:c r="D381" s="22" t="str"/>
       <x:c r="E381" t="str"/>
       <x:c r="F381" t="str"/>
       <x:c r="G381" t="str"/>
@@ -5486,10 +7116,10 @@
       <x:c r="J381" t="str"/>
     </x:row>
     <x:row r="382">
-      <x:c r="A382" s="24" t="str"/>
+      <x:c r="A382" s="22" t="str"/>
       <x:c r="B382" t="str"/>
       <x:c r="C382" t="str"/>
-      <x:c r="D382" s="24" t="str"/>
+      <x:c r="D382" s="22" t="str"/>
       <x:c r="E382" t="str"/>
       <x:c r="F382" t="str"/>
       <x:c r="G382" t="str"/>
@@ -5498,10 +7128,10 @@
       <x:c r="J382" t="str"/>
     </x:row>
     <x:row r="383">
-      <x:c r="A383" s="24" t="str"/>
+      <x:c r="A383" s="22" t="str"/>
       <x:c r="B383" t="str"/>
       <x:c r="C383" t="str"/>
-      <x:c r="D383" s="24" t="str"/>
+      <x:c r="D383" s="22" t="str"/>
       <x:c r="E383" t="str"/>
       <x:c r="F383" t="str"/>
       <x:c r="G383" t="str"/>
@@ -5510,10 +7140,10 @@
       <x:c r="J383" t="str"/>
     </x:row>
     <x:row r="384">
-      <x:c r="A384" s="24" t="str"/>
+      <x:c r="A384" s="22" t="str"/>
       <x:c r="B384" t="str"/>
       <x:c r="C384" t="str"/>
-      <x:c r="D384" s="24" t="str"/>
+      <x:c r="D384" s="22" t="str"/>
       <x:c r="E384" t="str"/>
       <x:c r="F384" t="str"/>
       <x:c r="G384" t="str"/>
@@ -5522,10 +7152,10 @@
       <x:c r="J384" t="str"/>
     </x:row>
     <x:row r="385">
-      <x:c r="A385" s="24" t="str"/>
+      <x:c r="A385" s="22" t="str"/>
       <x:c r="B385" t="str"/>
       <x:c r="C385" t="str"/>
-      <x:c r="D385" s="24" t="str"/>
+      <x:c r="D385" s="22" t="str"/>
       <x:c r="E385" t="str"/>
       <x:c r="F385" t="str"/>
       <x:c r="G385" t="str"/>
@@ -5534,10 +7164,10 @@
       <x:c r="J385" t="str"/>
     </x:row>
     <x:row r="386">
-      <x:c r="A386" s="24" t="str"/>
+      <x:c r="A386" s="22" t="str"/>
       <x:c r="B386" t="str"/>
       <x:c r="C386" t="str"/>
-      <x:c r="D386" s="24" t="str"/>
+      <x:c r="D386" s="22" t="str"/>
       <x:c r="E386" t="str"/>
       <x:c r="F386" t="str"/>
       <x:c r="G386" t="str"/>
@@ -5546,10 +7176,10 @@
       <x:c r="J386" t="str"/>
     </x:row>
     <x:row r="387">
-      <x:c r="A387" s="24" t="str"/>
+      <x:c r="A387" s="22" t="str"/>
       <x:c r="B387" t="str"/>
       <x:c r="C387" t="str"/>
-      <x:c r="D387" s="24" t="str"/>
+      <x:c r="D387" s="22" t="str"/>
       <x:c r="E387" t="str"/>
       <x:c r="F387" t="str"/>
       <x:c r="G387" t="str"/>
@@ -5558,10 +7188,10 @@
       <x:c r="J387" t="str"/>
     </x:row>
     <x:row r="388">
-      <x:c r="A388" s="24" t="str"/>
+      <x:c r="A388" s="22" t="str"/>
       <x:c r="B388" t="str"/>
       <x:c r="C388" t="str"/>
-      <x:c r="D388" s="24" t="str"/>
+      <x:c r="D388" s="22" t="str"/>
       <x:c r="E388" t="str"/>
       <x:c r="F388" t="str"/>
       <x:c r="G388" t="str"/>
@@ -5570,10 +7200,10 @@
       <x:c r="J388" t="str"/>
     </x:row>
     <x:row r="389">
-      <x:c r="A389" s="24" t="str"/>
+      <x:c r="A389" s="22" t="str"/>
       <x:c r="B389" t="str"/>
       <x:c r="C389" t="str"/>
-      <x:c r="D389" s="24" t="str"/>
+      <x:c r="D389" s="22" t="str"/>
       <x:c r="E389" t="str"/>
       <x:c r="F389" t="str"/>
       <x:c r="G389" t="str"/>
@@ -5582,10 +7212,10 @@
       <x:c r="J389" t="str"/>
     </x:row>
     <x:row r="390">
-      <x:c r="A390" s="24" t="str"/>
+      <x:c r="A390" s="22" t="str"/>
       <x:c r="B390" t="str"/>
       <x:c r="C390" t="str"/>
-      <x:c r="D390" s="24" t="str"/>
+      <x:c r="D390" s="22" t="str"/>
       <x:c r="E390" t="str"/>
       <x:c r="F390" t="str"/>
       <x:c r="G390" t="str"/>
@@ -5594,10 +7224,10 @@
       <x:c r="J390" t="str"/>
     </x:row>
     <x:row r="391">
-      <x:c r="A391" s="24" t="str"/>
+      <x:c r="A391" s="22" t="str"/>
       <x:c r="B391" t="str"/>
       <x:c r="C391" t="str"/>
-      <x:c r="D391" s="24" t="str"/>
+      <x:c r="D391" s="22" t="str"/>
       <x:c r="E391" t="str"/>
       <x:c r="F391" t="str"/>
       <x:c r="G391" t="str"/>
@@ -5606,10 +7236,10 @@
       <x:c r="J391" t="str"/>
     </x:row>
     <x:row r="392">
-      <x:c r="A392" s="24" t="str"/>
+      <x:c r="A392" s="22" t="str"/>
       <x:c r="B392" t="str"/>
       <x:c r="C392" t="str"/>
-      <x:c r="D392" s="24" t="str"/>
+      <x:c r="D392" s="22" t="str"/>
       <x:c r="E392" t="str"/>
       <x:c r="F392" t="str"/>
       <x:c r="G392" t="str"/>
@@ -5618,10 +7248,10 @@
       <x:c r="J392" t="str"/>
     </x:row>
     <x:row r="393">
-      <x:c r="A393" s="24" t="str"/>
+      <x:c r="A393" s="22" t="str"/>
       <x:c r="B393" t="str"/>
       <x:c r="C393" t="str"/>
-      <x:c r="D393" s="24" t="str"/>
+      <x:c r="D393" s="22" t="str"/>
       <x:c r="E393" t="str"/>
       <x:c r="F393" t="str"/>
       <x:c r="G393" t="str"/>
@@ -5630,10 +7260,10 @@
       <x:c r="J393" t="str"/>
     </x:row>
     <x:row r="394">
-      <x:c r="A394" s="24" t="str"/>
+      <x:c r="A394" s="22" t="str"/>
       <x:c r="B394" t="str"/>
       <x:c r="C394" t="str"/>
-      <x:c r="D394" s="24" t="str"/>
+      <x:c r="D394" s="22" t="str"/>
       <x:c r="E394" t="str"/>
       <x:c r="F394" t="str"/>
       <x:c r="G394" t="str"/>
@@ -5642,10 +7272,10 @@
       <x:c r="J394" t="str"/>
     </x:row>
     <x:row r="395">
-      <x:c r="A395" s="24" t="str"/>
+      <x:c r="A395" s="22" t="str"/>
       <x:c r="B395" t="str"/>
       <x:c r="C395" t="str"/>
-      <x:c r="D395" s="24" t="str"/>
+      <x:c r="D395" s="22" t="str"/>
       <x:c r="E395" t="str"/>
       <x:c r="F395" t="str"/>
       <x:c r="G395" t="str"/>
@@ -5654,10 +7284,10 @@
       <x:c r="J395" t="str"/>
     </x:row>
     <x:row r="396">
-      <x:c r="A396" s="24" t="str"/>
+      <x:c r="A396" s="22" t="str"/>
       <x:c r="B396" t="str"/>
       <x:c r="C396" t="str"/>
-      <x:c r="D396" s="24" t="str"/>
+      <x:c r="D396" s="22" t="str"/>
       <x:c r="E396" t="str"/>
       <x:c r="F396" t="str"/>
       <x:c r="G396" t="str"/>
@@ -5666,10 +7296,10 @@
       <x:c r="J396" t="str"/>
     </x:row>
     <x:row r="397">
-      <x:c r="A397" s="24" t="str"/>
+      <x:c r="A397" s="22" t="str"/>
       <x:c r="B397" t="str"/>
       <x:c r="C397" t="str"/>
-      <x:c r="D397" s="24" t="str"/>
+      <x:c r="D397" s="22" t="str"/>
       <x:c r="E397" t="str"/>
       <x:c r="F397" t="str"/>
       <x:c r="G397" t="str"/>
@@ -5678,10 +7308,10 @@
       <x:c r="J397" t="str"/>
     </x:row>
     <x:row r="398">
-      <x:c r="A398" s="24" t="str"/>
+      <x:c r="A398" s="22" t="str"/>
       <x:c r="B398" t="str"/>
       <x:c r="C398" t="str"/>
-      <x:c r="D398" s="24" t="str"/>
+      <x:c r="D398" s="22" t="str"/>
       <x:c r="E398" t="str"/>
       <x:c r="F398" t="str"/>
       <x:c r="G398" t="str"/>
@@ -5690,10 +7320,10 @@
       <x:c r="J398" t="str"/>
     </x:row>
     <x:row r="399">
-      <x:c r="A399" s="24" t="str"/>
+      <x:c r="A399" s="22" t="str"/>
       <x:c r="B399" t="str"/>
       <x:c r="C399" t="str"/>
-      <x:c r="D399" s="24" t="str"/>
+      <x:c r="D399" s="22" t="str"/>
       <x:c r="E399" t="str"/>
       <x:c r="F399" t="str"/>
       <x:c r="G399" t="str"/>
@@ -5702,10 +7332,10 @@
       <x:c r="J399" t="str"/>
     </x:row>
     <x:row r="400">
-      <x:c r="A400" s="24" t="str"/>
+      <x:c r="A400" s="22" t="str"/>
       <x:c r="B400" t="str"/>
       <x:c r="C400" t="str"/>
-      <x:c r="D400" s="24" t="str"/>
+      <x:c r="D400" s="22" t="str"/>
       <x:c r="E400" t="str"/>
       <x:c r="F400" t="str"/>
       <x:c r="G400" t="str"/>
@@ -5714,10 +7344,10 @@
       <x:c r="J400" t="str"/>
     </x:row>
     <x:row r="401">
-      <x:c r="A401" s="24" t="str"/>
+      <x:c r="A401" s="22" t="str"/>
       <x:c r="B401" t="str"/>
       <x:c r="C401" t="str"/>
-      <x:c r="D401" s="24" t="str"/>
+      <x:c r="D401" s="22" t="str"/>
       <x:c r="E401" t="str"/>
       <x:c r="F401" t="str"/>
       <x:c r="G401" t="str"/>
@@ -5726,10 +7356,10 @@
       <x:c r="J401" t="str"/>
     </x:row>
     <x:row r="402">
-      <x:c r="A402" s="24" t="str"/>
+      <x:c r="A402" s="22" t="str"/>
       <x:c r="B402" t="str"/>
       <x:c r="C402" t="str"/>
-      <x:c r="D402" s="24" t="str"/>
+      <x:c r="D402" s="22" t="str"/>
       <x:c r="E402" t="str"/>
       <x:c r="F402" t="str"/>
       <x:c r="G402" t="str"/>
@@ -5738,10 +7368,10 @@
       <x:c r="J402" t="str"/>
     </x:row>
     <x:row r="403">
-      <x:c r="A403" s="24" t="str"/>
+      <x:c r="A403" s="22" t="str"/>
       <x:c r="B403" t="str"/>
       <x:c r="C403" t="str"/>
-      <x:c r="D403" s="24" t="str"/>
+      <x:c r="D403" s="22" t="str"/>
       <x:c r="E403" t="str"/>
       <x:c r="F403" t="str"/>
       <x:c r="G403" t="str"/>
@@ -5750,10 +7380,10 @@
       <x:c r="J403" t="str"/>
     </x:row>
     <x:row r="404">
-      <x:c r="A404" s="24" t="str"/>
+      <x:c r="A404" s="22" t="str"/>
       <x:c r="B404" t="str"/>
       <x:c r="C404" t="str"/>
-      <x:c r="D404" s="24" t="str"/>
+      <x:c r="D404" s="22" t="str"/>
       <x:c r="E404" t="str"/>
       <x:c r="F404" t="str"/>
       <x:c r="G404" t="str"/>
@@ -5762,10 +7392,10 @@
       <x:c r="J404" t="str"/>
     </x:row>
     <x:row r="405">
-      <x:c r="A405" s="24" t="str"/>
+      <x:c r="A405" s="22" t="str"/>
       <x:c r="B405" t="str"/>
       <x:c r="C405" t="str"/>
-      <x:c r="D405" s="24" t="str"/>
+      <x:c r="D405" s="22" t="str"/>
       <x:c r="E405" t="str"/>
       <x:c r="F405" t="str"/>
       <x:c r="G405" t="str"/>
@@ -5774,10 +7404,10 @@
       <x:c r="J405" t="str"/>
     </x:row>
     <x:row r="406">
-      <x:c r="A406" s="24" t="str"/>
+      <x:c r="A406" s="22" t="str"/>
       <x:c r="B406" t="str"/>
       <x:c r="C406" t="str"/>
-      <x:c r="D406" s="24" t="str"/>
+      <x:c r="D406" s="22" t="str"/>
       <x:c r="E406" t="str"/>
       <x:c r="F406" t="str"/>
       <x:c r="G406" t="str"/>
@@ -5786,10 +7416,10 @@
       <x:c r="J406" t="str"/>
     </x:row>
     <x:row r="407">
-      <x:c r="A407" s="24" t="str"/>
+      <x:c r="A407" s="22" t="str"/>
       <x:c r="B407" t="str"/>
       <x:c r="C407" t="str"/>
-      <x:c r="D407" s="24" t="str"/>
+      <x:c r="D407" s="22" t="str"/>
       <x:c r="E407" t="str"/>
       <x:c r="F407" t="str"/>
       <x:c r="G407" t="str"/>
@@ -5798,10 +7428,10 @@
       <x:c r="J407" t="str"/>
     </x:row>
     <x:row r="408">
-      <x:c r="A408" s="24" t="str"/>
+      <x:c r="A408" s="22" t="str"/>
       <x:c r="B408" t="str"/>
       <x:c r="C408" t="str"/>
-      <x:c r="D408" s="24" t="str"/>
+      <x:c r="D408" s="22" t="str"/>
       <x:c r="E408" t="str"/>
       <x:c r="F408" t="str"/>
       <x:c r="G408" t="str"/>
@@ -5810,10 +7440,10 @@
       <x:c r="J408" t="str"/>
     </x:row>
     <x:row r="409">
-      <x:c r="A409" s="24" t="str"/>
+      <x:c r="A409" s="22" t="str"/>
       <x:c r="B409" t="str"/>
       <x:c r="C409" t="str"/>
-      <x:c r="D409" s="24" t="str"/>
+      <x:c r="D409" s="22" t="str"/>
       <x:c r="E409" t="str"/>
       <x:c r="F409" t="str"/>
       <x:c r="G409" t="str"/>
@@ -5822,10 +7452,10 @@
       <x:c r="J409" t="str"/>
     </x:row>
     <x:row r="410">
-      <x:c r="A410" s="24" t="str"/>
+      <x:c r="A410" s="22" t="str"/>
       <x:c r="B410" t="str"/>
       <x:c r="C410" t="str"/>
-      <x:c r="D410" s="24" t="str"/>
+      <x:c r="D410" s="22" t="str"/>
       <x:c r="E410" t="str"/>
       <x:c r="F410" t="str"/>
       <x:c r="G410" t="str"/>
@@ -5834,10 +7464,10 @@
       <x:c r="J410" t="str"/>
     </x:row>
     <x:row r="411">
-      <x:c r="A411" s="24" t="str"/>
+      <x:c r="A411" s="22" t="str"/>
       <x:c r="B411" t="str"/>
       <x:c r="C411" t="str"/>
-      <x:c r="D411" s="24" t="str"/>
+      <x:c r="D411" s="22" t="str"/>
       <x:c r="E411" t="str"/>
       <x:c r="F411" t="str"/>
       <x:c r="G411" t="str"/>
@@ -5846,10 +7476,10 @@
       <x:c r="J411" t="str"/>
     </x:row>
     <x:row r="412">
-      <x:c r="A412" s="24" t="str"/>
+      <x:c r="A412" s="22" t="str"/>
       <x:c r="B412" t="str"/>
       <x:c r="C412" t="str"/>
-      <x:c r="D412" s="24" t="str"/>
+      <x:c r="D412" s="22" t="str"/>
       <x:c r="E412" t="str"/>
       <x:c r="F412" t="str"/>
       <x:c r="G412" t="str"/>
@@ -5858,10 +7488,10 @@
       <x:c r="J412" t="str"/>
     </x:row>
     <x:row r="413">
-      <x:c r="A413" s="24" t="str"/>
+      <x:c r="A413" s="22" t="str"/>
       <x:c r="B413" t="str"/>
       <x:c r="C413" t="str"/>
-      <x:c r="D413" s="24" t="str"/>
+      <x:c r="D413" s="22" t="str"/>
       <x:c r="E413" t="str"/>
       <x:c r="F413" t="str"/>
       <x:c r="G413" t="str"/>
@@ -5870,10 +7500,10 @@
       <x:c r="J413" t="str"/>
     </x:row>
     <x:row r="414">
-      <x:c r="A414" s="24" t="str"/>
+      <x:c r="A414" s="22" t="str"/>
       <x:c r="B414" t="str"/>
       <x:c r="C414" t="str"/>
-      <x:c r="D414" s="24" t="str"/>
+      <x:c r="D414" s="22" t="str"/>
       <x:c r="E414" t="str"/>
       <x:c r="F414" t="str"/>
       <x:c r="G414" t="str"/>
@@ -5882,10 +7512,10 @@
       <x:c r="J414" t="str"/>
     </x:row>
     <x:row r="415">
-      <x:c r="A415" s="24" t="str"/>
+      <x:c r="A415" s="22" t="str"/>
       <x:c r="B415" t="str"/>
       <x:c r="C415" t="str"/>
-      <x:c r="D415" s="24" t="str"/>
+      <x:c r="D415" s="22" t="str"/>
       <x:c r="E415" t="str"/>
       <x:c r="F415" t="str"/>
       <x:c r="G415" t="str"/>
@@ -5894,10 +7524,10 @@
       <x:c r="J415" t="str"/>
     </x:row>
     <x:row r="416">
-      <x:c r="A416" s="24" t="str"/>
+      <x:c r="A416" s="22" t="str"/>
       <x:c r="B416" t="str"/>
       <x:c r="C416" t="str"/>
-      <x:c r="D416" s="24" t="str"/>
+      <x:c r="D416" s="22" t="str"/>
       <x:c r="E416" t="str"/>
       <x:c r="F416" t="str"/>
       <x:c r="G416" t="str"/>
@@ -5906,10 +7536,10 @@
       <x:c r="J416" t="str"/>
     </x:row>
     <x:row r="417">
-      <x:c r="A417" s="24" t="str"/>
+      <x:c r="A417" s="22" t="str"/>
       <x:c r="B417" t="str"/>
       <x:c r="C417" t="str"/>
-      <x:c r="D417" s="24" t="str"/>
+      <x:c r="D417" s="22" t="str"/>
       <x:c r="E417" t="str"/>
       <x:c r="F417" t="str"/>
       <x:c r="G417" t="str"/>
@@ -5918,10 +7548,10 @@
       <x:c r="J417" t="str"/>
     </x:row>
     <x:row r="418">
-      <x:c r="A418" s="24" t="str"/>
+      <x:c r="A418" s="22" t="str"/>
       <x:c r="B418" t="str"/>
       <x:c r="C418" t="str"/>
-      <x:c r="D418" s="24" t="str"/>
+      <x:c r="D418" s="22" t="str"/>
       <x:c r="E418" t="str"/>
       <x:c r="F418" t="str"/>
       <x:c r="G418" t="str"/>
@@ -5930,10 +7560,10 @@
       <x:c r="J418" t="str"/>
     </x:row>
     <x:row r="419">
-      <x:c r="A419" s="24" t="str"/>
+      <x:c r="A419" s="22" t="str"/>
       <x:c r="B419" t="str"/>
       <x:c r="C419" t="str"/>
-      <x:c r="D419" s="24" t="str"/>
+      <x:c r="D419" s="22" t="str"/>
       <x:c r="E419" t="str"/>
       <x:c r="F419" t="str"/>
       <x:c r="G419" t="str"/>
@@ -5942,10 +7572,10 @@
       <x:c r="J419" t="str"/>
     </x:row>
     <x:row r="420">
-      <x:c r="A420" s="24" t="str"/>
+      <x:c r="A420" s="22" t="str"/>
       <x:c r="B420" t="str"/>
       <x:c r="C420" t="str"/>
-      <x:c r="D420" s="24" t="str"/>
+      <x:c r="D420" s="22" t="str"/>
       <x:c r="E420" t="str"/>
       <x:c r="F420" t="str"/>
       <x:c r="G420" t="str"/>
@@ -5954,10 +7584,10 @@
       <x:c r="J420" t="str"/>
     </x:row>
     <x:row r="421">
-      <x:c r="A421" s="24" t="str"/>
+      <x:c r="A421" s="22" t="str"/>
       <x:c r="B421" t="str"/>
       <x:c r="C421" t="str"/>
-      <x:c r="D421" s="24" t="str"/>
+      <x:c r="D421" s="22" t="str"/>
       <x:c r="E421" t="str"/>
       <x:c r="F421" t="str"/>
       <x:c r="G421" t="str"/>
@@ -5966,10 +7596,10 @@
       <x:c r="J421" t="str"/>
     </x:row>
     <x:row r="422">
-      <x:c r="A422" s="24" t="str"/>
+      <x:c r="A422" s="22" t="str"/>
       <x:c r="B422" t="str"/>
       <x:c r="C422" t="str"/>
-      <x:c r="D422" s="24" t="str"/>
+      <x:c r="D422" s="22" t="str"/>
       <x:c r="E422" t="str"/>
       <x:c r="F422" t="str"/>
       <x:c r="G422" t="str"/>
@@ -5978,10 +7608,10 @@
       <x:c r="J422" t="str"/>
     </x:row>
     <x:row r="423">
-      <x:c r="A423" s="24" t="str"/>
+      <x:c r="A423" s="22" t="str"/>
       <x:c r="B423" t="str"/>
       <x:c r="C423" t="str"/>
-      <x:c r="D423" s="24" t="str"/>
+      <x:c r="D423" s="22" t="str"/>
       <x:c r="E423" t="str"/>
       <x:c r="F423" t="str"/>
       <x:c r="G423" t="str"/>
@@ -5990,10 +7620,10 @@
       <x:c r="J423" t="str"/>
     </x:row>
     <x:row r="424">
-      <x:c r="A424" s="24" t="str"/>
+      <x:c r="A424" s="22" t="str"/>
       <x:c r="B424" t="str"/>
       <x:c r="C424" t="str"/>
-      <x:c r="D424" s="24" t="str"/>
+      <x:c r="D424" s="22" t="str"/>
       <x:c r="E424" t="str"/>
       <x:c r="F424" t="str"/>
       <x:c r="G424" t="str"/>
@@ -6002,10 +7632,10 @@
       <x:c r="J424" t="str"/>
     </x:row>
     <x:row r="425">
-      <x:c r="A425" s="24" t="str"/>
+      <x:c r="A425" s="22" t="str"/>
       <x:c r="B425" t="str"/>
       <x:c r="C425" t="str"/>
-      <x:c r="D425" s="24" t="str"/>
+      <x:c r="D425" s="22" t="str"/>
       <x:c r="E425" t="str"/>
       <x:c r="F425" t="str"/>
       <x:c r="G425" t="str"/>
@@ -6014,10 +7644,10 @@
       <x:c r="J425" t="str"/>
     </x:row>
     <x:row r="426">
-      <x:c r="A426" s="24" t="str"/>
+      <x:c r="A426" s="22" t="str"/>
       <x:c r="B426" t="str"/>
       <x:c r="C426" t="str"/>
-      <x:c r="D426" s="24" t="str"/>
+      <x:c r="D426" s="22" t="str"/>
       <x:c r="E426" t="str"/>
       <x:c r="F426" t="str"/>
       <x:c r="G426" t="str"/>
@@ -6026,10 +7656,10 @@
       <x:c r="J426" t="str"/>
     </x:row>
     <x:row r="427">
-      <x:c r="A427" s="24" t="str"/>
+      <x:c r="A427" s="22" t="str"/>
       <x:c r="B427" t="str"/>
       <x:c r="C427" t="str"/>
-      <x:c r="D427" s="24" t="str"/>
+      <x:c r="D427" s="22" t="str"/>
       <x:c r="E427" t="str"/>
       <x:c r="F427" t="str"/>
       <x:c r="G427" t="str"/>
@@ -6038,10 +7668,10 @@
       <x:c r="J427" t="str"/>
     </x:row>
     <x:row r="428">
-      <x:c r="A428" s="24" t="str"/>
+      <x:c r="A428" s="22" t="str"/>
       <x:c r="B428" t="str"/>
       <x:c r="C428" t="str"/>
-      <x:c r="D428" s="24" t="str"/>
+      <x:c r="D428" s="22" t="str"/>
       <x:c r="E428" t="str"/>
       <x:c r="F428" t="str"/>
       <x:c r="G428" t="str"/>
@@ -6050,10 +7680,10 @@
       <x:c r="J428" t="str"/>
     </x:row>
     <x:row r="429">
-      <x:c r="A429" s="24" t="str"/>
+      <x:c r="A429" s="22" t="str"/>
       <x:c r="B429" t="str"/>
       <x:c r="C429" t="str"/>
-      <x:c r="D429" s="24" t="str"/>
+      <x:c r="D429" s="22" t="str"/>
       <x:c r="E429" t="str"/>
       <x:c r="F429" t="str"/>
       <x:c r="G429" t="str"/>
@@ -6062,10 +7692,10 @@
       <x:c r="J429" t="str"/>
     </x:row>
     <x:row r="430">
-      <x:c r="A430" s="24" t="str"/>
+      <x:c r="A430" s="22" t="str"/>
       <x:c r="B430" t="str"/>
       <x:c r="C430" t="str"/>
-      <x:c r="D430" s="24" t="str"/>
+      <x:c r="D430" s="22" t="str"/>
       <x:c r="E430" t="str"/>
       <x:c r="F430" t="str"/>
       <x:c r="G430" t="str"/>
@@ -6074,10 +7704,10 @@
       <x:c r="J430" t="str"/>
     </x:row>
     <x:row r="431">
-      <x:c r="A431" s="24" t="str"/>
+      <x:c r="A431" s="22" t="str"/>
       <x:c r="B431" t="str"/>
       <x:c r="C431" t="str"/>
-      <x:c r="D431" s="24" t="str"/>
+      <x:c r="D431" s="22" t="str"/>
       <x:c r="E431" t="str"/>
       <x:c r="F431" t="str"/>
       <x:c r="G431" t="str"/>
@@ -6086,10 +7716,10 @@
       <x:c r="J431" t="str"/>
     </x:row>
     <x:row r="432">
-      <x:c r="A432" s="24" t="str"/>
+      <x:c r="A432" s="22" t="str"/>
       <x:c r="B432" t="str"/>
       <x:c r="C432" t="str"/>
-      <x:c r="D432" s="24" t="str"/>
+      <x:c r="D432" s="22" t="str"/>
       <x:c r="E432" t="str"/>
       <x:c r="F432" t="str"/>
       <x:c r="G432" t="str"/>
@@ -6098,10 +7728,10 @@
       <x:c r="J432" t="str"/>
     </x:row>
     <x:row r="433">
-      <x:c r="A433" s="24" t="str"/>
+      <x:c r="A433" s="22" t="str"/>
       <x:c r="B433" t="str"/>
       <x:c r="C433" t="str"/>
-      <x:c r="D433" s="24" t="str"/>
+      <x:c r="D433" s="22" t="str"/>
       <x:c r="E433" t="str"/>
       <x:c r="F433" t="str"/>
       <x:c r="G433" t="str"/>
@@ -6110,10 +7740,10 @@
       <x:c r="J433" t="str"/>
     </x:row>
     <x:row r="434">
-      <x:c r="A434" s="24" t="str"/>
+      <x:c r="A434" s="22" t="str"/>
       <x:c r="B434" t="str"/>
       <x:c r="C434" t="str"/>
-      <x:c r="D434" s="24" t="str"/>
+      <x:c r="D434" s="22" t="str"/>
       <x:c r="E434" t="str"/>
       <x:c r="F434" t="str"/>
       <x:c r="G434" t="str"/>
@@ -6122,10 +7752,10 @@
       <x:c r="J434" t="str"/>
     </x:row>
     <x:row r="435">
-      <x:c r="A435" s="24" t="str"/>
+      <x:c r="A435" s="22" t="str"/>
       <x:c r="B435" t="str"/>
       <x:c r="C435" t="str"/>
-      <x:c r="D435" s="24" t="str"/>
+      <x:c r="D435" s="22" t="str"/>
       <x:c r="E435" t="str"/>
       <x:c r="F435" t="str"/>
       <x:c r="G435" t="str"/>
@@ -6134,10 +7764,10 @@
       <x:c r="J435" t="str"/>
     </x:row>
     <x:row r="436">
-      <x:c r="A436" s="24" t="str"/>
+      <x:c r="A436" s="22" t="str"/>
       <x:c r="B436" t="str"/>
       <x:c r="C436" t="str"/>
-      <x:c r="D436" s="24" t="str"/>
+      <x:c r="D436" s="22" t="str"/>
       <x:c r="E436" t="str"/>
       <x:c r="F436" t="str"/>
       <x:c r="G436" t="str"/>
@@ -6146,10 +7776,10 @@
       <x:c r="J436" t="str"/>
     </x:row>
     <x:row r="437">
-      <x:c r="A437" s="24" t="str"/>
+      <x:c r="A437" s="22" t="str"/>
       <x:c r="B437" t="str"/>
       <x:c r="C437" t="str"/>
-      <x:c r="D437" s="24" t="str"/>
+      <x:c r="D437" s="22" t="str"/>
       <x:c r="E437" t="str"/>
       <x:c r="F437" t="str"/>
       <x:c r="G437" t="str"/>
@@ -6158,10 +7788,10 @@
       <x:c r="J437" t="str"/>
     </x:row>
     <x:row r="438">
-      <x:c r="A438" s="24" t="str"/>
+      <x:c r="A438" s="22" t="str"/>
       <x:c r="B438" t="str"/>
       <x:c r="C438" t="str"/>
-      <x:c r="D438" s="24" t="str"/>
+      <x:c r="D438" s="22" t="str"/>
       <x:c r="E438" t="str"/>
       <x:c r="F438" t="str"/>
       <x:c r="G438" t="str"/>
@@ -6170,10 +7800,10 @@
       <x:c r="J438" t="str"/>
     </x:row>
     <x:row r="439">
-      <x:c r="A439" s="24" t="str"/>
+      <x:c r="A439" s="22" t="str"/>
       <x:c r="B439" t="str"/>
       <x:c r="C439" t="str"/>
-      <x:c r="D439" s="24" t="str"/>
+      <x:c r="D439" s="22" t="str"/>
       <x:c r="E439" t="str"/>
       <x:c r="F439" t="str"/>
       <x:c r="G439" t="str"/>
@@ -6182,10 +7812,10 @@
       <x:c r="J439" t="str"/>
     </x:row>
     <x:row r="440">
-      <x:c r="A440" s="24" t="str"/>
+      <x:c r="A440" s="22" t="str"/>
       <x:c r="B440" t="str"/>
       <x:c r="C440" t="str"/>
-      <x:c r="D440" s="24" t="str"/>
+      <x:c r="D440" s="22" t="str"/>
       <x:c r="E440" t="str"/>
       <x:c r="F440" t="str"/>
       <x:c r="G440" t="str"/>
@@ -6194,10 +7824,10 @@
       <x:c r="J440" t="str"/>
     </x:row>
     <x:row r="441">
-      <x:c r="A441" s="24" t="str"/>
+      <x:c r="A441" s="22" t="str"/>
       <x:c r="B441" t="str"/>
       <x:c r="C441" t="str"/>
-      <x:c r="D441" s="24" t="str"/>
+      <x:c r="D441" s="22" t="str"/>
       <x:c r="E441" t="str"/>
       <x:c r="F441" t="str"/>
       <x:c r="G441" t="str"/>
@@ -6206,10 +7836,10 @@
       <x:c r="J441" t="str"/>
     </x:row>
     <x:row r="442">
-      <x:c r="A442" s="24" t="str"/>
+      <x:c r="A442" s="22" t="str"/>
       <x:c r="B442" t="str"/>
       <x:c r="C442" t="str"/>
-      <x:c r="D442" s="24" t="str"/>
+      <x:c r="D442" s="22" t="str"/>
       <x:c r="E442" t="str"/>
       <x:c r="F442" t="str"/>
       <x:c r="G442" t="str"/>
@@ -6218,10 +7848,10 @@
       <x:c r="J442" t="str"/>
     </x:row>
     <x:row r="443">
-      <x:c r="A443" s="24" t="str"/>
+      <x:c r="A443" s="22" t="str"/>
       <x:c r="B443" t="str"/>
       <x:c r="C443" t="str"/>
-      <x:c r="D443" s="24" t="str"/>
+      <x:c r="D443" s="22" t="str"/>
       <x:c r="E443" t="str"/>
       <x:c r="F443" t="str"/>
       <x:c r="G443" t="str"/>
@@ -6230,10 +7860,10 @@
       <x:c r="J443" t="str"/>
     </x:row>
     <x:row r="444">
-      <x:c r="A444" s="24" t="str"/>
+      <x:c r="A444" s="22" t="str"/>
       <x:c r="B444" t="str"/>
       <x:c r="C444" t="str"/>
-      <x:c r="D444" s="24" t="str"/>
+      <x:c r="D444" s="22" t="str"/>
       <x:c r="E444" t="str"/>
       <x:c r="F444" t="str"/>
       <x:c r="G444" t="str"/>
@@ -6242,10 +7872,10 @@
       <x:c r="J444" t="str"/>
     </x:row>
     <x:row r="445">
-      <x:c r="A445" s="24" t="str"/>
+      <x:c r="A445" s="22" t="str"/>
       <x:c r="B445" t="str"/>
       <x:c r="C445" t="str"/>
-      <x:c r="D445" s="24" t="str"/>
+      <x:c r="D445" s="22" t="str"/>
       <x:c r="E445" t="str"/>
       <x:c r="F445" t="str"/>
       <x:c r="G445" t="str"/>
@@ -6254,10 +7884,10 @@
       <x:c r="J445" t="str"/>
     </x:row>
     <x:row r="446">
-      <x:c r="A446" s="24" t="str"/>
+      <x:c r="A446" s="22" t="str"/>
       <x:c r="B446" t="str"/>
       <x:c r="C446" t="str"/>
-      <x:c r="D446" s="24" t="str"/>
+      <x:c r="D446" s="22" t="str"/>
       <x:c r="E446" t="str"/>
       <x:c r="F446" t="str"/>
       <x:c r="G446" t="str"/>
@@ -6266,10 +7896,10 @@
       <x:c r="J446" t="str"/>
     </x:row>
     <x:row r="447">
-      <x:c r="A447" s="24" t="str"/>
+      <x:c r="A447" s="22" t="str"/>
       <x:c r="B447" t="str"/>
       <x:c r="C447" t="str"/>
-      <x:c r="D447" s="24" t="str"/>
+      <x:c r="D447" s="22" t="str"/>
       <x:c r="E447" t="str"/>
       <x:c r="F447" t="str"/>
       <x:c r="G447" t="str"/>
@@ -6278,10 +7908,10 @@
       <x:c r="J447" t="str"/>
     </x:row>
     <x:row r="448">
-      <x:c r="A448" s="24" t="str"/>
+      <x:c r="A448" s="22" t="str"/>
       <x:c r="B448" t="str"/>
       <x:c r="C448" t="str"/>
-      <x:c r="D448" s="24" t="str"/>
+      <x:c r="D448" s="22" t="str"/>
       <x:c r="E448" t="str"/>
       <x:c r="F448" t="str"/>
       <x:c r="G448" t="str"/>
@@ -6290,10 +7920,10 @@
       <x:c r="J448" t="str"/>
     </x:row>
     <x:row r="449">
-      <x:c r="A449" s="24" t="str"/>
+      <x:c r="A449" s="22" t="str"/>
       <x:c r="B449" t="str"/>
       <x:c r="C449" t="str"/>
-      <x:c r="D449" s="24" t="str"/>
+      <x:c r="D449" s="22" t="str"/>
       <x:c r="E449" t="str"/>
       <x:c r="F449" t="str"/>
       <x:c r="G449" t="str"/>
@@ -6302,10 +7932,10 @@
       <x:c r="J449" t="str"/>
     </x:row>
     <x:row r="450">
-      <x:c r="A450" s="24" t="str"/>
+      <x:c r="A450" s="22" t="str"/>
       <x:c r="B450" t="str"/>
       <x:c r="C450" t="str"/>
-      <x:c r="D450" s="24" t="str"/>
+      <x:c r="D450" s="22" t="str"/>
       <x:c r="E450" t="str"/>
       <x:c r="F450" t="str"/>
       <x:c r="G450" t="str"/>
@@ -6314,10 +7944,10 @@
       <x:c r="J450" t="str"/>
     </x:row>
     <x:row r="451">
-      <x:c r="A451" s="24" t="str"/>
+      <x:c r="A451" s="22" t="str"/>
       <x:c r="B451" t="str"/>
       <x:c r="C451" t="str"/>
-      <x:c r="D451" s="24" t="str"/>
+      <x:c r="D451" s="22" t="str"/>
       <x:c r="E451" t="str"/>
       <x:c r="F451" t="str"/>
       <x:c r="G451" t="str"/>
@@ -6326,10 +7956,10 @@
       <x:c r="J451" t="str"/>
     </x:row>
     <x:row r="452">
-      <x:c r="A452" s="24" t="str"/>
+      <x:c r="A452" s="22" t="str"/>
       <x:c r="B452" t="str"/>
       <x:c r="C452" t="str"/>
-      <x:c r="D452" s="24" t="str"/>
+      <x:c r="D452" s="22" t="str"/>
       <x:c r="E452" t="str"/>
       <x:c r="F452" t="str"/>
       <x:c r="G452" t="str"/>
@@ -6338,10 +7968,10 @@
       <x:c r="J452" t="str"/>
     </x:row>
     <x:row r="453">
-      <x:c r="A453" s="24" t="str"/>
+      <x:c r="A453" s="22" t="str"/>
       <x:c r="B453" t="str"/>
       <x:c r="C453" t="str"/>
-      <x:c r="D453" s="24" t="str"/>
+      <x:c r="D453" s="22" t="str"/>
       <x:c r="E453" t="str"/>
       <x:c r="F453" t="str"/>
       <x:c r="G453" t="str"/>
@@ -6350,10 +7980,10 @@
       <x:c r="J453" t="str"/>
     </x:row>
     <x:row r="454">
-      <x:c r="A454" s="24" t="str"/>
+      <x:c r="A454" s="22" t="str"/>
       <x:c r="B454" t="str"/>
       <x:c r="C454" t="str"/>
-      <x:c r="D454" s="24" t="str"/>
+      <x:c r="D454" s="22" t="str"/>
       <x:c r="E454" t="str"/>
       <x:c r="F454" t="str"/>
       <x:c r="G454" t="str"/>
@@ -6362,10 +7992,10 @@
       <x:c r="J454" t="str"/>
     </x:row>
     <x:row r="455">
-      <x:c r="A455" s="24" t="str"/>
+      <x:c r="A455" s="22" t="str"/>
       <x:c r="B455" t="str"/>
       <x:c r="C455" t="str"/>
-      <x:c r="D455" s="24" t="str"/>
+      <x:c r="D455" s="22" t="str"/>
       <x:c r="E455" t="str"/>
       <x:c r="F455" t="str"/>
       <x:c r="G455" t="str"/>
@@ -6374,10 +8004,10 @@
       <x:c r="J455" t="str"/>
     </x:row>
     <x:row r="456">
-      <x:c r="A456" s="24" t="str"/>
+      <x:c r="A456" s="22" t="str"/>
       <x:c r="B456" t="str"/>
       <x:c r="C456" t="str"/>
-      <x:c r="D456" s="24" t="str"/>
+      <x:c r="D456" s="22" t="str"/>
       <x:c r="E456" t="str"/>
       <x:c r="F456" t="str"/>
       <x:c r="G456" t="str"/>
@@ -6386,10 +8016,10 @@
       <x:c r="J456" t="str"/>
     </x:row>
     <x:row r="457">
-      <x:c r="A457" s="24" t="str"/>
+      <x:c r="A457" s="22" t="str"/>
       <x:c r="B457" t="str"/>
       <x:c r="C457" t="str"/>
-      <x:c r="D457" s="24" t="str"/>
+      <x:c r="D457" s="22" t="str"/>
       <x:c r="E457" t="str"/>
       <x:c r="F457" t="str"/>
       <x:c r="G457" t="str"/>
@@ -6398,10 +8028,10 @@
       <x:c r="J457" t="str"/>
     </x:row>
     <x:row r="458">
-      <x:c r="A458" s="24" t="str"/>
+      <x:c r="A458" s="22" t="str"/>
       <x:c r="B458" t="str"/>
       <x:c r="C458" t="str"/>
-      <x:c r="D458" s="24" t="str"/>
+      <x:c r="D458" s="22" t="str"/>
       <x:c r="E458" t="str"/>
       <x:c r="F458" t="str"/>
       <x:c r="G458" t="str"/>
@@ -6410,10 +8040,10 @@
       <x:c r="J458" t="str"/>
     </x:row>
     <x:row r="459">
-      <x:c r="A459" s="24" t="str"/>
+      <x:c r="A459" s="22" t="str"/>
       <x:c r="B459" t="str"/>
       <x:c r="C459" t="str"/>
-      <x:c r="D459" s="24" t="str"/>
+      <x:c r="D459" s="22" t="str"/>
       <x:c r="E459" t="str"/>
       <x:c r="F459" t="str"/>
       <x:c r="G459" t="str"/>
@@ -6422,10 +8052,10 @@
       <x:c r="J459" t="str"/>
     </x:row>
     <x:row r="460">
-      <x:c r="A460" s="24" t="str"/>
+      <x:c r="A460" s="22" t="str"/>
       <x:c r="B460" t="str"/>
       <x:c r="C460" t="str"/>
-      <x:c r="D460" s="24" t="str"/>
+      <x:c r="D460" s="22" t="str"/>
       <x:c r="E460" t="str"/>
       <x:c r="F460" t="str"/>
       <x:c r="G460" t="str"/>
@@ -6434,10 +8064,10 @@
       <x:c r="J460" t="str"/>
     </x:row>
     <x:row r="461">
-      <x:c r="A461" s="24" t="str"/>
+      <x:c r="A461" s="22" t="str"/>
       <x:c r="B461" t="str"/>
       <x:c r="C461" t="str"/>
-      <x:c r="D461" s="24" t="str"/>
+      <x:c r="D461" s="22" t="str"/>
       <x:c r="E461" t="str"/>
       <x:c r="F461" t="str"/>
       <x:c r="G461" t="str"/>
@@ -6446,10 +8076,10 @@
       <x:c r="J461" t="str"/>
     </x:row>
     <x:row r="462">
-      <x:c r="A462" s="24" t="str"/>
+      <x:c r="A462" s="22" t="str"/>
       <x:c r="B462" t="str"/>
       <x:c r="C462" t="str"/>
-      <x:c r="D462" s="24" t="str"/>
+      <x:c r="D462" s="22" t="str"/>
       <x:c r="E462" t="str"/>
       <x:c r="F462" t="str"/>
       <x:c r="G462" t="str"/>
@@ -6458,10 +8088,10 @@
       <x:c r="J462" t="str"/>
     </x:row>
     <x:row r="463">
-      <x:c r="A463" s="24" t="str"/>
+      <x:c r="A463" s="22" t="str"/>
       <x:c r="B463" t="str"/>
       <x:c r="C463" t="str"/>
-      <x:c r="D463" s="24" t="str"/>
+      <x:c r="D463" s="22" t="str"/>
       <x:c r="E463" t="str"/>
       <x:c r="F463" t="str"/>
       <x:c r="G463" t="str"/>
@@ -6470,10 +8100,10 @@
       <x:c r="J463" t="str"/>
     </x:row>
     <x:row r="464">
-      <x:c r="A464" s="24" t="str"/>
+      <x:c r="A464" s="22" t="str"/>
       <x:c r="B464" t="str"/>
       <x:c r="C464" t="str"/>
-      <x:c r="D464" s="24" t="str"/>
+      <x:c r="D464" s="22" t="str"/>
       <x:c r="E464" t="str"/>
       <x:c r="F464" t="str"/>
       <x:c r="G464" t="str"/>
@@ -6482,10 +8112,10 @@
       <x:c r="J464" t="str"/>
     </x:row>
     <x:row r="465">
-      <x:c r="A465" s="24" t="str"/>
+      <x:c r="A465" s="22" t="str"/>
       <x:c r="B465" t="str"/>
       <x:c r="C465" t="str"/>
-      <x:c r="D465" s="24" t="str"/>
+      <x:c r="D465" s="22" t="str"/>
       <x:c r="E465" t="str"/>
       <x:c r="F465" t="str"/>
       <x:c r="G465" t="str"/>
@@ -6494,10 +8124,10 @@
       <x:c r="J465" t="str"/>
     </x:row>
     <x:row r="466">
-      <x:c r="A466" s="24" t="str"/>
+      <x:c r="A466" s="22" t="str"/>
       <x:c r="B466" t="str"/>
       <x:c r="C466" t="str"/>
-      <x:c r="D466" s="24" t="str"/>
+      <x:c r="D466" s="22" t="str"/>
       <x:c r="E466" t="str"/>
       <x:c r="F466" t="str"/>
       <x:c r="G466" t="str"/>
@@ -6506,10 +8136,10 @@
       <x:c r="J466" t="str"/>
     </x:row>
     <x:row r="467">
-      <x:c r="A467" s="24" t="str"/>
+      <x:c r="A467" s="22" t="str"/>
       <x:c r="B467" t="str"/>
       <x:c r="C467" t="str"/>
-      <x:c r="D467" s="24" t="str"/>
+      <x:c r="D467" s="22" t="str"/>
       <x:c r="E467" t="str"/>
       <x:c r="F467" t="str"/>
       <x:c r="G467" t="str"/>
@@ -6518,10 +8148,10 @@
       <x:c r="J467" t="str"/>
     </x:row>
     <x:row r="468">
-      <x:c r="A468" s="24" t="str"/>
+      <x:c r="A468" s="22" t="str"/>
       <x:c r="B468" t="str"/>
       <x:c r="C468" t="str"/>
-      <x:c r="D468" s="24" t="str"/>
+      <x:c r="D468" s="22" t="str"/>
       <x:c r="E468" t="str"/>
       <x:c r="F468" t="str"/>
       <x:c r="G468" t="str"/>
@@ -6530,10 +8160,10 @@
       <x:c r="J468" t="str"/>
     </x:row>
     <x:row r="469">
-      <x:c r="A469" s="24" t="str"/>
+      <x:c r="A469" s="22" t="str"/>
       <x:c r="B469" t="str"/>
       <x:c r="C469" t="str"/>
-      <x:c r="D469" s="24" t="str"/>
+      <x:c r="D469" s="22" t="str"/>
       <x:c r="E469" t="str"/>
       <x:c r="F469" t="str"/>
       <x:c r="G469" t="str"/>
@@ -6542,10 +8172,10 @@
       <x:c r="J469" t="str"/>
     </x:row>
     <x:row r="470">
-      <x:c r="A470" s="24" t="str"/>
+      <x:c r="A470" s="22" t="str"/>
       <x:c r="B470" t="str"/>
       <x:c r="C470" t="str"/>
-      <x:c r="D470" s="24" t="str"/>
+      <x:c r="D470" s="22" t="str"/>
       <x:c r="E470" t="str"/>
       <x:c r="F470" t="str"/>
       <x:c r="G470" t="str"/>
@@ -6554,10 +8184,10 @@
       <x:c r="J470" t="str"/>
     </x:row>
     <x:row r="471">
-      <x:c r="A471" s="24" t="str"/>
+      <x:c r="A471" s="22" t="str"/>
       <x:c r="B471" t="str"/>
       <x:c r="C471" t="str"/>
-      <x:c r="D471" s="24" t="str"/>
+      <x:c r="D471" s="22" t="str"/>
       <x:c r="E471" t="str"/>
       <x:c r="F471" t="str"/>
       <x:c r="G471" t="str"/>
@@ -6566,10 +8196,10 @@
       <x:c r="J471" t="str"/>
     </x:row>
     <x:row r="472">
-      <x:c r="A472" s="24" t="str"/>
+      <x:c r="A472" s="22" t="str"/>
       <x:c r="B472" t="str"/>
       <x:c r="C472" t="str"/>
-      <x:c r="D472" s="24" t="str"/>
+      <x:c r="D472" s="22" t="str"/>
       <x:c r="E472" t="str"/>
       <x:c r="F472" t="str"/>
       <x:c r="G472" t="str"/>
@@ -6578,10 +8208,10 @@
       <x:c r="J472" t="str"/>
     </x:row>
     <x:row r="473">
-      <x:c r="A473" s="24" t="str"/>
+      <x:c r="A473" s="22" t="str"/>
       <x:c r="B473" t="str"/>
       <x:c r="C473" t="str"/>
-      <x:c r="D473" s="24" t="str"/>
+      <x:c r="D473" s="22" t="str"/>
       <x:c r="E473" t="str"/>
       <x:c r="F473" t="str"/>
       <x:c r="G473" t="str"/>
@@ -6590,10 +8220,10 @@
       <x:c r="J473" t="str"/>
     </x:row>
     <x:row r="474">
-      <x:c r="A474" s="24" t="str"/>
+      <x:c r="A474" s="22" t="str"/>
       <x:c r="B474" t="str"/>
       <x:c r="C474" t="str"/>
-      <x:c r="D474" s="24" t="str"/>
+      <x:c r="D474" s="22" t="str"/>
       <x:c r="E474" t="str"/>
       <x:c r="F474" t="str"/>
       <x:c r="G474" t="str"/>
@@ -6602,10 +8232,10 @@
       <x:c r="J474" t="str"/>
     </x:row>
     <x:row r="475">
-      <x:c r="A475" s="24" t="str"/>
+      <x:c r="A475" s="22" t="str"/>
       <x:c r="B475" t="str"/>
       <x:c r="C475" t="str"/>
-      <x:c r="D475" s="24" t="str"/>
+      <x:c r="D475" s="22" t="str"/>
       <x:c r="E475" t="str"/>
       <x:c r="F475" t="str"/>
       <x:c r="G475" t="str"/>
@@ -6614,10 +8244,10 @@
       <x:c r="J475" t="str"/>
     </x:row>
     <x:row r="476">
-      <x:c r="A476" s="24" t="str"/>
+      <x:c r="A476" s="22" t="str"/>
       <x:c r="B476" t="str"/>
       <x:c r="C476" t="str"/>
-      <x:c r="D476" s="24" t="str"/>
+      <x:c r="D476" s="22" t="str"/>
       <x:c r="E476" t="str"/>
       <x:c r="F476" t="str"/>
       <x:c r="G476" t="str"/>
@@ -6626,10 +8256,10 @@
       <x:c r="J476" t="str"/>
     </x:row>
     <x:row r="477">
-      <x:c r="A477" s="24" t="str"/>
+      <x:c r="A477" s="22" t="str"/>
       <x:c r="B477" t="str"/>
       <x:c r="C477" t="str"/>
-      <x:c r="D477" s="24" t="str"/>
+      <x:c r="D477" s="22" t="str"/>
       <x:c r="E477" t="str"/>
       <x:c r="F477" t="str"/>
       <x:c r="G477" t="str"/>
@@ -6638,10 +8268,10 @@
       <x:c r="J477" t="str"/>
     </x:row>
     <x:row r="478">
-      <x:c r="A478" s="24" t="str"/>
+      <x:c r="A478" s="22" t="str"/>
       <x:c r="B478" t="str"/>
       <x:c r="C478" t="str"/>
-      <x:c r="D478" s="24" t="str"/>
+      <x:c r="D478" s="22" t="str"/>
       <x:c r="E478" t="str"/>
       <x:c r="F478" t="str"/>
       <x:c r="G478" t="str"/>
@@ -6650,10 +8280,10 @@
       <x:c r="J478" t="str"/>
     </x:row>
     <x:row r="479">
-      <x:c r="A479" s="24" t="str"/>
+      <x:c r="A479" s="22" t="str"/>
       <x:c r="B479" t="str"/>
       <x:c r="C479" t="str"/>
-      <x:c r="D479" s="24" t="str"/>
+      <x:c r="D479" s="22" t="str"/>
       <x:c r="E479" t="str"/>
       <x:c r="F479" t="str"/>
       <x:c r="G479" t="str"/>
@@ -6662,10 +8292,10 @@
       <x:c r="J479" t="str"/>
     </x:row>
     <x:row r="480">
-      <x:c r="A480" s="24" t="str"/>
+      <x:c r="A480" s="22" t="str"/>
       <x:c r="B480" t="str"/>
       <x:c r="C480" t="str"/>
-      <x:c r="D480" s="24" t="str"/>
+      <x:c r="D480" s="22" t="str"/>
       <x:c r="E480" t="str"/>
       <x:c r="F480" t="str"/>
       <x:c r="G480" t="str"/>
@@ -6674,10 +8304,10 @@
       <x:c r="J480" t="str"/>
     </x:row>
     <x:row r="481">
-      <x:c r="A481" s="24" t="str"/>
+      <x:c r="A481" s="22" t="str"/>
       <x:c r="B481" t="str"/>
       <x:c r="C481" t="str"/>
-      <x:c r="D481" s="24" t="str"/>
+      <x:c r="D481" s="22" t="str"/>
       <x:c r="E481" t="str"/>
       <x:c r="F481" t="str"/>
       <x:c r="G481" t="str"/>
@@ -6686,10 +8316,10 @@
       <x:c r="J481" t="str"/>
     </x:row>
     <x:row r="482">
-      <x:c r="A482" s="24" t="str"/>
+      <x:c r="A482" s="22" t="str"/>
       <x:c r="B482" t="str"/>
       <x:c r="C482" t="str"/>
-      <x:c r="D482" s="24" t="str"/>
+      <x:c r="D482" s="22" t="str"/>
       <x:c r="E482" t="str"/>
       <x:c r="F482" t="str"/>
       <x:c r="G482" t="str"/>
@@ -6698,10 +8328,10 @@
       <x:c r="J482" t="str"/>
     </x:row>
     <x:row r="483">
-      <x:c r="A483" s="24" t="str"/>
+      <x:c r="A483" s="22" t="str"/>
       <x:c r="B483" t="str"/>
       <x:c r="C483" t="str"/>
-      <x:c r="D483" s="24" t="str"/>
+      <x:c r="D483" s="22" t="str"/>
       <x:c r="E483" t="str"/>
       <x:c r="F483" t="str"/>
       <x:c r="G483" t="str"/>
@@ -6710,10 +8340,10 @@
       <x:c r="J483" t="str"/>
     </x:row>
     <x:row r="484">
-      <x:c r="A484" s="24" t="str"/>
+      <x:c r="A484" s="22" t="str"/>
       <x:c r="B484" t="str"/>
       <x:c r="C484" t="str"/>
-      <x:c r="D484" s="24" t="str"/>
+      <x:c r="D484" s="22" t="str"/>
       <x:c r="E484" t="str"/>
       <x:c r="F484" t="str"/>
       <x:c r="G484" t="str"/>
@@ -6722,10 +8352,10 @@
       <x:c r="J484" t="str"/>
     </x:row>
     <x:row r="485">
-      <x:c r="A485" s="24" t="str"/>
+      <x:c r="A485" s="22" t="str"/>
       <x:c r="B485" t="str"/>
       <x:c r="C485" t="str"/>
-      <x:c r="D485" s="24" t="str"/>
+      <x:c r="D485" s="22" t="str"/>
       <x:c r="E485" t="str"/>
       <x:c r="F485" t="str"/>
       <x:c r="G485" t="str"/>
@@ -6734,10 +8364,10 @@
       <x:c r="J485" t="str"/>
     </x:row>
     <x:row r="486">
-      <x:c r="A486" s="24" t="str"/>
+      <x:c r="A486" s="22" t="str"/>
       <x:c r="B486" t="str"/>
       <x:c r="C486" t="str"/>
-      <x:c r="D486" s="24" t="str"/>
+      <x:c r="D486" s="22" t="str"/>
       <x:c r="E486" t="str"/>
       <x:c r="F486" t="str"/>
       <x:c r="G486" t="str"/>
@@ -6746,10 +8376,10 @@
       <x:c r="J486" t="str"/>
     </x:row>
     <x:row r="487">
-      <x:c r="A487" s="24" t="str"/>
+      <x:c r="A487" s="22" t="str"/>
       <x:c r="B487" t="str"/>
       <x:c r="C487" t="str"/>
-      <x:c r="D487" s="24" t="str"/>
+      <x:c r="D487" s="22" t="str"/>
       <x:c r="E487" t="str"/>
       <x:c r="F487" t="str"/>
       <x:c r="G487" t="str"/>
@@ -6758,10 +8388,10 @@
       <x:c r="J487" t="str"/>
     </x:row>
     <x:row r="488">
-      <x:c r="A488" s="24" t="str"/>
+      <x:c r="A488" s="22" t="str"/>
       <x:c r="B488" t="str"/>
       <x:c r="C488" t="str"/>
-      <x:c r="D488" s="24" t="str"/>
+      <x:c r="D488" s="22" t="str"/>
       <x:c r="E488" t="str"/>
       <x:c r="F488" t="str"/>
       <x:c r="G488" t="str"/>
@@ -6770,10 +8400,10 @@
       <x:c r="J488" t="str"/>
     </x:row>
     <x:row r="489">
-      <x:c r="A489" s="24" t="str"/>
+      <x:c r="A489" s="22" t="str"/>
       <x:c r="B489" t="str"/>
       <x:c r="C489" t="str"/>
-      <x:c r="D489" s="24" t="str"/>
+      <x:c r="D489" s="22" t="str"/>
       <x:c r="E489" t="str"/>
       <x:c r="F489" t="str"/>
       <x:c r="G489" t="str"/>
@@ -6782,10 +8412,10 @@
       <x:c r="J489" t="str"/>
     </x:row>
     <x:row r="490">
-      <x:c r="A490" s="24" t="str"/>
+      <x:c r="A490" s="22" t="str"/>
       <x:c r="B490" t="str"/>
       <x:c r="C490" t="str"/>
-      <x:c r="D490" s="24" t="str"/>
+      <x:c r="D490" s="22" t="str"/>
       <x:c r="E490" t="str"/>
       <x:c r="F490" t="str"/>
       <x:c r="G490" t="str"/>
@@ -6794,10 +8424,10 @@
       <x:c r="J490" t="str"/>
     </x:row>
     <x:row r="491">
-      <x:c r="A491" s="24" t="str"/>
+      <x:c r="A491" s="22" t="str"/>
       <x:c r="B491" t="str"/>
       <x:c r="C491" t="str"/>
-      <x:c r="D491" s="24" t="str"/>
+      <x:c r="D491" s="22" t="str"/>
       <x:c r="E491" t="str"/>
       <x:c r="F491" t="str"/>
       <x:c r="G491" t="str"/>
@@ -6806,10 +8436,10 @@
       <x:c r="J491" t="str"/>
     </x:row>
     <x:row r="492">
-      <x:c r="A492" s="24" t="str"/>
+      <x:c r="A492" s="22" t="str"/>
       <x:c r="B492" t="str"/>
       <x:c r="C492" t="str"/>
-      <x:c r="D492" s="24" t="str"/>
+      <x:c r="D492" s="22" t="str"/>
       <x:c r="E492" t="str"/>
       <x:c r="F492" t="str"/>
       <x:c r="G492" t="str"/>
@@ -6818,10 +8448,10 @@
       <x:c r="J492" t="str"/>
     </x:row>
     <x:row r="493">
-      <x:c r="A493" s="24" t="str"/>
+      <x:c r="A493" s="22" t="str"/>
       <x:c r="B493" t="str"/>
       <x:c r="C493" t="str"/>
-      <x:c r="D493" s="24" t="str"/>
+      <x:c r="D493" s="22" t="str"/>
       <x:c r="E493" t="str"/>
       <x:c r="F493" t="str"/>
       <x:c r="G493" t="str"/>
@@ -6830,10 +8460,10 @@
       <x:c r="J493" t="str"/>
     </x:row>
     <x:row r="494">
-      <x:c r="A494" s="24" t="str"/>
+      <x:c r="A494" s="22" t="str"/>
       <x:c r="B494" t="str"/>
       <x:c r="C494" t="str"/>
-      <x:c r="D494" s="24" t="str"/>
+      <x:c r="D494" s="22" t="str"/>
       <x:c r="E494" t="str"/>
       <x:c r="F494" t="str"/>
       <x:c r="G494" t="str"/>
@@ -6842,10 +8472,10 @@
       <x:c r="J494" t="str"/>
     </x:row>
     <x:row r="495">
-      <x:c r="A495" s="24" t="str"/>
+      <x:c r="A495" s="22" t="str"/>
       <x:c r="B495" t="str"/>
       <x:c r="C495" t="str"/>
-      <x:c r="D495" s="24" t="str"/>
+      <x:c r="D495" s="22" t="str"/>
       <x:c r="E495" t="str"/>
       <x:c r="F495" t="str"/>
       <x:c r="G495" t="str"/>
@@ -6854,10 +8484,10 @@
       <x:c r="J495" t="str"/>
     </x:row>
     <x:row r="496">
-      <x:c r="A496" s="24" t="str"/>
+      <x:c r="A496" s="22" t="str"/>
       <x:c r="B496" t="str"/>
       <x:c r="C496" t="str"/>
-      <x:c r="D496" s="24" t="str"/>
+      <x:c r="D496" s="22" t="str"/>
       <x:c r="E496" t="str"/>
       <x:c r="F496" t="str"/>
       <x:c r="G496" t="str"/>
@@ -6866,10 +8496,10 @@
       <x:c r="J496" t="str"/>
     </x:row>
     <x:row r="497">
-      <x:c r="A497" s="24" t="str"/>
+      <x:c r="A497" s="22" t="str"/>
       <x:c r="B497" t="str"/>
       <x:c r="C497" t="str"/>
-      <x:c r="D497" s="24" t="str"/>
+      <x:c r="D497" s="22" t="str"/>
       <x:c r="E497" t="str"/>
       <x:c r="F497" t="str"/>
       <x:c r="G497" t="str"/>
@@ -6878,10 +8508,10 @@
       <x:c r="J497" t="str"/>
     </x:row>
     <x:row r="498">
-      <x:c r="A498" s="24" t="str"/>
+      <x:c r="A498" s="22" t="str"/>
       <x:c r="B498" t="str"/>
       <x:c r="C498" t="str"/>
-      <x:c r="D498" s="24" t="str"/>
+      <x:c r="D498" s="22" t="str"/>
       <x:c r="E498" t="str"/>
       <x:c r="F498" t="str"/>
       <x:c r="G498" t="str"/>
@@ -6890,10 +8520,10 @@
       <x:c r="J498" t="str"/>
     </x:row>
     <x:row r="499">
-      <x:c r="A499" s="24" t="str"/>
+      <x:c r="A499" s="22" t="str"/>
       <x:c r="B499" t="str"/>
       <x:c r="C499" t="str"/>
-      <x:c r="D499" s="24" t="str"/>
+      <x:c r="D499" s="22" t="str"/>
       <x:c r="E499" t="str"/>
       <x:c r="F499" t="str"/>
       <x:c r="G499" t="str"/>
@@ -6902,10 +8532,10 @@
       <x:c r="J499" t="str"/>
     </x:row>
     <x:row r="500">
-      <x:c r="A500" s="24" t="str"/>
+      <x:c r="A500" s="22" t="str"/>
       <x:c r="B500" t="str"/>
       <x:c r="C500" t="str"/>
-      <x:c r="D500" s="24" t="str"/>
+      <x:c r="D500" s="22" t="str"/>
       <x:c r="E500" t="str"/>
       <x:c r="F500" t="str"/>
       <x:c r="G500" t="str"/>
@@ -6914,10 +8544,10 @@
       <x:c r="J500" t="str"/>
     </x:row>
     <x:row r="501">
-      <x:c r="A501" s="24" t="str"/>
+      <x:c r="A501" s="22" t="str"/>
       <x:c r="B501" t="str"/>
       <x:c r="C501" t="str"/>
-      <x:c r="D501" s="24" t="str"/>
+      <x:c r="D501" s="22" t="str"/>
       <x:c r="E501" t="str"/>
       <x:c r="F501" t="str"/>
       <x:c r="G501" t="str"/>
@@ -6926,47 +8556,32 @@
       <x:c r="J501" t="str"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="6">
+  <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="E2:E501">
       <x:formula1>"Regional,Gymnasial"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="F2:F501">
-      <x:formula1>Workshops!$B$2:$B$31</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="G2:G501">
-      <x:formula1>Workshops!$B$2:$B$31</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="H2:H501">
-      <x:formula1>Workshops!$B$2:$B$31</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="I2:I501">
-      <x:formula1>Workshops!$B$2:$B$31</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="J2:J501">
-      <x:formula1>Workshops!$A$2:$A$31</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="40" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="44" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="20" t="str">
+      <x:c r="A1" s="18" t="str">
         <x:v>Person-ID</x:v>
       </x:c>
-      <x:c r="B1" s="20" t="str">
+      <x:c r="B1" s="18" t="str">
         <x:v>Durchführungs-ID</x:v>
       </x:c>
-      <x:c r="C1" s="20" t="str">
+      <x:c r="C1" s="18" t="str">
         <x:v>Grund / Hinweis</x:v>
       </x:c>
     </x:row>
@@ -9471,14 +11086,6 @@
       <x:c r="C501" t="str"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
-    <x:dataValidation type="list" sqref="A2:A501">
-      <x:formula1>Kursanwahl!$A$2:$A$501</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="B2:B501">
-      <x:formula1>Workshops!$A$2:$A$31</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>